--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -1459,13 +1459,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.38951664352</v>
+        <v>46065.55618331018</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.547958055555</v>
+        <v>46092.714624722226</v>
       </c>
       <c r="D4" s="5">
-        <v>46141.61330008102</v>
+        <v>46141.77996674769</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1508,13 +1508,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.38951724537</v>
+        <v>46065.556183912035</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.54792871528</v>
+        <v>46092.71459538194</v>
       </c>
       <c r="D5" s="8">
-        <v>46147.008964189816</v>
+        <v>46147.17563085648</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1571,13 +1571,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.38951759259</v>
+        <v>46065.55618425926</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.547929305554</v>
+        <v>46092.714595972226</v>
       </c>
       <c r="D6" s="5">
-        <v>46147.008964039356</v>
+        <v>46147.17563070601</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1636,13 +1636,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.38951795139</v>
+        <v>46065.55618461806</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54792972222</v>
+        <v>46092.71459638889</v>
       </c>
       <c r="D7" s="8">
-        <v>46147.0089640625</v>
+        <v>46147.175630729165</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1701,13 +1701,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.38951825231</v>
+        <v>46065.55618491898</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.547930138884</v>
+        <v>46092.714596805556</v>
       </c>
       <c r="D8" s="5">
-        <v>46147.008964016204</v>
+        <v>46147.175630682876</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1764,13 +1764,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.38951861111</v>
+        <v>46065.556185277776</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54793074074</v>
+        <v>46092.71459740741</v>
       </c>
       <c r="D9" s="8">
-        <v>46147.008964444445</v>
+        <v>46147.17563111111</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1829,13 +1829,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.38951894676</v>
+        <v>46065.55618561343</v>
       </c>
       <c r="C10" s="5">
-        <v>46154.39088356482</v>
+        <v>46154.55755023148</v>
       </c>
       <c r="D10" s="5">
-        <v>46154.43029402778</v>
+        <v>46154.59696069444</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1878,13 +1878,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.38951925926</v>
+        <v>46065.556185925925</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.30508837963</v>
+        <v>46114.471755046296</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.3051068287</v>
+        <v>46114.471773495374</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1943,11 +1943,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.38951961805</v>
+        <v>46065.556186284724</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46160.51675268519</v>
+        <v>46160.68341935185</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2006,13 +2006,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.38951994213</v>
+        <v>46065.556186608796</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.3467809838</v>
+        <v>46114.51344765046</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.346793668985</v>
+        <v>46114.51346033565</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2059,13 +2059,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.38951606481</v>
+        <v>46065.55618273148</v>
       </c>
       <c r="C14" s="5">
-        <v>46107.54966615741</v>
+        <v>46107.71633282407</v>
       </c>
       <c r="D14" s="5">
-        <v>46107.549685289356</v>
+        <v>46107.71635195602</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2124,13 +2124,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.38951679398</v>
+        <v>46065.55618346065</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.549728645834</v>
+        <v>46107.7163953125</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.54974859954</v>
+        <v>46107.7164152662</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2189,13 +2189,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.38951710648</v>
+        <v>46065.55618377315</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.549819328706</v>
+        <v>46107.71648599537</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.549835011574</v>
+        <v>46107.71650167824</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2254,13 +2254,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.38951743055</v>
+        <v>46065.55618409722</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34676168981</v>
+        <v>46114.513428356484</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.346781898144</v>
+        <v>46114.513448564816</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2319,13 +2319,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.389517766205</v>
+        <v>46065.55618443287</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.346884178245</v>
+        <v>46114.5135508449</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.346898125004</v>
+        <v>46114.51356479166</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2372,13 +2372,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.38951809028</v>
+        <v>46065.55618475695</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.549961875004</v>
+        <v>46107.71662854167</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.549979965275</v>
+        <v>46107.71664663195</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2437,13 +2437,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.3895184375</v>
+        <v>46065.55618510417</v>
       </c>
       <c r="C20" s="5">
-        <v>46107.55000682871</v>
+        <v>46107.71667349537</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.55002149305</v>
+        <v>46107.71668815972</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2502,13 +2502,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.38951879629</v>
+        <v>46065.55618546296</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.34686798611</v>
+        <v>46114.51353465278</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.346884375</v>
+        <v>46114.513551041666</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2567,13 +2567,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.389519131946</v>
+        <v>46065.55618579861</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.55006083334</v>
+        <v>46107.716727499996</v>
       </c>
       <c r="D22" s="5">
-        <v>46107.55007583334</v>
+        <v>46107.7167425</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2632,13 +2632,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.38951710648</v>
+        <v>46065.55618377315</v>
       </c>
       <c r="C23" s="8">
-        <v>46107.55029724537</v>
+        <v>46107.71696391204</v>
       </c>
       <c r="D23" s="8">
-        <v>46107.55031475694</v>
+        <v>46107.71698142361</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2697,13 +2697,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.38951741898</v>
+        <v>46065.55618408565</v>
       </c>
       <c r="C24" s="5">
-        <v>46155.6624807176</v>
+        <v>46155.829147384255</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.66249818287</v>
+        <v>46155.829164849536</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2750,13 +2750,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.38951790509</v>
+        <v>46065.55618457176</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.62113777778</v>
+        <v>46111.787804444444</v>
       </c>
       <c r="D25" s="8">
-        <v>46111.62113914352</v>
+        <v>46111.787805810185</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2815,13 +2815,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.38951821759</v>
+        <v>46065.55618488426</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.62098633102</v>
+        <v>46111.787652997686</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.62098839121</v>
+        <v>46111.787655057866</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -2876,13 +2876,13 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.38951853009</v>
+        <v>46065.55618519676</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.62103630787</v>
+        <v>46111.787702974536</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.621037777775</v>
+        <v>46111.78770444445</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -2937,13 +2937,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.38951887732</v>
+        <v>46065.55618554398</v>
       </c>
       <c r="C28" s="5">
-        <v>46154.39079186342</v>
+        <v>46154.55745853009</v>
       </c>
       <c r="D28" s="5">
-        <v>46181.017315474535</v>
+        <v>46181.1839821412</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3002,13 +3002,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.389519247685</v>
+        <v>46065.55618591435</v>
       </c>
       <c r="C29" s="8">
-        <v>46129.428751875</v>
+        <v>46129.59541854166</v>
       </c>
       <c r="D29" s="8">
-        <v>46129.428753125</v>
+        <v>46129.595419791665</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3063,13 +3063,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.389519652774</v>
+        <v>46065.556186319445</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.39077186343</v>
+        <v>46154.55743853009</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.390773391206</v>
+        <v>46154.55744005787</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3124,13 +3124,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.389519965276</v>
+        <v>46065.55618663195</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.6213315625</v>
+        <v>46111.78799822916</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.62134431713</v>
+        <v>46111.7880109838</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3189,13 +3189,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.389520625</v>
+        <v>46065.556187291666</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.6212590162</v>
+        <v>46111.787925682875</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.62126035879</v>
+        <v>46111.78792702546</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3250,13 +3250,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.38952170139</v>
+        <v>46065.55618836806</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.62131702546</v>
+        <v>46111.787983692135</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.621318668986</v>
+        <v>46111.78798533565</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3311,13 +3311,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46067.69045797454</v>
+        <v>46067.8571246412</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.62158</v>
+        <v>46111.78824666666</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.621604375</v>
+        <v>46111.78827104167</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3376,13 +3376,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46067.69061002315</v>
+        <v>46067.857276689814</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.62149472222</v>
+        <v>46111.78816138889</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.621495949075</v>
+        <v>46111.78816261574</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3431,13 +3431,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46067.69069710648</v>
+        <v>46067.857363773146</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.621563622684</v>
+        <v>46111.788230289356</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.62156525463</v>
+        <v>46111.788231921295</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3486,13 +3486,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46067.69078010417</v>
+        <v>46067.85744677084</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.621536562496</v>
+        <v>46111.78820322917</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.62153788195</v>
+        <v>46111.78820454861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3541,13 +3541,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.38952369213</v>
+        <v>46065.556190358795</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.621906747685</v>
+        <v>46111.78857341435</v>
       </c>
       <c r="D38" s="5">
-        <v>46135.41441790509</v>
+        <v>46135.581084571764</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3606,13 +3606,13 @@
         <v>147</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.3895240625</v>
+        <v>46065.55619072917</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.622016134264</v>
+        <v>46111.78868280092</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.346894375005</v>
+        <v>46114.51356104166</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>77</v>
@@ -3667,13 +3667,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.389524432874</v>
+        <v>46065.55619109954</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.62209619213</v>
+        <v>46111.78876285879</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.62209752315</v>
+        <v>46111.78876418981</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3728,13 +3728,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.38951626157</v>
+        <v>46065.55618292824</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.630251319446</v>
+        <v>46114.79691798611</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.630264004634</v>
+        <v>46114.79693067129</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3781,13 +3781,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.64314940972</v>
+        <v>46070.80981607639</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59716626158</v>
+        <v>46114.76383292824</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.597182604164</v>
+        <v>46114.763849270836</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3846,13 +3846,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.38951653935</v>
+        <v>46065.55618320602</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.630152858794</v>
+        <v>46114.796819525465</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.63016990741</v>
+        <v>46114.796836574074</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -3911,13 +3911,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46086.459633136576</v>
+        <v>46086.62629980324</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.63019277778</v>
+        <v>46114.79685944444</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.63020814815</v>
+        <v>46114.79687481481</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3974,13 +3974,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="8">
-        <v>46086.45999190972</v>
+        <v>46086.62665857639</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.63022989583</v>
+        <v>46114.796896562504</v>
       </c>
       <c r="D45" s="8">
-        <v>46123.013042708335</v>
+        <v>46123.179709375</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>169</v>
@@ -4037,13 +4037,13 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46065.38951681713</v>
+        <v>46065.5561834838</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.550847199076</v>
+        <v>46107.71751386574</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.55086023148</v>
+        <v>46107.71752689815</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4090,13 +4090,13 @@
         <v>175</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.389517083335</v>
+        <v>46065.55618375</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.55074893519</v>
+        <v>46107.71741560185</v>
       </c>
       <c r="D47" s="8">
-        <v>46135.41438908565</v>
+        <v>46135.581055752315</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>176</v>
@@ -4155,13 +4155,13 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46065.38951743055</v>
+        <v>46065.55618409722</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.55083096065</v>
+        <v>46107.717497627316</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.55084773148</v>
+        <v>46107.717514398144</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>181</v>
@@ -4220,13 +4220,13 @@
         <v>185</v>
       </c>
       <c r="B49" s="8">
-        <v>46065.3895194213</v>
+        <v>46065.55618608797</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.55120021991</v>
+        <v>46107.717866886574</v>
       </c>
       <c r="D49" s="8">
-        <v>46135.414471655095</v>
+        <v>46135.58113832176</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>186</v>
@@ -4271,13 +4271,13 @@
         <v>188</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.38952199074</v>
+        <v>46065.55618865741</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.5509347801</v>
+        <v>46107.717601446755</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.55095311343</v>
+        <v>46107.71761978009</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>189</v>
@@ -4336,13 +4336,13 @@
         <v>193</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.389524479164</v>
+        <v>46065.556191145835</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.551059722224</v>
+        <v>46107.71772638889</v>
       </c>
       <c r="D51" s="8">
-        <v>46135.41434469908</v>
+        <v>46135.581011365735</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>194</v>
@@ -4401,13 +4401,13 @@
         <v>197</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.389516446754</v>
+        <v>46065.556183113426</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.55118377315</v>
+        <v>46107.71785043982</v>
       </c>
       <c r="D52" s="5">
-        <v>46135.41444496528</v>
+        <v>46135.581111631946</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>198</v>
@@ -4464,13 +4464,13 @@
         <v>201</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.389516875</v>
+        <v>46065.55618354167</v>
       </c>
       <c r="C53" s="8">
-        <v>46154.3908409838</v>
+        <v>46154.55750765046</v>
       </c>
       <c r="D53" s="8">
-        <v>46154.390852916666</v>
+        <v>46154.55751958334</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>173</v>
@@ -4517,13 +4517,13 @@
         <v>203</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.38951719907</v>
+        <v>46065.556183865745</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.5523522338</v>
+        <v>46107.71901890046</v>
       </c>
       <c r="D54" s="5">
-        <v>46135.414625868056</v>
+        <v>46135.58129253473</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>204</v>
@@ -4580,13 +4580,13 @@
         <v>206</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.389517511576</v>
+        <v>46065.55618417824</v>
       </c>
       <c r="C55" s="8">
-        <v>46107.552395833336</v>
+        <v>46107.7190625</v>
       </c>
       <c r="D55" s="8">
-        <v>46135.41464859954</v>
+        <v>46135.5813152662</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>207</v>
@@ -4643,13 +4643,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.38951784722</v>
+        <v>46065.55618451389</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.55242975694</v>
+        <v>46107.71909642361</v>
       </c>
       <c r="D56" s="5">
-        <v>46135.41467578703</v>
+        <v>46135.581342453705</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4706,13 +4706,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.3895181713</v>
+        <v>46065.55618483796</v>
       </c>
       <c r="C57" s="8">
-        <v>46154.39082331018</v>
+        <v>46154.557489976854</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.01731546296</v>
+        <v>46181.18398212963</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>56</v>
@@ -4769,13 +4769,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.389518807875</v>
+        <v>46065.55618547453</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.5519617824</v>
+        <v>46107.718628449074</v>
       </c>
       <c r="D58" s="5">
-        <v>46135.41480413194</v>
+        <v>46135.581470798614</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4818,13 +4818,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.389519108794</v>
+        <v>46065.556185775466</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.55139565972</v>
+        <v>46107.718062326385</v>
       </c>
       <c r="D59" s="8">
-        <v>46115.99319787037</v>
+        <v>46116.15986453704</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4883,13 +4883,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.3895194213</v>
+        <v>46065.55618608797</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.55150810185</v>
+        <v>46107.71817476852</v>
       </c>
       <c r="D60" s="5">
-        <v>46135.41579668982</v>
+        <v>46135.58246335648</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4946,13 +4946,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.38951586805</v>
+        <v>46065.556182534725</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.5516275463</v>
+        <v>46107.71829421296</v>
       </c>
       <c r="D61" s="8">
-        <v>46135.414911597225</v>
+        <v>46135.58157826389</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>225</v>
@@ -5009,13 +5009,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.38951627315</v>
+        <v>46065.556182939814</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.55173928241</v>
+        <v>46107.718405949076</v>
       </c>
       <c r="D62" s="5">
-        <v>46135.41491212963</v>
+        <v>46135.58157879629</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5072,13 +5072,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.38951688657</v>
+        <v>46065.55618355324</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.551834872684</v>
+        <v>46107.71850153935</v>
       </c>
       <c r="D63" s="8">
-        <v>46122.01326224537</v>
+        <v>46122.17992891204</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>170</v>
@@ -5135,13 +5135,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.389517187505</v>
+        <v>46065.55618385416</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.551940335645</v>
+        <v>46107.718607002316</v>
       </c>
       <c r="D64" s="5">
-        <v>46135.416054305555</v>
+        <v>46135.58272097222</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5198,11 +5198,11 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.38951746528</v>
+        <v>46065.55618413194</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46126.694463657404</v>
+        <v>46126.861130324076</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5245,11 +5245,11 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.389517766205</v>
+        <v>46065.55618443287</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46154.43029587963</v>
+        <v>46154.5969625463</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5306,11 +5306,11 @@
         <v>246</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.389518055556</v>
+        <v>46065.55618472223</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46154.4302944213</v>
+        <v>46154.59696108796</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>247</v>
@@ -5367,11 +5367,11 @@
         <v>250</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.389518344906</v>
+        <v>46065.55618501158</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46135.41697914352</v>
+        <v>46135.583645810184</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>251</v>
@@ -5428,11 +5428,11 @@
         <v>253</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.38951862269</v>
+        <v>46065.55618528935</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46135.417107511574</v>
+        <v>46135.583774178245</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>254</v>
@@ -5489,11 +5489,11 @@
         <v>256</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.38951620371</v>
+        <v>46065.55618287037</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.694466863424</v>
+        <v>46126.861133530096</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>257</v>
@@ -5542,11 +5542,11 @@
         <v>259</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.389516863426</v>
+        <v>46065.55618353009</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46135.41723983796</v>
+        <v>46135.58390650463</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>260</v>
@@ -5605,11 +5605,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.3895165625</v>
+        <v>46065.55618322917</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46135.41730811342</v>
+        <v>46135.58397478009</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5668,11 +5668,11 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46086.45525143518</v>
+        <v>46086.62191810185</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46126.694466967594</v>
+        <v>46126.86113363426</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5715,11 +5715,11 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46086.455943946756</v>
+        <v>46086.62261061343</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46135.41739127315</v>
+        <v>46135.584057939814</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5778,11 +5778,11 @@
         <v>272</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.380529780094</v>
+        <v>46090.54719644676</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46135.41745488426</v>
+        <v>46135.58412155093</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -355,397 +355,397 @@
     <t>Generación OC Tableros,Fabricación Tablero</t>
   </si>
   <si>
+    <t>1213242666769875</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros</t>
+  </si>
+  <si>
+    <t>Tableros,Fabricación Tablero</t>
+  </si>
+  <si>
+    <t>1213242666769876</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero</t>
+  </si>
+  <si>
+    <t>Tableros,Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>1213242666769877</t>
+  </si>
+  <si>
+    <t>rodete</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete,Fabricación Rodete</t>
+  </si>
+  <si>
+    <t>1213242666769878</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete,rodete</t>
+  </si>
+  <si>
+    <t>1213242666769879</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete</t>
+  </si>
+  <si>
+    <t>rodete,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1213282776310054</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Generación oc Motor,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1213282776310056</t>
+  </si>
+  <si>
+    <t>Generación oc Motor</t>
+  </si>
+  <si>
+    <t>Fabricación motor,Planos motor proveedor,Motor</t>
+  </si>
+  <si>
+    <t>1213282776310057</t>
+  </si>
+  <si>
+    <t>Fabricación motor</t>
+  </si>
+  <si>
+    <t>Recepcion Motor,Motor</t>
+  </si>
+  <si>
+    <t>1213282776310058</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Motor,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1213242666769884</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>1213242666769885</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales,Materiales a codigo // compras locales aprovisionamientomiento</t>
+  </si>
+  <si>
+    <t>1213242666769886</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213242666769890</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos Definitivos,Planos Preliminar,Check Planos,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213317916241331</t>
+  </si>
+  <si>
+    <t>Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Check Planos,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>1213242666769891</t>
+  </si>
+  <si>
+    <t>Planos Definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check Planos</t>
+  </si>
+  <si>
+    <t>1213541970459377</t>
+  </si>
+  <si>
+    <t>Check Planos</t>
+  </si>
+  <si>
+    <t>Planos Preliminar,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Control de calidad Armado,Montaje Rodete,Montaje motor,Armado,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213541970459379</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>1213242666769892</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213242666769893</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:</t>
+  </si>
+  <si>
+    <t>1213242666769894</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1213242666769895</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213242666769896</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Caldereria:,Armado</t>
+  </si>
+  <si>
+    <t>1213242667616377</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Check Planos</t>
+  </si>
+  <si>
+    <t>Caldereria:,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213242667616378</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>Armado,Check Planos</t>
+  </si>
+  <si>
+    <t>Caldereria:,Revestimiento</t>
+  </si>
+  <si>
+    <t>1213242667616379</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion Rodete,Recepcion Motor,Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>1213242667616380</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213242667616381</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213242667616382</t>
+  </si>
+  <si>
+    <t>Recepcion Motor</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213242667616383</t>
+  </si>
+  <si>
+    <t>Bodega:,Revision tableros pruebas</t>
+  </si>
+  <si>
+    <t>1213242667616385</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1213242667616386</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Rodete,Montaje motor,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213242667616387</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Motor,Check Planos</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,Montaje:</t>
+  </si>
+  <si>
+    <t>1213242667616388</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Alabe,Check Planos</t>
+  </si>
+  <si>
+    <t>1213242667616389</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Rodete,Check Planos</t>
+  </si>
+  <si>
+    <t>1213242667616391</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Alabe,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>Montaje:,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213242667616392</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Montaje:,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1213242667616393</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Despacho,PACKING LIST,Embalaje,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1213242667616394</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,Revision tableros pruebas</t>
+  </si>
+  <si>
+    <t>Logistica:,Embalaje</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213242666769875</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros</t>
-  </si>
-  <si>
-    <t>Tableros,Fabricación Tablero</t>
-  </si>
-  <si>
-    <t>1213242666769876</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero</t>
-  </si>
-  <si>
-    <t>Tableros,Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>1213242666769877</t>
-  </si>
-  <si>
-    <t>rodete</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete,Fabricación Rodete</t>
-  </si>
-  <si>
-    <t>1213242666769878</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete,rodete</t>
-  </si>
-  <si>
-    <t>1213242666769879</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete</t>
-  </si>
-  <si>
-    <t>rodete,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1213282776310054</t>
-  </si>
-  <si>
-    <t>Motor</t>
-  </si>
-  <si>
-    <t>Generación oc Motor,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1213282776310056</t>
-  </si>
-  <si>
-    <t>Generación oc Motor</t>
-  </si>
-  <si>
-    <t>Fabricación motor,Planos motor proveedor,Motor</t>
-  </si>
-  <si>
-    <t>1213282776310057</t>
-  </si>
-  <si>
-    <t>Fabricación motor</t>
-  </si>
-  <si>
-    <t>Recepcion Motor,Motor</t>
-  </si>
-  <si>
-    <t>1213282776310058</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Motor,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1213242666769884</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>1213242666769885</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales,Materiales a codigo // compras locales aprovisionamientomiento</t>
-  </si>
-  <si>
-    <t>1213242666769886</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213242666769890</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos Definitivos,Planos Preliminar,Check Planos,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213317916241331</t>
-  </si>
-  <si>
-    <t>Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Check Planos,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>1213242666769891</t>
-  </si>
-  <si>
-    <t>Planos Definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check Planos</t>
-  </si>
-  <si>
-    <t>1213541970459377</t>
-  </si>
-  <si>
-    <t>Check Planos</t>
-  </si>
-  <si>
-    <t>Planos Preliminar,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Control de calidad Armado,Montaje Rodete,Montaje motor,Armado,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213541970459379</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>1213242666769892</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213242666769893</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:</t>
-  </si>
-  <si>
-    <t>1213242666769894</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1213242666769895</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213242666769896</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Caldereria:,Armado</t>
-  </si>
-  <si>
-    <t>1213242667616377</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Check Planos</t>
-  </si>
-  <si>
-    <t>Caldereria:,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213242667616378</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>Armado,Check Planos</t>
-  </si>
-  <si>
-    <t>Caldereria:,Revestimiento</t>
-  </si>
-  <si>
-    <t>1213242667616379</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion Rodete,Recepcion Motor,Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>1213242667616380</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213242667616381</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213242667616382</t>
-  </si>
-  <si>
-    <t>Recepcion Motor</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213242667616383</t>
-  </si>
-  <si>
-    <t>Bodega:,Revision tableros pruebas</t>
-  </si>
-  <si>
-    <t>1213242667616385</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1213242667616386</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Rodete,Montaje motor,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213242667616387</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Motor,Check Planos</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,Montaje:</t>
-  </si>
-  <si>
-    <t>1213242667616388</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Alabe,Check Planos</t>
-  </si>
-  <si>
-    <t>1213242667616389</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Rodete,Check Planos</t>
-  </si>
-  <si>
-    <t>1213242667616391</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>Montaje:,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213242667616392</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1213242667616393</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Despacho,PACKING LIST,Embalaje,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1213242667616394</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,Revision tableros pruebas</t>
-  </si>
-  <si>
-    <t>Logistica:,Embalaje</t>
   </si>
   <si>
     <t>Tarea en curso</t>
@@ -2943,7 +2943,7 @@
         <v>46154.55745853009</v>
       </c>
       <c r="D28" s="5">
-        <v>46181.1839821412</v>
+        <v>46189.16759819444</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -2990,8 +2990,8 @@
       <c r="S28" s="6">
         <v>1</v>
       </c>
-      <c r="T28" s="12" t="s">
-        <v>114</v>
+      <c r="T28" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U28" s="11" t="s">
         <v>32</v>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46065.55618591435</v>
@@ -3011,7 +3011,7 @@
         <v>46129.595419791665</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3044,7 +3044,7 @@
         <v>85</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46065.556186319445</v>
@@ -3072,7 +3072,7 @@
         <v>46154.55744005787</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3102,10 +3102,10 @@
         <v>112</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3121,7 +3121,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46065.55618663195</v>
@@ -3133,7 +3133,7 @@
         <v>46111.7880109838</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3163,7 +3163,7 @@
         <v>96</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>96</v>
@@ -3186,7 +3186,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46065.556187291666</v>
@@ -3198,7 +3198,7 @@
         <v>46111.78792702546</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3225,13 +3225,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46065.55618836806</v>
@@ -3259,7 +3259,7 @@
         <v>46111.78798533565</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3308,7 +3308,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46067.8571246412</v>
@@ -3320,7 +3320,7 @@
         <v>46111.78827104167</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3350,7 +3350,7 @@
         <v>96</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46067.857276689814</v>
@@ -3385,7 +3385,7 @@
         <v>46111.78816261574</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3428,7 +3428,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46067.857363773146</v>
@@ -3440,7 +3440,7 @@
         <v>46111.788231921295</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3467,13 +3467,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46067.85744677084</v>
@@ -3495,7 +3495,7 @@
         <v>46111.78820454861</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3522,13 +3522,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46065.556190358795</v>
@@ -3550,16 +3550,16 @@
         <v>46135.581084571764</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="I38" s="5">
         <v>46065</v>
@@ -3580,7 +3580,7 @@
         <v>96</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>96</v>
@@ -3603,7 +3603,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46065.55619072917</v>
@@ -3621,10 +3621,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>144</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>145</v>
       </c>
       <c r="I39" s="8">
         <v>46065</v>
@@ -3642,13 +3642,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>75</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46065.55619109954</v>
@@ -3676,16 +3676,16 @@
         <v>46111.78876418981</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="I40" s="5">
         <v>46076</v>
@@ -3703,13 +3703,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3725,7 +3725,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46065.55618292824</v>
@@ -3737,7 +3737,7 @@
         <v>46114.79693067129</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>25</v>
@@ -3761,7 +3761,7 @@
         <v>26</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46070.80981607639</v>
@@ -3790,16 +3790,16 @@
         <v>46114.763849270836</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I42" s="5">
         <v>46063</v>
@@ -3817,13 +3817,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="5">
         <v>46069</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46065.55618320602</v>
@@ -3855,16 +3855,16 @@
         <v>46114.796836574074</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>158</v>
       </c>
       <c r="I43" s="8">
         <v>46084</v>
@@ -3882,13 +3882,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="P43" s="9" t="s">
         <v>162</v>
-      </c>
-      <c r="P43" s="9" t="s">
-        <v>163</v>
       </c>
       <c r="Q43" s="8">
         <v>46090</v>
@@ -3908,7 +3908,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46086.62629980324</v>
@@ -3920,16 +3920,16 @@
         <v>46114.79687481481</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -3945,13 +3945,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="Q44" s="5">
         <v>46091</v>
@@ -3971,7 +3971,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B45" s="8">
         <v>46086.62665857639</v>
@@ -3983,16 +3983,16 @@
         <v>46123.179709375</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>158</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4008,13 +4008,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O45" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="P45" s="9" t="s">
         <v>170</v>
-      </c>
-      <c r="P45" s="9" t="s">
-        <v>171</v>
       </c>
       <c r="Q45" s="8">
         <v>46122</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46065.5561834838</v>
@@ -4046,7 +4046,7 @@
         <v>46107.71752689815</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4070,7 +4070,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4087,7 +4087,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="8">
         <v>46065.55618375</v>
@@ -4099,16 +4099,16 @@
         <v>46135.581055752315</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>177</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>178</v>
       </c>
       <c r="I47" s="8">
         <v>46092</v>
@@ -4126,13 +4126,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="8">
         <v>46093</v>
@@ -4152,7 +4152,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46065.55618409722</v>
@@ -4164,16 +4164,16 @@
         <v>46107.717514398144</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
+      <c r="H48" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I48" s="5">
         <v>46094</v>
@@ -4191,13 +4191,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q48" s="5">
         <v>46097</v>
@@ -4217,7 +4217,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B49" s="8">
         <v>46065.55618608797</v>
@@ -4229,7 +4229,7 @@
         <v>46135.58113832176</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>25</v>
@@ -4253,7 +4253,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4268,7 +4268,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46065.55618865741</v>
@@ -4280,16 +4280,16 @@
         <v>46107.71761978009</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I50" s="5">
         <v>46098</v>
@@ -4307,13 +4307,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q50" s="5">
         <v>46100</v>
@@ -4333,7 +4333,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B51" s="8">
         <v>46065.556191145835</v>
@@ -4345,16 +4345,16 @@
         <v>46135.581011365735</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="I51" s="8">
         <v>46101</v>
@@ -4372,13 +4372,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="P51" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="Q51" s="8">
         <v>46107</v>
@@ -4398,7 +4398,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B52" s="5">
         <v>46065.556183113426</v>
@@ -4410,16 +4410,16 @@
         <v>46135.581111631946</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4435,13 +4435,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="Q52" s="5">
         <v>46108</v>
@@ -4461,7 +4461,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B53" s="8">
         <v>46065.55618354167</v>
@@ -4473,7 +4473,7 @@
         <v>46154.55751958334</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4497,7 +4497,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B54" s="5">
         <v>46065.556183865745</v>
@@ -4526,16 +4526,16 @@
         <v>46135.58129253473</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4551,13 +4551,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46070</v>
@@ -4577,7 +4577,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B55" s="8">
         <v>46065.55618417824</v>
@@ -4589,16 +4589,16 @@
         <v>46135.5813152662</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>177</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>178</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4614,13 +4614,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="8">
         <v>46086</v>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46065.55618451389</v>
@@ -4652,16 +4652,16 @@
         <v>46135.581342453705</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -4677,13 +4677,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46065.55618483796</v>
@@ -4712,7 +4712,7 @@
         <v>46154.557489976854</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.18398212963</v>
+        <v>46189.16759806713</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>56</v>
@@ -4721,10 +4721,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>177</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>178</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -4740,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="8">
         <v>46188</v>
@@ -4757,8 +4757,8 @@
       <c r="S57" s="9">
         <v>1</v>
       </c>
-      <c r="T57" s="12" t="s">
-        <v>114</v>
+      <c r="T57" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U57" s="11" t="s">
         <v>32</v>
@@ -4766,7 +4766,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46065.55618547453</v>
@@ -4778,7 +4778,7 @@
         <v>46135.581470798614</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4802,7 +4802,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4815,7 +4815,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B59" s="8">
         <v>46065.556185775466</v>
@@ -4827,7 +4827,7 @@
         <v>46116.15986453704</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -4854,13 +4854,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q59" s="8">
         <v>46115</v>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46065.55618608797</v>
@@ -4892,7 +4892,7 @@
         <v>46135.58246335648</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4917,13 +4917,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="Q60" s="5">
         <v>46119</v>
@@ -4943,7 +4943,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
         <v>46065.556182534725</v>
@@ -4955,7 +4955,7 @@
         <v>46135.58157826389</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -4980,13 +4980,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="8">
         <v>46119</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46065.556182939814</v>
@@ -5018,7 +5018,7 @@
         <v>46135.58157879629</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5043,13 +5043,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q62" s="5">
         <v>46120</v>
@@ -5069,7 +5069,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B63" s="8">
         <v>46065.55618355324</v>
@@ -5081,7 +5081,7 @@
         <v>46122.17992891204</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5106,13 +5106,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O63" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>231</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>232</v>
       </c>
       <c r="Q63" s="8">
         <v>46121</v>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B64" s="5">
         <v>46065.55618385416</v>
@@ -5144,7 +5144,7 @@
         <v>46135.58272097222</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5169,13 +5169,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q64" s="5">
         <v>46125</v>
@@ -5195,7 +5195,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B65" s="8">
         <v>46065.55618413194</v>
@@ -5205,7 +5205,7 @@
         <v>46126.861130324076</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5229,7 +5229,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5242,7 +5242,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B66" s="5">
         <v>46065.55618443287</v>
@@ -5252,16 +5252,16 @@
         <v>46154.5969625463</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5277,13 +5277,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>243</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="Q66" s="5">
         <v>46191</v>
@@ -5295,7 +5295,7 @@
         <v>0</v>
       </c>
       <c r="T66" s="12" t="s">
-        <v>114</v>
+        <v>244</v>
       </c>
       <c r="U66" s="12" t="s">
         <v>245</v>
@@ -5338,7 +5338,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>248</v>
@@ -5380,10 +5380,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5399,7 +5399,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>247</v>
@@ -5441,10 +5441,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5460,7 +5460,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>251</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46154.5969625463</v>
+        <v>46191.16754472222</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>239</v>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46154.59696108796</v>
+        <v>46191.17808832176</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>247</v>
@@ -5355,8 +5355,8 @@
       <c r="S67" s="9">
         <v>0</v>
       </c>
-      <c r="T67" s="11" t="s">
-        <v>106</v>
+      <c r="T67" s="12" t="s">
+        <v>244</v>
       </c>
       <c r="U67" s="10" t="s">
         <v>107</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -745,22 +745,22 @@
     <t>Logistica:,Embalaje</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1213242667616395</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Revision tableros pruebas</t>
+  </si>
+  <si>
+    <t>Logistica:,PACKING LIST</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213242667616395</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Revision tableros pruebas</t>
-  </si>
-  <si>
-    <t>Logistica:,PACKING LIST</t>
   </si>
   <si>
     <t>1213242667616396</t>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46191.16754472222</v>
+        <v>46192.20270207176</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>239</v>
@@ -5294,16 +5294,16 @@
       <c r="S66" s="6">
         <v>0</v>
       </c>
-      <c r="T66" s="12" t="s">
+      <c r="T66" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U66" s="12" t="s">
         <v>244</v>
-      </c>
-      <c r="U66" s="12" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B67" s="8">
         <v>46065.55618472223</v>
@@ -5313,7 +5313,7 @@
         <v>46191.17808832176</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5341,10 +5341,10 @@
         <v>236</v>
       </c>
       <c r="O67" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="P67" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="P67" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="Q67" s="8">
         <v>46198</v>
@@ -5356,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="T67" s="12" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="U67" s="10" t="s">
         <v>107</v>
@@ -5402,7 +5402,7 @@
         <v>236</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>252</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -5371,7 +5371,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46135.583645810184</v>
+        <v>46195.19091449074</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>251</v>
@@ -5416,8 +5416,8 @@
       <c r="S68" s="6">
         <v>0</v>
       </c>
-      <c r="T68" s="11" t="s">
-        <v>106</v>
+      <c r="T68" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="U68" s="10" t="s">
         <v>107</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46135.583774178245</v>
+        <v>46196.19992135417</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>254</v>
@@ -5477,8 +5477,8 @@
       <c r="S69" s="9">
         <v>0</v>
       </c>
-      <c r="T69" s="11" t="s">
-        <v>106</v>
+      <c r="T69" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="U69" s="10" t="s">
         <v>107</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="274">
   <si>
     <t>50001515 - CLIENTE POR DEFINIR</t>
   </si>
@@ -154,6 +154,9 @@
     <t>Ingenieria electrica,Revision tableros pruebas</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1213188413754429</t>
   </si>
   <si>
@@ -743,9 +746,6 @@
   </si>
   <si>
     <t>Logistica:,Embalaje</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213242667616395</t>
@@ -1835,7 +1835,7 @@
         <v>46154.55755023148</v>
       </c>
       <c r="D10" s="5">
-        <v>46154.59696069444</v>
+        <v>46196.78518097222</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1871,11 +1871,13 @@
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="U10" s="12" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="8">
         <v>46065.556185925925</v>
@@ -1887,16 +1889,16 @@
         <v>46114.471773495374</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I11" s="8">
         <v>46058</v>
@@ -1920,7 +1922,7 @@
         <v>40</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q11" s="8">
         <v>46062</v>
@@ -1940,26 +1942,28 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="5">
         <v>46065.556186284724</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46196.78516135417</v>
+      </c>
       <c r="D12" s="5">
-        <v>46160.68341935185</v>
+        <v>46196.78516428241</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I12" s="5">
         <v>46191</v>
@@ -1980,10 +1984,10 @@
         <v>45</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="5">
         <v>46129</v>
@@ -2003,7 +2007,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" s="8">
         <v>46065.556186608796</v>
@@ -2015,7 +2019,7 @@
         <v>46114.51346033565</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2039,7 +2043,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2056,7 +2060,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="5">
         <v>46065.55618273148</v>
@@ -2068,7 +2072,7 @@
         <v>46107.71635195602</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2095,13 +2099,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q14" s="5">
         <v>46059</v>
@@ -2121,7 +2125,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8">
         <v>46065.55618346065</v>
@@ -2133,7 +2137,7 @@
         <v>46107.7164152662</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2160,13 +2164,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="8">
         <v>46059</v>
@@ -2186,7 +2190,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
         <v>46065.55618377315</v>
@@ -2198,7 +2202,7 @@
         <v>46107.71650167824</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2225,13 +2229,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46062</v>
@@ -2251,7 +2255,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="8">
         <v>46065.55618409722</v>
@@ -2263,7 +2267,7 @@
         <v>46114.513448564816</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2290,13 +2294,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="8">
         <v>46063</v>
@@ -2316,7 +2320,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46065.55618443287</v>
@@ -2328,7 +2332,7 @@
         <v>46114.51356479166</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2352,10 +2356,10 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -2369,7 +2373,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="8">
         <v>46065.55618475695</v>
@@ -2381,7 +2385,7 @@
         <v>46107.71664663195</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2408,13 +2412,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q19" s="8">
         <v>46063</v>
@@ -2434,7 +2438,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46065.55618510417</v>
@@ -2446,7 +2450,7 @@
         <v>46107.71668815972</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2473,13 +2477,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46063</v>
@@ -2499,7 +2503,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" s="8">
         <v>46065.55618546296</v>
@@ -2511,7 +2515,7 @@
         <v>46114.513551041666</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2538,13 +2542,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="8">
         <v>46063</v>
@@ -2564,7 +2568,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46065.55618579861</v>
@@ -2576,16 +2580,16 @@
         <v>46107.7167425</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I22" s="5">
         <v>46062</v>
@@ -2603,13 +2607,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46063</v>
@@ -2629,7 +2633,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46065.55618377315</v>
@@ -2641,16 +2645,16 @@
         <v>46107.71698142361</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="8">
         <v>46063</v>
@@ -2668,13 +2672,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q23" s="8">
         <v>46064</v>
@@ -2694,7 +2698,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46065.55618408565</v>
@@ -2706,7 +2710,7 @@
         <v>46155.829164849536</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>25</v>
@@ -2730,7 +2734,7 @@
         <v>26</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2747,7 +2751,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="8">
         <v>46065.55618457176</v>
@@ -2759,16 +2763,16 @@
         <v>46111.787805810185</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I25" s="8">
         <v>46064</v>
@@ -2786,13 +2790,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q25" s="8">
         <v>46069</v>
@@ -2812,7 +2816,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46065.55618488426</v>
@@ -2824,16 +2828,16 @@
         <v>46111.787655057866</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I26" s="5">
         <v>46064</v>
@@ -2851,13 +2855,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2865,15 +2869,15 @@
         <v>0</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="8">
         <v>46065.55618519676</v>
@@ -2885,16 +2889,16 @@
         <v>46111.78770444445</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I27" s="8">
         <v>46066</v>
@@ -2912,13 +2916,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2926,15 +2930,15 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46065.55618554398</v>
@@ -2946,16 +2950,16 @@
         <v>46189.16759819444</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I28" s="5">
         <v>46129</v>
@@ -2973,13 +2977,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q28" s="5">
         <v>46188</v>
@@ -2999,7 +3003,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="8">
         <v>46065.55618591435</v>
@@ -3011,16 +3015,16 @@
         <v>46129.595419791665</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I29" s="8">
         <v>46129</v>
@@ -3038,13 +3042,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3052,15 +3056,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46065.556186319445</v>
@@ -3072,16 +3076,16 @@
         <v>46154.55744005787</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" s="5">
         <v>46141</v>
@@ -3099,13 +3103,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3113,15 +3117,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="8">
         <v>46065.55618663195</v>
@@ -3133,16 +3137,16 @@
         <v>46111.7880109838</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I31" s="8">
         <v>46064</v>
@@ -3160,13 +3164,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q31" s="8">
         <v>46084</v>
@@ -3186,7 +3190,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46065.556187291666</v>
@@ -3198,16 +3202,16 @@
         <v>46111.78792702546</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I32" s="5">
         <v>46064</v>
@@ -3225,13 +3229,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3239,15 +3243,15 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46065.55618836806</v>
@@ -3259,16 +3263,16 @@
         <v>46111.78798533565</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I33" s="8">
         <v>46065</v>
@@ -3286,13 +3290,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3300,15 +3304,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46067.8571246412</v>
@@ -3320,16 +3324,16 @@
         <v>46111.78827104167</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I34" s="5">
         <v>46064</v>
@@ -3347,10 +3351,10 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3373,7 +3377,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46067.857276689814</v>
@@ -3385,16 +3389,16 @@
         <v>46111.78816261574</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I35" s="8">
         <v>46064</v>
@@ -3412,13 +3416,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3428,7 +3432,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46067.857363773146</v>
@@ -3440,16 +3444,16 @@
         <v>46111.788231921295</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I36" s="5">
         <v>46073</v>
@@ -3467,13 +3471,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3483,7 +3487,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46067.85744677084</v>
@@ -3495,16 +3499,16 @@
         <v>46111.78820454861</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I37" s="8">
         <v>46073</v>
@@ -3522,13 +3526,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3538,7 +3542,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46065.556190358795</v>
@@ -3550,16 +3554,16 @@
         <v>46135.581084571764</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I38" s="5">
         <v>46065</v>
@@ -3577,13 +3581,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q38" s="5">
         <v>46091</v>
@@ -3603,7 +3607,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B39" s="8">
         <v>46065.55619072917</v>
@@ -3615,16 +3619,16 @@
         <v>46114.51356104166</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I39" s="8">
         <v>46065</v>
@@ -3642,13 +3646,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3656,15 +3660,15 @@
         <v>0</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46065.55619109954</v>
@@ -3676,16 +3680,16 @@
         <v>46111.78876418981</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I40" s="5">
         <v>46076</v>
@@ -3703,13 +3707,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3717,15 +3721,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46065.55618292824</v>
@@ -3737,7 +3741,7 @@
         <v>46114.79693067129</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>25</v>
@@ -3761,7 +3765,7 @@
         <v>26</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -3778,7 +3782,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46070.80981607639</v>
@@ -3790,16 +3794,16 @@
         <v>46114.763849270836</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I42" s="5">
         <v>46063</v>
@@ -3817,13 +3821,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q42" s="5">
         <v>46069</v>
@@ -3843,7 +3847,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46065.55618320602</v>
@@ -3855,16 +3859,16 @@
         <v>46114.796836574074</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I43" s="8">
         <v>46084</v>
@@ -3882,13 +3886,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q43" s="8">
         <v>46090</v>
@@ -3908,7 +3912,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46086.62629980324</v>
@@ -3920,16 +3924,16 @@
         <v>46114.79687481481</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -3945,13 +3949,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="5">
         <v>46091</v>
@@ -3971,7 +3975,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="8">
         <v>46086.62665857639</v>
@@ -3983,16 +3987,16 @@
         <v>46123.179709375</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4008,13 +4012,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="8">
         <v>46122</v>
@@ -4034,7 +4038,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46065.5561834838</v>
@@ -4046,7 +4050,7 @@
         <v>46107.71752689815</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4070,7 +4074,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4087,7 +4091,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="8">
         <v>46065.55618375</v>
@@ -4099,16 +4103,16 @@
         <v>46135.581055752315</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I47" s="8">
         <v>46092</v>
@@ -4126,13 +4130,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q47" s="8">
         <v>46093</v>
@@ -4152,7 +4156,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46065.55618409722</v>
@@ -4164,16 +4168,16 @@
         <v>46107.717514398144</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I48" s="5">
         <v>46094</v>
@@ -4191,13 +4195,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q48" s="5">
         <v>46097</v>
@@ -4217,7 +4221,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B49" s="8">
         <v>46065.55618608797</v>
@@ -4229,7 +4233,7 @@
         <v>46135.58113832176</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>25</v>
@@ -4253,7 +4257,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4268,7 +4272,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B50" s="5">
         <v>46065.55618865741</v>
@@ -4280,16 +4284,16 @@
         <v>46107.71761978009</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I50" s="5">
         <v>46098</v>
@@ -4307,13 +4311,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q50" s="5">
         <v>46100</v>
@@ -4333,7 +4337,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B51" s="8">
         <v>46065.556191145835</v>
@@ -4345,16 +4349,16 @@
         <v>46135.581011365735</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I51" s="8">
         <v>46101</v>
@@ -4372,13 +4376,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q51" s="8">
         <v>46107</v>
@@ -4398,7 +4402,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B52" s="5">
         <v>46065.556183113426</v>
@@ -4410,16 +4414,16 @@
         <v>46135.581111631946</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4435,13 +4439,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q52" s="5">
         <v>46108</v>
@@ -4461,7 +4465,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B53" s="8">
         <v>46065.55618354167</v>
@@ -4473,7 +4477,7 @@
         <v>46154.55751958334</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4497,7 +4501,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4514,7 +4518,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B54" s="5">
         <v>46065.556183865745</v>
@@ -4526,16 +4530,16 @@
         <v>46135.58129253473</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4551,13 +4555,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q54" s="5">
         <v>46070</v>
@@ -4577,7 +4581,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B55" s="8">
         <v>46065.55618417824</v>
@@ -4589,16 +4593,16 @@
         <v>46135.5813152662</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4614,13 +4618,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q55" s="8">
         <v>46086</v>
@@ -4640,7 +4644,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B56" s="5">
         <v>46065.55618451389</v>
@@ -4652,16 +4656,16 @@
         <v>46135.581342453705</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -4677,13 +4681,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4703,7 +4707,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B57" s="8">
         <v>46065.55618483796</v>
@@ -4715,16 +4719,16 @@
         <v>46189.16759806713</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -4740,13 +4744,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q57" s="8">
         <v>46188</v>
@@ -4766,7 +4770,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46065.55618547453</v>
@@ -4778,7 +4782,7 @@
         <v>46135.581470798614</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4802,7 +4806,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4815,7 +4819,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="8">
         <v>46065.556185775466</v>
@@ -4827,16 +4831,16 @@
         <v>46116.15986453704</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I59" s="8">
         <v>46111</v>
@@ -4854,13 +4858,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="8">
         <v>46115</v>
@@ -4880,7 +4884,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46065.55618608797</v>
@@ -4892,16 +4896,16 @@
         <v>46135.58246335648</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -4917,13 +4921,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q60" s="5">
         <v>46119</v>
@@ -4943,7 +4947,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B61" s="8">
         <v>46065.556182534725</v>
@@ -4955,16 +4959,16 @@
         <v>46135.58157826389</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -4980,13 +4984,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="8">
         <v>46119</v>
@@ -5006,7 +5010,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
         <v>46065.556182939814</v>
@@ -5018,16 +5022,16 @@
         <v>46135.58157879629</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5043,13 +5047,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q62" s="5">
         <v>46120</v>
@@ -5069,7 +5073,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B63" s="8">
         <v>46065.55618355324</v>
@@ -5081,16 +5085,16 @@
         <v>46122.17992891204</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5106,13 +5110,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q63" s="8">
         <v>46121</v>
@@ -5132,7 +5136,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B64" s="5">
         <v>46065.55618385416</v>
@@ -5144,16 +5148,16 @@
         <v>46135.58272097222</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5169,13 +5173,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q64" s="5">
         <v>46125</v>
@@ -5195,7 +5199,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B65" s="8">
         <v>46065.55618413194</v>
@@ -5205,7 +5209,7 @@
         <v>46126.861130324076</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5229,7 +5233,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5242,26 +5246,26 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B66" s="5">
         <v>46065.55618443287</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46192.20270207176</v>
+        <v>46196.785174178236</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5277,13 +5281,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q66" s="5">
         <v>46191</v>
@@ -5298,7 +5302,7 @@
         <v>31</v>
       </c>
       <c r="U66" s="12" t="s">
-        <v>244</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5310,7 +5314,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46191.17808832176</v>
+        <v>46196.78517265046</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5319,10 +5323,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5338,7 +5342,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>247</v>
@@ -5359,7 +5363,7 @@
         <v>249</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5380,10 +5384,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5399,7 +5403,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>246</v>
@@ -5420,7 +5424,7 @@
         <v>249</v>
       </c>
       <c r="U68" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5441,10 +5445,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5460,7 +5464,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>251</v>
@@ -5481,7 +5485,7 @@
         <v>249</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5531,10 +5535,10 @@
         <v>0</v>
       </c>
       <c r="T70" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U70" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5594,10 +5598,10 @@
         <v>0</v>
       </c>
       <c r="T71" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5657,10 +5661,10 @@
         <v>0</v>
       </c>
       <c r="T72" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5728,10 +5732,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I74" s="5">
         <v>46206</v>
@@ -5767,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="T74" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5791,10 +5795,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I75" s="8">
         <v>46218</v>
@@ -5830,10 +5834,10 @@
         <v>0</v>
       </c>
       <c r="T75" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46126.861130324076</v>
+        <v>46197.49889483796</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5312,9 +5312,11 @@
       <c r="B67" s="8">
         <v>46065.55618472223</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="8">
+        <v>46197.498886817135</v>
+      </c>
       <c r="D67" s="8">
-        <v>46196.78517265046</v>
+        <v>46197.4989081713</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5357,13 +5359,13 @@
         <v>46198</v>
       </c>
       <c r="S67" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="U67" s="10" t="s">
-        <v>108</v>
+      <c r="U67" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5375,7 +5377,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46195.19091449074</v>
+        <v>46197.49890484953</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>251</v>
@@ -5423,8 +5425,8 @@
       <c r="T68" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="U68" s="10" t="s">
-        <v>108</v>
+      <c r="U68" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="274">
   <si>
     <t>50001515 - CLIENTE POR DEFINIR</t>
   </si>
@@ -5204,9 +5204,11 @@
       <c r="B65" s="8">
         <v>46065.55618413194</v>
       </c>
-      <c r="C65" s="9"/>
+      <c r="C65" s="8">
+        <v>46197.58418903935</v>
+      </c>
       <c r="D65" s="8">
-        <v>46197.49889483796</v>
+        <v>46197.584207858796</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5240,9 +5242,13 @@
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
-      <c r="S65" s="9"/>
+      <c r="S65" s="9">
+        <v>1</v>
+      </c>
       <c r="T65" s="9"/>
-      <c r="U65" s="9"/>
+      <c r="U65" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
@@ -5251,9 +5257,11 @@
       <c r="B66" s="5">
         <v>46065.55618443287</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46197.584170208334</v>
+      </c>
       <c r="D66" s="5">
-        <v>46196.785174178236</v>
+        <v>46197.584189560184</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5296,13 +5304,13 @@
         <v>46191</v>
       </c>
       <c r="S66" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U66" s="12" t="s">
-        <v>47</v>
+      <c r="U66" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5316,7 +5324,7 @@
         <v>46197.498886817135</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.4989081713</v>
+        <v>46197.58418701389</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5364,8 +5372,8 @@
       <c r="T67" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="U67" s="11" t="s">
-        <v>32</v>
+      <c r="U67" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5375,9 +5383,11 @@
       <c r="B68" s="5">
         <v>46065.55618501158</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46197.58183895833</v>
+      </c>
       <c r="D68" s="5">
-        <v>46197.49890484953</v>
+        <v>46197.58185835648</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>251</v>
@@ -5420,13 +5430,13 @@
         <v>46202</v>
       </c>
       <c r="S68" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="U68" s="12" t="s">
-        <v>47</v>
+      <c r="U68" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5436,9 +5446,11 @@
       <c r="B69" s="8">
         <v>46065.55618528935</v>
       </c>
-      <c r="C69" s="9"/>
+      <c r="C69" s="8">
+        <v>46197.58195770833</v>
+      </c>
       <c r="D69" s="8">
-        <v>46196.19992135417</v>
+        <v>46197.58252302083</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>254</v>
@@ -5481,13 +5493,13 @@
         <v>46203</v>
       </c>
       <c r="S69" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="U69" s="10" t="s">
-        <v>108</v>
+      <c r="U69" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5552,7 +5564,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46135.58390650463</v>
+        <v>46197.581980393516</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>260</v>
@@ -5602,8 +5614,8 @@
       <c r="T71" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="U71" s="10" t="s">
-        <v>108</v>
+      <c r="U71" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5615,7 +5627,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46135.58397478009</v>
+        <v>46197.581980787036</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5665,8 +5677,8 @@
       <c r="T72" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="U72" s="10" t="s">
-        <v>108</v>
+      <c r="U72" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5725,7 +5737,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46135.584057939814</v>
+        <v>46197.58198023148</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5775,8 +5787,8 @@
       <c r="T74" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="U74" s="10" t="s">
-        <v>108</v>
+      <c r="U74" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -1459,13 +1459,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.55618331018</v>
+        <v>46065.38951664352</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.714624722226</v>
+        <v>46092.547958055555</v>
       </c>
       <c r="D4" s="5">
-        <v>46141.77996674769</v>
+        <v>46141.61330008102</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1508,13 +1508,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.556183912035</v>
+        <v>46065.38951724537</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.71459538194</v>
+        <v>46092.54792871528</v>
       </c>
       <c r="D5" s="8">
-        <v>46147.17563085648</v>
+        <v>46147.008964189816</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1571,13 +1571,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.55618425926</v>
+        <v>46065.38951759259</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.714595972226</v>
+        <v>46092.547929305554</v>
       </c>
       <c r="D6" s="5">
-        <v>46147.17563070601</v>
+        <v>46147.008964039356</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1636,13 +1636,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.55618461806</v>
+        <v>46065.38951795139</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71459638889</v>
+        <v>46092.54792972222</v>
       </c>
       <c r="D7" s="8">
-        <v>46147.175630729165</v>
+        <v>46147.0089640625</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1701,13 +1701,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.55618491898</v>
+        <v>46065.38951825231</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.714596805556</v>
+        <v>46092.547930138884</v>
       </c>
       <c r="D8" s="5">
-        <v>46147.175630682876</v>
+        <v>46147.008964016204</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1764,13 +1764,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.556185277776</v>
+        <v>46065.38951861111</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71459740741</v>
+        <v>46092.54793074074</v>
       </c>
       <c r="D9" s="8">
-        <v>46147.17563111111</v>
+        <v>46147.008964444445</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1829,13 +1829,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.55618561343</v>
+        <v>46065.38951894676</v>
       </c>
       <c r="C10" s="5">
-        <v>46154.55755023148</v>
+        <v>46154.39088356482</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.78518097222</v>
+        <v>46196.618514305555</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1880,13 +1880,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.556185925925</v>
+        <v>46065.38951925926</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.471755046296</v>
+        <v>46114.30508837963</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.471773495374</v>
+        <v>46114.3051068287</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1945,13 +1945,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.556186284724</v>
+        <v>46065.38951961805</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.78516135417</v>
+        <v>46196.6184946875</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.78516428241</v>
+        <v>46196.61849761574</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2010,13 +2010,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.556186608796</v>
+        <v>46065.38951994213</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51344765046</v>
+        <v>46114.3467809838</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.51346033565</v>
+        <v>46114.346793668985</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2063,13 +2063,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.55618273148</v>
+        <v>46065.38951606481</v>
       </c>
       <c r="C14" s="5">
-        <v>46107.71633282407</v>
+        <v>46107.54966615741</v>
       </c>
       <c r="D14" s="5">
-        <v>46107.71635195602</v>
+        <v>46107.549685289356</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2128,13 +2128,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.55618346065</v>
+        <v>46065.38951679398</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.7163953125</v>
+        <v>46107.549728645834</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.7164152662</v>
+        <v>46107.54974859954</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2193,13 +2193,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.55618377315</v>
+        <v>46065.38951710648</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.71648599537</v>
+        <v>46107.549819328706</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.71650167824</v>
+        <v>46107.549835011574</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2258,13 +2258,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.55618409722</v>
+        <v>46065.38951743055</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.513428356484</v>
+        <v>46114.34676168981</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.513448564816</v>
+        <v>46114.346781898144</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2323,13 +2323,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.55618443287</v>
+        <v>46065.389517766205</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.5135508449</v>
+        <v>46114.346884178245</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.51356479166</v>
+        <v>46114.346898125004</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2376,13 +2376,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.55618475695</v>
+        <v>46065.38951809028</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.71662854167</v>
+        <v>46107.549961875004</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.71664663195</v>
+        <v>46107.549979965275</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2441,13 +2441,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.55618510417</v>
+        <v>46065.3895184375</v>
       </c>
       <c r="C20" s="5">
-        <v>46107.71667349537</v>
+        <v>46107.55000682871</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.71668815972</v>
+        <v>46107.55002149305</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2506,13 +2506,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.55618546296</v>
+        <v>46065.38951879629</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.51353465278</v>
+        <v>46114.34686798611</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.513551041666</v>
+        <v>46114.346884375</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>
@@ -2571,13 +2571,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.55618579861</v>
+        <v>46065.389519131946</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.716727499996</v>
+        <v>46107.55006083334</v>
       </c>
       <c r="D22" s="5">
-        <v>46107.7167425</v>
+        <v>46107.55007583334</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2636,13 +2636,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.55618377315</v>
+        <v>46065.38951710648</v>
       </c>
       <c r="C23" s="8">
-        <v>46107.71696391204</v>
+        <v>46107.55029724537</v>
       </c>
       <c r="D23" s="8">
-        <v>46107.71698142361</v>
+        <v>46107.55031475694</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2701,13 +2701,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.55618408565</v>
+        <v>46065.38951741898</v>
       </c>
       <c r="C24" s="5">
-        <v>46155.829147384255</v>
+        <v>46155.6624807176</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.829164849536</v>
+        <v>46155.66249818287</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2754,13 +2754,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.55618457176</v>
+        <v>46065.38951790509</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.787804444444</v>
+        <v>46111.62113777778</v>
       </c>
       <c r="D25" s="8">
-        <v>46111.787805810185</v>
+        <v>46111.62113914352</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2819,13 +2819,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.55618488426</v>
+        <v>46065.38951821759</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.787652997686</v>
+        <v>46111.62098633102</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.787655057866</v>
+        <v>46111.62098839121</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2880,13 +2880,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.55618519676</v>
+        <v>46065.38951853009</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.787702974536</v>
+        <v>46111.62103630787</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.78770444445</v>
+        <v>46111.621037777775</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>110</v>
@@ -2941,13 +2941,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.55618554398</v>
+        <v>46065.38951887732</v>
       </c>
       <c r="C28" s="5">
-        <v>46154.55745853009</v>
+        <v>46154.39079186342</v>
       </c>
       <c r="D28" s="5">
-        <v>46189.16759819444</v>
+        <v>46189.00093152778</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3006,13 +3006,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.55618591435</v>
+        <v>46065.389519247685</v>
       </c>
       <c r="C29" s="8">
-        <v>46129.59541854166</v>
+        <v>46129.428751875</v>
       </c>
       <c r="D29" s="8">
-        <v>46129.595419791665</v>
+        <v>46129.428753125</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3067,13 +3067,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.556186319445</v>
+        <v>46065.389519652774</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.55743853009</v>
+        <v>46154.39077186343</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.55744005787</v>
+        <v>46154.390773391206</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3128,13 +3128,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.55618663195</v>
+        <v>46065.389519965276</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.78799822916</v>
+        <v>46111.6213315625</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.7880109838</v>
+        <v>46111.62134431713</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3193,13 +3193,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.556187291666</v>
+        <v>46065.389520625</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.787925682875</v>
+        <v>46111.6212590162</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.78792702546</v>
+        <v>46111.62126035879</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3254,13 +3254,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.55618836806</v>
+        <v>46065.38952170139</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.787983692135</v>
+        <v>46111.62131702546</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.78798533565</v>
+        <v>46111.621318668986</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3315,13 +3315,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46067.8571246412</v>
+        <v>46067.69045797454</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.78824666666</v>
+        <v>46111.62158</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.78827104167</v>
+        <v>46111.621604375</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3380,13 +3380,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46067.857276689814</v>
+        <v>46067.69061002315</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.78816138889</v>
+        <v>46111.62149472222</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.78816261574</v>
+        <v>46111.621495949075</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3435,13 +3435,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46067.857363773146</v>
+        <v>46067.69069710648</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.788230289356</v>
+        <v>46111.621563622684</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.788231921295</v>
+        <v>46111.62156525463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3490,13 +3490,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46067.85744677084</v>
+        <v>46067.69078010417</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.78820322917</v>
+        <v>46111.621536562496</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.78820454861</v>
+        <v>46111.62153788195</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3545,13 +3545,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.556190358795</v>
+        <v>46065.38952369213</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.78857341435</v>
+        <v>46111.621906747685</v>
       </c>
       <c r="D38" s="5">
-        <v>46135.581084571764</v>
+        <v>46135.41441790509</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3610,13 +3610,13 @@
         <v>147</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.55619072917</v>
+        <v>46065.3895240625</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.78868280092</v>
+        <v>46111.622016134264</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.51356104166</v>
+        <v>46114.346894375005</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>78</v>
@@ -3671,13 +3671,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.55619109954</v>
+        <v>46065.389524432874</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.78876285879</v>
+        <v>46111.62209619213</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.78876418981</v>
+        <v>46111.62209752315</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3732,13 +3732,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.55618292824</v>
+        <v>46065.38951626157</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.79691798611</v>
+        <v>46114.630251319446</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.79693067129</v>
+        <v>46114.630264004634</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3785,13 +3785,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.80981607639</v>
+        <v>46070.64314940972</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.76383292824</v>
+        <v>46114.59716626158</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.763849270836</v>
+        <v>46114.597182604164</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3850,13 +3850,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.55618320602</v>
+        <v>46065.38951653935</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.796819525465</v>
+        <v>46114.630152858794</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.796836574074</v>
+        <v>46114.63016990741</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -3915,13 +3915,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46086.62629980324</v>
+        <v>46086.459633136576</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.79685944444</v>
+        <v>46114.63019277778</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.79687481481</v>
+        <v>46114.63020814815</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3978,13 +3978,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="8">
-        <v>46086.62665857639</v>
+        <v>46086.45999190972</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.796896562504</v>
+        <v>46114.63022989583</v>
       </c>
       <c r="D45" s="8">
-        <v>46123.179709375</v>
+        <v>46123.013042708335</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>169</v>
@@ -4041,13 +4041,13 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46065.5561834838</v>
+        <v>46065.38951681713</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.71751386574</v>
+        <v>46107.550847199076</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.71752689815</v>
+        <v>46107.55086023148</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4094,13 +4094,13 @@
         <v>175</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.55618375</v>
+        <v>46065.389517083335</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.71741560185</v>
+        <v>46107.55074893519</v>
       </c>
       <c r="D47" s="8">
-        <v>46135.581055752315</v>
+        <v>46135.41438908565</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>176</v>
@@ -4159,13 +4159,13 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46065.55618409722</v>
+        <v>46065.38951743055</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.717497627316</v>
+        <v>46107.55083096065</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.717514398144</v>
+        <v>46107.55084773148</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>181</v>
@@ -4224,13 +4224,13 @@
         <v>185</v>
       </c>
       <c r="B49" s="8">
-        <v>46065.55618608797</v>
+        <v>46065.3895194213</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.717866886574</v>
+        <v>46107.55120021991</v>
       </c>
       <c r="D49" s="8">
-        <v>46135.58113832176</v>
+        <v>46135.414471655095</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>186</v>
@@ -4275,13 +4275,13 @@
         <v>188</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.55618865741</v>
+        <v>46065.38952199074</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.717601446755</v>
+        <v>46107.5509347801</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.71761978009</v>
+        <v>46107.55095311343</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>189</v>
@@ -4340,13 +4340,13 @@
         <v>193</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.556191145835</v>
+        <v>46065.389524479164</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.71772638889</v>
+        <v>46107.551059722224</v>
       </c>
       <c r="D51" s="8">
-        <v>46135.581011365735</v>
+        <v>46135.41434469908</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>194</v>
@@ -4405,13 +4405,13 @@
         <v>197</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.556183113426</v>
+        <v>46065.389516446754</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.71785043982</v>
+        <v>46107.55118377315</v>
       </c>
       <c r="D52" s="5">
-        <v>46135.581111631946</v>
+        <v>46135.41444496528</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>198</v>
@@ -4468,13 +4468,13 @@
         <v>201</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.55618354167</v>
+        <v>46065.389516875</v>
       </c>
       <c r="C53" s="8">
-        <v>46154.55750765046</v>
+        <v>46154.3908409838</v>
       </c>
       <c r="D53" s="8">
-        <v>46154.55751958334</v>
+        <v>46154.390852916666</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>173</v>
@@ -4521,13 +4521,13 @@
         <v>203</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.556183865745</v>
+        <v>46065.38951719907</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.71901890046</v>
+        <v>46107.5523522338</v>
       </c>
       <c r="D54" s="5">
-        <v>46135.58129253473</v>
+        <v>46135.414625868056</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>204</v>
@@ -4584,13 +4584,13 @@
         <v>206</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.55618417824</v>
+        <v>46065.389517511576</v>
       </c>
       <c r="C55" s="8">
-        <v>46107.7190625</v>
+        <v>46107.552395833336</v>
       </c>
       <c r="D55" s="8">
-        <v>46135.5813152662</v>
+        <v>46135.41464859954</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>207</v>
@@ -4647,13 +4647,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.55618451389</v>
+        <v>46065.38951784722</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.71909642361</v>
+        <v>46107.55242975694</v>
       </c>
       <c r="D56" s="5">
-        <v>46135.581342453705</v>
+        <v>46135.41467578703</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4710,13 +4710,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.55618483796</v>
+        <v>46065.3895181713</v>
       </c>
       <c r="C57" s="8">
-        <v>46154.557489976854</v>
+        <v>46154.39082331018</v>
       </c>
       <c r="D57" s="8">
-        <v>46189.16759806713</v>
+        <v>46189.000931400464</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>57</v>
@@ -4773,13 +4773,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.55618547453</v>
+        <v>46065.389518807875</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.718628449074</v>
+        <v>46107.5519617824</v>
       </c>
       <c r="D58" s="5">
-        <v>46135.581470798614</v>
+        <v>46135.41480413194</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4822,13 +4822,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.556185775466</v>
+        <v>46065.389519108794</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.718062326385</v>
+        <v>46107.55139565972</v>
       </c>
       <c r="D59" s="8">
-        <v>46116.15986453704</v>
+        <v>46115.99319787037</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4887,13 +4887,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.55618608797</v>
+        <v>46065.3895194213</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.71817476852</v>
+        <v>46107.55150810185</v>
       </c>
       <c r="D60" s="5">
-        <v>46135.58246335648</v>
+        <v>46135.41579668982</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4950,13 +4950,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.556182534725</v>
+        <v>46065.38951586805</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.71829421296</v>
+        <v>46107.5516275463</v>
       </c>
       <c r="D61" s="8">
-        <v>46135.58157826389</v>
+        <v>46135.414911597225</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>225</v>
@@ -5013,13 +5013,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.556182939814</v>
+        <v>46065.38951627315</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.718405949076</v>
+        <v>46107.55173928241</v>
       </c>
       <c r="D62" s="5">
-        <v>46135.58157879629</v>
+        <v>46135.41491212963</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5076,13 +5076,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.55618355324</v>
+        <v>46065.38951688657</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.71850153935</v>
+        <v>46107.551834872684</v>
       </c>
       <c r="D63" s="8">
-        <v>46122.17992891204</v>
+        <v>46122.01326224537</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>170</v>
@@ -5139,13 +5139,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.55618385416</v>
+        <v>46065.389517187505</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.718607002316</v>
+        <v>46107.551940335645</v>
       </c>
       <c r="D64" s="5">
-        <v>46135.58272097222</v>
+        <v>46135.416054305555</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5202,13 +5202,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.55618413194</v>
+        <v>46065.38951746528</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.58418903935</v>
+        <v>46197.417522372685</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.584207858796</v>
+        <v>46197.41754119213</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5255,13 +5255,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.55618443287</v>
+        <v>46065.389517766205</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.584170208334</v>
+        <v>46197.41750354167</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.584189560184</v>
+        <v>46197.41752289352</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5318,13 +5318,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.55618472223</v>
+        <v>46065.389518055556</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.498886817135</v>
+        <v>46197.33222015046</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.58418701389</v>
+        <v>46197.417520347226</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5381,13 +5381,13 @@
         <v>250</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.55618501158</v>
+        <v>46065.389518344906</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.58183895833</v>
+        <v>46197.415172291665</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.58185835648</v>
+        <v>46197.41519168981</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>251</v>
@@ -5444,13 +5444,13 @@
         <v>253</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.55618528935</v>
+        <v>46065.38951862269</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.58195770833</v>
+        <v>46197.41529104167</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.58252302083</v>
+        <v>46197.41585635417</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>254</v>
@@ -5507,11 +5507,11 @@
         <v>256</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.55618287037</v>
+        <v>46065.38951620371</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.861133530096</v>
+        <v>46126.694466863424</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>257</v>
@@ -5560,11 +5560,11 @@
         <v>259</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.55618353009</v>
+        <v>46065.389516863426</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.581980393516</v>
+        <v>46197.41531372685</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>260</v>
@@ -5623,11 +5623,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.55618322917</v>
+        <v>46065.3895165625</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.581980787036</v>
+        <v>46197.41531412037</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5686,11 +5686,11 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46086.62191810185</v>
+        <v>46086.45525143518</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46126.86113363426</v>
+        <v>46126.694466967594</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5733,11 +5733,11 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46086.62261061343</v>
+        <v>46086.455943946756</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46197.58198023148</v>
+        <v>46197.415313564816</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5796,11 +5796,11 @@
         <v>272</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.54719644676</v>
+        <v>46090.380529780094</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46135.58412155093</v>
+        <v>46135.41745488426</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -1459,13 +1459,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.38951664352</v>
+        <v>46065.55618331018</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.547958055555</v>
+        <v>46092.714624722226</v>
       </c>
       <c r="D4" s="5">
-        <v>46141.61330008102</v>
+        <v>46141.77996674769</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1508,13 +1508,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.38951724537</v>
+        <v>46065.556183912035</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.54792871528</v>
+        <v>46092.71459538194</v>
       </c>
       <c r="D5" s="8">
-        <v>46147.008964189816</v>
+        <v>46147.17563085648</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1571,13 +1571,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.38951759259</v>
+        <v>46065.55618425926</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.547929305554</v>
+        <v>46092.714595972226</v>
       </c>
       <c r="D6" s="5">
-        <v>46147.008964039356</v>
+        <v>46147.17563070601</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1636,13 +1636,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.38951795139</v>
+        <v>46065.55618461806</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54792972222</v>
+        <v>46092.71459638889</v>
       </c>
       <c r="D7" s="8">
-        <v>46147.0089640625</v>
+        <v>46147.175630729165</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1701,13 +1701,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.38951825231</v>
+        <v>46065.55618491898</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.547930138884</v>
+        <v>46092.714596805556</v>
       </c>
       <c r="D8" s="5">
-        <v>46147.008964016204</v>
+        <v>46147.175630682876</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1764,13 +1764,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.38951861111</v>
+        <v>46065.556185277776</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54793074074</v>
+        <v>46092.71459740741</v>
       </c>
       <c r="D9" s="8">
-        <v>46147.008964444445</v>
+        <v>46147.17563111111</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1829,13 +1829,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.38951894676</v>
+        <v>46065.55618561343</v>
       </c>
       <c r="C10" s="5">
-        <v>46154.39088356482</v>
+        <v>46154.55755023148</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.618514305555</v>
+        <v>46196.78518097222</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1880,13 +1880,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.38951925926</v>
+        <v>46065.556185925925</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.30508837963</v>
+        <v>46114.471755046296</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.3051068287</v>
+        <v>46114.471773495374</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1945,13 +1945,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.38951961805</v>
+        <v>46065.556186284724</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.6184946875</v>
+        <v>46196.78516135417</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.61849761574</v>
+        <v>46196.78516428241</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2010,13 +2010,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.38951994213</v>
+        <v>46065.556186608796</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.3467809838</v>
+        <v>46114.51344765046</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.346793668985</v>
+        <v>46114.51346033565</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2063,13 +2063,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.38951606481</v>
+        <v>46065.55618273148</v>
       </c>
       <c r="C14" s="5">
-        <v>46107.54966615741</v>
+        <v>46107.71633282407</v>
       </c>
       <c r="D14" s="5">
-        <v>46107.549685289356</v>
+        <v>46107.71635195602</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2128,13 +2128,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.38951679398</v>
+        <v>46065.55618346065</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.549728645834</v>
+        <v>46107.7163953125</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.54974859954</v>
+        <v>46107.7164152662</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2193,13 +2193,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.38951710648</v>
+        <v>46065.55618377315</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.549819328706</v>
+        <v>46107.71648599537</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.549835011574</v>
+        <v>46107.71650167824</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2258,13 +2258,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.38951743055</v>
+        <v>46065.55618409722</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34676168981</v>
+        <v>46114.513428356484</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.346781898144</v>
+        <v>46114.513448564816</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2323,13 +2323,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.389517766205</v>
+        <v>46065.55618443287</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.346884178245</v>
+        <v>46114.5135508449</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.346898125004</v>
+        <v>46114.51356479166</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2376,13 +2376,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.38951809028</v>
+        <v>46065.55618475695</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.549961875004</v>
+        <v>46107.71662854167</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.549979965275</v>
+        <v>46107.71664663195</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2441,13 +2441,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.3895184375</v>
+        <v>46065.55618510417</v>
       </c>
       <c r="C20" s="5">
-        <v>46107.55000682871</v>
+        <v>46107.71667349537</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.55002149305</v>
+        <v>46107.71668815972</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2506,13 +2506,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.38951879629</v>
+        <v>46065.55618546296</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.34686798611</v>
+        <v>46114.51353465278</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.346884375</v>
+        <v>46114.513551041666</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>
@@ -2571,13 +2571,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.389519131946</v>
+        <v>46065.55618579861</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.55006083334</v>
+        <v>46107.716727499996</v>
       </c>
       <c r="D22" s="5">
-        <v>46107.55007583334</v>
+        <v>46107.7167425</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2636,13 +2636,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.38951710648</v>
+        <v>46065.55618377315</v>
       </c>
       <c r="C23" s="8">
-        <v>46107.55029724537</v>
+        <v>46107.71696391204</v>
       </c>
       <c r="D23" s="8">
-        <v>46107.55031475694</v>
+        <v>46107.71698142361</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2701,13 +2701,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.38951741898</v>
+        <v>46065.55618408565</v>
       </c>
       <c r="C24" s="5">
-        <v>46155.6624807176</v>
+        <v>46155.829147384255</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.66249818287</v>
+        <v>46155.829164849536</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2754,13 +2754,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.38951790509</v>
+        <v>46065.55618457176</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.62113777778</v>
+        <v>46111.787804444444</v>
       </c>
       <c r="D25" s="8">
-        <v>46111.62113914352</v>
+        <v>46111.787805810185</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2819,13 +2819,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.38951821759</v>
+        <v>46065.55618488426</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.62098633102</v>
+        <v>46111.787652997686</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.62098839121</v>
+        <v>46111.787655057866</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2880,13 +2880,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.38951853009</v>
+        <v>46065.55618519676</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.62103630787</v>
+        <v>46111.787702974536</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.621037777775</v>
+        <v>46111.78770444445</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>110</v>
@@ -2941,13 +2941,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.38951887732</v>
+        <v>46065.55618554398</v>
       </c>
       <c r="C28" s="5">
-        <v>46154.39079186342</v>
+        <v>46154.55745853009</v>
       </c>
       <c r="D28" s="5">
-        <v>46189.00093152778</v>
+        <v>46189.16759819444</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3006,13 +3006,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.389519247685</v>
+        <v>46065.55618591435</v>
       </c>
       <c r="C29" s="8">
-        <v>46129.428751875</v>
+        <v>46129.59541854166</v>
       </c>
       <c r="D29" s="8">
-        <v>46129.428753125</v>
+        <v>46129.595419791665</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3067,13 +3067,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.389519652774</v>
+        <v>46065.556186319445</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.39077186343</v>
+        <v>46154.55743853009</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.390773391206</v>
+        <v>46154.55744005787</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3128,13 +3128,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.389519965276</v>
+        <v>46065.55618663195</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.6213315625</v>
+        <v>46111.78799822916</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.62134431713</v>
+        <v>46111.7880109838</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3193,13 +3193,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.389520625</v>
+        <v>46065.556187291666</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.6212590162</v>
+        <v>46111.787925682875</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.62126035879</v>
+        <v>46111.78792702546</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3254,13 +3254,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.38952170139</v>
+        <v>46065.55618836806</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.62131702546</v>
+        <v>46111.787983692135</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.621318668986</v>
+        <v>46111.78798533565</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3315,13 +3315,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46067.69045797454</v>
+        <v>46067.8571246412</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.62158</v>
+        <v>46111.78824666666</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.621604375</v>
+        <v>46111.78827104167</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3380,13 +3380,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46067.69061002315</v>
+        <v>46067.857276689814</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.62149472222</v>
+        <v>46111.78816138889</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.621495949075</v>
+        <v>46111.78816261574</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3435,13 +3435,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46067.69069710648</v>
+        <v>46067.857363773146</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.621563622684</v>
+        <v>46111.788230289356</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.62156525463</v>
+        <v>46111.788231921295</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3490,13 +3490,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46067.69078010417</v>
+        <v>46067.85744677084</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.621536562496</v>
+        <v>46111.78820322917</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.62153788195</v>
+        <v>46111.78820454861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3545,13 +3545,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.38952369213</v>
+        <v>46065.556190358795</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.621906747685</v>
+        <v>46111.78857341435</v>
       </c>
       <c r="D38" s="5">
-        <v>46135.41441790509</v>
+        <v>46135.581084571764</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3610,13 +3610,13 @@
         <v>147</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.3895240625</v>
+        <v>46065.55619072917</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.622016134264</v>
+        <v>46111.78868280092</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.346894375005</v>
+        <v>46114.51356104166</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>78</v>
@@ -3671,13 +3671,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.389524432874</v>
+        <v>46065.55619109954</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.62209619213</v>
+        <v>46111.78876285879</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.62209752315</v>
+        <v>46111.78876418981</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3732,13 +3732,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.38951626157</v>
+        <v>46065.55618292824</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.630251319446</v>
+        <v>46114.79691798611</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.630264004634</v>
+        <v>46114.79693067129</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3785,13 +3785,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.64314940972</v>
+        <v>46070.80981607639</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59716626158</v>
+        <v>46114.76383292824</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.597182604164</v>
+        <v>46114.763849270836</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3850,13 +3850,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.38951653935</v>
+        <v>46065.55618320602</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.630152858794</v>
+        <v>46114.796819525465</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.63016990741</v>
+        <v>46114.796836574074</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -3915,13 +3915,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46086.459633136576</v>
+        <v>46086.62629980324</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.63019277778</v>
+        <v>46114.79685944444</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.63020814815</v>
+        <v>46114.79687481481</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3978,13 +3978,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="8">
-        <v>46086.45999190972</v>
+        <v>46086.62665857639</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.63022989583</v>
+        <v>46114.796896562504</v>
       </c>
       <c r="D45" s="8">
-        <v>46123.013042708335</v>
+        <v>46123.179709375</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>169</v>
@@ -4041,13 +4041,13 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46065.38951681713</v>
+        <v>46065.5561834838</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.550847199076</v>
+        <v>46107.71751386574</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.55086023148</v>
+        <v>46107.71752689815</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4094,13 +4094,13 @@
         <v>175</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.389517083335</v>
+        <v>46065.55618375</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.55074893519</v>
+        <v>46107.71741560185</v>
       </c>
       <c r="D47" s="8">
-        <v>46135.41438908565</v>
+        <v>46135.581055752315</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>176</v>
@@ -4159,13 +4159,13 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46065.38951743055</v>
+        <v>46065.55618409722</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.55083096065</v>
+        <v>46107.717497627316</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.55084773148</v>
+        <v>46107.717514398144</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>181</v>
@@ -4224,13 +4224,13 @@
         <v>185</v>
       </c>
       <c r="B49" s="8">
-        <v>46065.3895194213</v>
+        <v>46065.55618608797</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.55120021991</v>
+        <v>46107.717866886574</v>
       </c>
       <c r="D49" s="8">
-        <v>46135.414471655095</v>
+        <v>46135.58113832176</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>186</v>
@@ -4275,13 +4275,13 @@
         <v>188</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.38952199074</v>
+        <v>46065.55618865741</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.5509347801</v>
+        <v>46107.717601446755</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.55095311343</v>
+        <v>46107.71761978009</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>189</v>
@@ -4340,13 +4340,13 @@
         <v>193</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.389524479164</v>
+        <v>46065.556191145835</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.551059722224</v>
+        <v>46107.71772638889</v>
       </c>
       <c r="D51" s="8">
-        <v>46135.41434469908</v>
+        <v>46135.581011365735</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>194</v>
@@ -4405,13 +4405,13 @@
         <v>197</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.389516446754</v>
+        <v>46065.556183113426</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.55118377315</v>
+        <v>46107.71785043982</v>
       </c>
       <c r="D52" s="5">
-        <v>46135.41444496528</v>
+        <v>46135.581111631946</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>198</v>
@@ -4468,13 +4468,13 @@
         <v>201</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.389516875</v>
+        <v>46065.55618354167</v>
       </c>
       <c r="C53" s="8">
-        <v>46154.3908409838</v>
+        <v>46154.55750765046</v>
       </c>
       <c r="D53" s="8">
-        <v>46154.390852916666</v>
+        <v>46154.55751958334</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>173</v>
@@ -4521,13 +4521,13 @@
         <v>203</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.38951719907</v>
+        <v>46065.556183865745</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.5523522338</v>
+        <v>46107.71901890046</v>
       </c>
       <c r="D54" s="5">
-        <v>46135.414625868056</v>
+        <v>46135.58129253473</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>204</v>
@@ -4584,13 +4584,13 @@
         <v>206</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.389517511576</v>
+        <v>46065.55618417824</v>
       </c>
       <c r="C55" s="8">
-        <v>46107.552395833336</v>
+        <v>46107.7190625</v>
       </c>
       <c r="D55" s="8">
-        <v>46135.41464859954</v>
+        <v>46135.5813152662</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>207</v>
@@ -4647,13 +4647,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.38951784722</v>
+        <v>46065.55618451389</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.55242975694</v>
+        <v>46107.71909642361</v>
       </c>
       <c r="D56" s="5">
-        <v>46135.41467578703</v>
+        <v>46135.581342453705</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4710,13 +4710,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.3895181713</v>
+        <v>46065.55618483796</v>
       </c>
       <c r="C57" s="8">
-        <v>46154.39082331018</v>
+        <v>46154.557489976854</v>
       </c>
       <c r="D57" s="8">
-        <v>46189.000931400464</v>
+        <v>46189.16759806713</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>57</v>
@@ -4773,13 +4773,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.389518807875</v>
+        <v>46065.55618547453</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.5519617824</v>
+        <v>46107.718628449074</v>
       </c>
       <c r="D58" s="5">
-        <v>46135.41480413194</v>
+        <v>46135.581470798614</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4822,13 +4822,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.389519108794</v>
+        <v>46065.556185775466</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.55139565972</v>
+        <v>46107.718062326385</v>
       </c>
       <c r="D59" s="8">
-        <v>46115.99319787037</v>
+        <v>46116.15986453704</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4887,13 +4887,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.3895194213</v>
+        <v>46065.55618608797</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.55150810185</v>
+        <v>46107.71817476852</v>
       </c>
       <c r="D60" s="5">
-        <v>46135.41579668982</v>
+        <v>46135.58246335648</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4950,13 +4950,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.38951586805</v>
+        <v>46065.556182534725</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.5516275463</v>
+        <v>46107.71829421296</v>
       </c>
       <c r="D61" s="8">
-        <v>46135.414911597225</v>
+        <v>46135.58157826389</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>225</v>
@@ -5013,13 +5013,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.38951627315</v>
+        <v>46065.556182939814</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.55173928241</v>
+        <v>46107.718405949076</v>
       </c>
       <c r="D62" s="5">
-        <v>46135.41491212963</v>
+        <v>46135.58157879629</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5076,13 +5076,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.38951688657</v>
+        <v>46065.55618355324</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.551834872684</v>
+        <v>46107.71850153935</v>
       </c>
       <c r="D63" s="8">
-        <v>46122.01326224537</v>
+        <v>46122.17992891204</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>170</v>
@@ -5139,13 +5139,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.389517187505</v>
+        <v>46065.55618385416</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.551940335645</v>
+        <v>46107.718607002316</v>
       </c>
       <c r="D64" s="5">
-        <v>46135.416054305555</v>
+        <v>46135.58272097222</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5202,13 +5202,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.38951746528</v>
+        <v>46065.55618413194</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.417522372685</v>
+        <v>46197.58418903935</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.41754119213</v>
+        <v>46197.584207858796</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5255,13 +5255,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.389517766205</v>
+        <v>46065.55618443287</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.41750354167</v>
+        <v>46197.584170208334</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.41752289352</v>
+        <v>46197.584189560184</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5318,13 +5318,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.389518055556</v>
+        <v>46065.55618472223</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.33222015046</v>
+        <v>46197.498886817135</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.417520347226</v>
+        <v>46197.58418701389</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5381,13 +5381,13 @@
         <v>250</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.389518344906</v>
+        <v>46065.55618501158</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.415172291665</v>
+        <v>46197.58183895833</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.41519168981</v>
+        <v>46197.58185835648</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>251</v>
@@ -5444,13 +5444,13 @@
         <v>253</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.38951862269</v>
+        <v>46065.55618528935</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.41529104167</v>
+        <v>46197.58195770833</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.41585635417</v>
+        <v>46197.58252302083</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>254</v>
@@ -5507,11 +5507,11 @@
         <v>256</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.38951620371</v>
+        <v>46065.55618287037</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.694466863424</v>
+        <v>46126.861133530096</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>257</v>
@@ -5560,11 +5560,11 @@
         <v>259</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.389516863426</v>
+        <v>46065.55618353009</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.41531372685</v>
+        <v>46197.581980393516</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>260</v>
@@ -5623,11 +5623,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.3895165625</v>
+        <v>46065.55618322917</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.41531412037</v>
+        <v>46197.581980787036</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5686,11 +5686,11 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46086.45525143518</v>
+        <v>46086.62191810185</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46126.694466967594</v>
+        <v>46126.86113363426</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5733,11 +5733,11 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46086.455943946756</v>
+        <v>46086.62261061343</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46197.415313564816</v>
+        <v>46197.58198023148</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5796,11 +5796,11 @@
         <v>272</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.380529780094</v>
+        <v>46090.54719644676</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46135.41745488426</v>
+        <v>46135.58412155093</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="274">
   <si>
     <t>50001515 - CLIENTE POR DEFINIR</t>
   </si>
@@ -5688,9 +5688,11 @@
       <c r="B73" s="8">
         <v>46086.62191810185</v>
       </c>
-      <c r="C73" s="9"/>
+      <c r="C73" s="8">
+        <v>46198.633247314814</v>
+      </c>
       <c r="D73" s="8">
-        <v>46126.86113363426</v>
+        <v>46198.63326113426</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5724,9 +5726,13 @@
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
-      <c r="S73" s="9"/>
+      <c r="S73" s="9">
+        <v>1</v>
+      </c>
       <c r="T73" s="9"/>
-      <c r="U73" s="9"/>
+      <c r="U73" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
@@ -5735,9 +5741,11 @@
       <c r="B74" s="5">
         <v>46086.62261061343</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46198.633180185185</v>
+      </c>
       <c r="D74" s="5">
-        <v>46197.58198023148</v>
+        <v>46198.63339207176</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5782,13 +5790,13 @@
         <v>46206</v>
       </c>
       <c r="S74" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="U74" s="12" t="s">
-        <v>47</v>
+      <c r="U74" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5798,9 +5806,11 @@
       <c r="B75" s="8">
         <v>46090.54719644676</v>
       </c>
-      <c r="C75" s="9"/>
+      <c r="C75" s="8">
+        <v>46198.63323150463</v>
+      </c>
       <c r="D75" s="8">
-        <v>46135.58412155093</v>
+        <v>46198.63332905092</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>
@@ -5845,13 +5855,13 @@
         <v>46218</v>
       </c>
       <c r="S75" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="U75" s="10" t="s">
-        <v>108</v>
+      <c r="U75" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -1459,13 +1459,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.55618331018</v>
+        <v>46065.38951664352</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.714624722226</v>
+        <v>46092.547958055555</v>
       </c>
       <c r="D4" s="5">
-        <v>46141.77996674769</v>
+        <v>46141.61330008102</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1508,13 +1508,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.556183912035</v>
+        <v>46065.38951724537</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.71459538194</v>
+        <v>46092.54792871528</v>
       </c>
       <c r="D5" s="8">
-        <v>46147.17563085648</v>
+        <v>46147.008964189816</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1571,13 +1571,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.55618425926</v>
+        <v>46065.38951759259</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.714595972226</v>
+        <v>46092.547929305554</v>
       </c>
       <c r="D6" s="5">
-        <v>46147.17563070601</v>
+        <v>46147.008964039356</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1636,13 +1636,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.55618461806</v>
+        <v>46065.38951795139</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71459638889</v>
+        <v>46092.54792972222</v>
       </c>
       <c r="D7" s="8">
-        <v>46147.175630729165</v>
+        <v>46147.0089640625</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1701,13 +1701,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.55618491898</v>
+        <v>46065.38951825231</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.714596805556</v>
+        <v>46092.547930138884</v>
       </c>
       <c r="D8" s="5">
-        <v>46147.175630682876</v>
+        <v>46147.008964016204</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1764,13 +1764,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.556185277776</v>
+        <v>46065.38951861111</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71459740741</v>
+        <v>46092.54793074074</v>
       </c>
       <c r="D9" s="8">
-        <v>46147.17563111111</v>
+        <v>46147.008964444445</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1829,13 +1829,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.55618561343</v>
+        <v>46065.38951894676</v>
       </c>
       <c r="C10" s="5">
-        <v>46154.55755023148</v>
+        <v>46154.39088356482</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.78518097222</v>
+        <v>46196.618514305555</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1880,13 +1880,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.556185925925</v>
+        <v>46065.38951925926</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.471755046296</v>
+        <v>46114.30508837963</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.471773495374</v>
+        <v>46114.3051068287</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1945,13 +1945,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.556186284724</v>
+        <v>46065.38951961805</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.78516135417</v>
+        <v>46196.6184946875</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.78516428241</v>
+        <v>46196.61849761574</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2010,13 +2010,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.556186608796</v>
+        <v>46065.38951994213</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51344765046</v>
+        <v>46114.3467809838</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.51346033565</v>
+        <v>46114.346793668985</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2063,13 +2063,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.55618273148</v>
+        <v>46065.38951606481</v>
       </c>
       <c r="C14" s="5">
-        <v>46107.71633282407</v>
+        <v>46107.54966615741</v>
       </c>
       <c r="D14" s="5">
-        <v>46107.71635195602</v>
+        <v>46107.549685289356</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2128,13 +2128,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.55618346065</v>
+        <v>46065.38951679398</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.7163953125</v>
+        <v>46107.549728645834</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.7164152662</v>
+        <v>46107.54974859954</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2193,13 +2193,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.55618377315</v>
+        <v>46065.38951710648</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.71648599537</v>
+        <v>46107.549819328706</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.71650167824</v>
+        <v>46107.549835011574</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2258,13 +2258,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.55618409722</v>
+        <v>46065.38951743055</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.513428356484</v>
+        <v>46114.34676168981</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.513448564816</v>
+        <v>46114.346781898144</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2323,13 +2323,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.55618443287</v>
+        <v>46065.389517766205</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.5135508449</v>
+        <v>46114.346884178245</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.51356479166</v>
+        <v>46114.346898125004</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2376,13 +2376,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.55618475695</v>
+        <v>46065.38951809028</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.71662854167</v>
+        <v>46107.549961875004</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.71664663195</v>
+        <v>46107.549979965275</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2441,13 +2441,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.55618510417</v>
+        <v>46065.3895184375</v>
       </c>
       <c r="C20" s="5">
-        <v>46107.71667349537</v>
+        <v>46107.55000682871</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.71668815972</v>
+        <v>46107.55002149305</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2506,13 +2506,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.55618546296</v>
+        <v>46065.38951879629</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.51353465278</v>
+        <v>46114.34686798611</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.513551041666</v>
+        <v>46114.346884375</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>
@@ -2571,13 +2571,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.55618579861</v>
+        <v>46065.389519131946</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.716727499996</v>
+        <v>46107.55006083334</v>
       </c>
       <c r="D22" s="5">
-        <v>46107.7167425</v>
+        <v>46107.55007583334</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2636,13 +2636,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.55618377315</v>
+        <v>46065.38951710648</v>
       </c>
       <c r="C23" s="8">
-        <v>46107.71696391204</v>
+        <v>46107.55029724537</v>
       </c>
       <c r="D23" s="8">
-        <v>46107.71698142361</v>
+        <v>46107.55031475694</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2701,13 +2701,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.55618408565</v>
+        <v>46065.38951741898</v>
       </c>
       <c r="C24" s="5">
-        <v>46155.829147384255</v>
+        <v>46155.6624807176</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.829164849536</v>
+        <v>46155.66249818287</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2754,13 +2754,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.55618457176</v>
+        <v>46065.38951790509</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.787804444444</v>
+        <v>46111.62113777778</v>
       </c>
       <c r="D25" s="8">
-        <v>46111.787805810185</v>
+        <v>46111.62113914352</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2819,13 +2819,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.55618488426</v>
+        <v>46065.38951821759</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.787652997686</v>
+        <v>46111.62098633102</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.787655057866</v>
+        <v>46111.62098839121</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2880,13 +2880,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.55618519676</v>
+        <v>46065.38951853009</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.787702974536</v>
+        <v>46111.62103630787</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.78770444445</v>
+        <v>46111.621037777775</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>110</v>
@@ -2941,13 +2941,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.55618554398</v>
+        <v>46065.38951887732</v>
       </c>
       <c r="C28" s="5">
-        <v>46154.55745853009</v>
+        <v>46154.39079186342</v>
       </c>
       <c r="D28" s="5">
-        <v>46189.16759819444</v>
+        <v>46189.00093152778</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3006,13 +3006,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.55618591435</v>
+        <v>46065.389519247685</v>
       </c>
       <c r="C29" s="8">
-        <v>46129.59541854166</v>
+        <v>46129.428751875</v>
       </c>
       <c r="D29" s="8">
-        <v>46129.595419791665</v>
+        <v>46129.428753125</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3067,13 +3067,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.556186319445</v>
+        <v>46065.389519652774</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.55743853009</v>
+        <v>46154.39077186343</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.55744005787</v>
+        <v>46154.390773391206</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3128,13 +3128,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.55618663195</v>
+        <v>46065.389519965276</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.78799822916</v>
+        <v>46111.6213315625</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.7880109838</v>
+        <v>46111.62134431713</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3193,13 +3193,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.556187291666</v>
+        <v>46065.389520625</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.787925682875</v>
+        <v>46111.6212590162</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.78792702546</v>
+        <v>46111.62126035879</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3254,13 +3254,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.55618836806</v>
+        <v>46065.38952170139</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.787983692135</v>
+        <v>46111.62131702546</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.78798533565</v>
+        <v>46111.621318668986</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3315,13 +3315,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46067.8571246412</v>
+        <v>46067.69045797454</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.78824666666</v>
+        <v>46111.62158</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.78827104167</v>
+        <v>46111.621604375</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3380,13 +3380,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46067.857276689814</v>
+        <v>46067.69061002315</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.78816138889</v>
+        <v>46111.62149472222</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.78816261574</v>
+        <v>46111.621495949075</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3435,13 +3435,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46067.857363773146</v>
+        <v>46067.69069710648</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.788230289356</v>
+        <v>46111.621563622684</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.788231921295</v>
+        <v>46111.62156525463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3490,13 +3490,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46067.85744677084</v>
+        <v>46067.69078010417</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.78820322917</v>
+        <v>46111.621536562496</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.78820454861</v>
+        <v>46111.62153788195</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3545,13 +3545,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.556190358795</v>
+        <v>46065.38952369213</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.78857341435</v>
+        <v>46111.621906747685</v>
       </c>
       <c r="D38" s="5">
-        <v>46135.581084571764</v>
+        <v>46135.41441790509</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3610,13 +3610,13 @@
         <v>147</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.55619072917</v>
+        <v>46065.3895240625</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.78868280092</v>
+        <v>46111.622016134264</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.51356104166</v>
+        <v>46114.346894375005</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>78</v>
@@ -3671,13 +3671,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.55619109954</v>
+        <v>46065.389524432874</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.78876285879</v>
+        <v>46111.62209619213</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.78876418981</v>
+        <v>46111.62209752315</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3732,13 +3732,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.55618292824</v>
+        <v>46065.38951626157</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.79691798611</v>
+        <v>46114.630251319446</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.79693067129</v>
+        <v>46114.630264004634</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3785,13 +3785,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.80981607639</v>
+        <v>46070.64314940972</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.76383292824</v>
+        <v>46114.59716626158</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.763849270836</v>
+        <v>46114.597182604164</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3850,13 +3850,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.55618320602</v>
+        <v>46065.38951653935</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.796819525465</v>
+        <v>46114.630152858794</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.796836574074</v>
+        <v>46114.63016990741</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -3915,13 +3915,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46086.62629980324</v>
+        <v>46086.459633136576</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.79685944444</v>
+        <v>46114.63019277778</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.79687481481</v>
+        <v>46114.63020814815</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3978,13 +3978,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="8">
-        <v>46086.62665857639</v>
+        <v>46086.45999190972</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.796896562504</v>
+        <v>46114.63022989583</v>
       </c>
       <c r="D45" s="8">
-        <v>46123.179709375</v>
+        <v>46123.013042708335</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>169</v>
@@ -4041,13 +4041,13 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46065.5561834838</v>
+        <v>46065.38951681713</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.71751386574</v>
+        <v>46107.550847199076</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.71752689815</v>
+        <v>46107.55086023148</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4094,13 +4094,13 @@
         <v>175</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.55618375</v>
+        <v>46065.389517083335</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.71741560185</v>
+        <v>46107.55074893519</v>
       </c>
       <c r="D47" s="8">
-        <v>46135.581055752315</v>
+        <v>46135.41438908565</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>176</v>
@@ -4159,13 +4159,13 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46065.55618409722</v>
+        <v>46065.38951743055</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.717497627316</v>
+        <v>46107.55083096065</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.717514398144</v>
+        <v>46107.55084773148</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>181</v>
@@ -4224,13 +4224,13 @@
         <v>185</v>
       </c>
       <c r="B49" s="8">
-        <v>46065.55618608797</v>
+        <v>46065.3895194213</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.717866886574</v>
+        <v>46107.55120021991</v>
       </c>
       <c r="D49" s="8">
-        <v>46135.58113832176</v>
+        <v>46135.414471655095</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>186</v>
@@ -4275,13 +4275,13 @@
         <v>188</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.55618865741</v>
+        <v>46065.38952199074</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.717601446755</v>
+        <v>46107.5509347801</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.71761978009</v>
+        <v>46107.55095311343</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>189</v>
@@ -4340,13 +4340,13 @@
         <v>193</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.556191145835</v>
+        <v>46065.389524479164</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.71772638889</v>
+        <v>46107.551059722224</v>
       </c>
       <c r="D51" s="8">
-        <v>46135.581011365735</v>
+        <v>46135.41434469908</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>194</v>
@@ -4405,13 +4405,13 @@
         <v>197</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.556183113426</v>
+        <v>46065.389516446754</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.71785043982</v>
+        <v>46107.55118377315</v>
       </c>
       <c r="D52" s="5">
-        <v>46135.581111631946</v>
+        <v>46135.41444496528</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>198</v>
@@ -4468,13 +4468,13 @@
         <v>201</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.55618354167</v>
+        <v>46065.389516875</v>
       </c>
       <c r="C53" s="8">
-        <v>46154.55750765046</v>
+        <v>46154.3908409838</v>
       </c>
       <c r="D53" s="8">
-        <v>46154.55751958334</v>
+        <v>46154.390852916666</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>173</v>
@@ -4521,13 +4521,13 @@
         <v>203</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.556183865745</v>
+        <v>46065.38951719907</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.71901890046</v>
+        <v>46107.5523522338</v>
       </c>
       <c r="D54" s="5">
-        <v>46135.58129253473</v>
+        <v>46135.414625868056</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>204</v>
@@ -4584,13 +4584,13 @@
         <v>206</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.55618417824</v>
+        <v>46065.389517511576</v>
       </c>
       <c r="C55" s="8">
-        <v>46107.7190625</v>
+        <v>46107.552395833336</v>
       </c>
       <c r="D55" s="8">
-        <v>46135.5813152662</v>
+        <v>46135.41464859954</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>207</v>
@@ -4647,13 +4647,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.55618451389</v>
+        <v>46065.38951784722</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.71909642361</v>
+        <v>46107.55242975694</v>
       </c>
       <c r="D56" s="5">
-        <v>46135.581342453705</v>
+        <v>46135.41467578703</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4710,13 +4710,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.55618483796</v>
+        <v>46065.3895181713</v>
       </c>
       <c r="C57" s="8">
-        <v>46154.557489976854</v>
+        <v>46154.39082331018</v>
       </c>
       <c r="D57" s="8">
-        <v>46189.16759806713</v>
+        <v>46189.000931400464</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>57</v>
@@ -4773,13 +4773,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.55618547453</v>
+        <v>46065.389518807875</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.718628449074</v>
+        <v>46107.5519617824</v>
       </c>
       <c r="D58" s="5">
-        <v>46135.581470798614</v>
+        <v>46135.41480413194</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4822,13 +4822,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.556185775466</v>
+        <v>46065.389519108794</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.718062326385</v>
+        <v>46107.55139565972</v>
       </c>
       <c r="D59" s="8">
-        <v>46116.15986453704</v>
+        <v>46115.99319787037</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4887,13 +4887,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.55618608797</v>
+        <v>46065.3895194213</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.71817476852</v>
+        <v>46107.55150810185</v>
       </c>
       <c r="D60" s="5">
-        <v>46135.58246335648</v>
+        <v>46135.41579668982</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4950,13 +4950,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.556182534725</v>
+        <v>46065.38951586805</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.71829421296</v>
+        <v>46107.5516275463</v>
       </c>
       <c r="D61" s="8">
-        <v>46135.58157826389</v>
+        <v>46135.414911597225</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>225</v>
@@ -5013,13 +5013,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.556182939814</v>
+        <v>46065.38951627315</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.718405949076</v>
+        <v>46107.55173928241</v>
       </c>
       <c r="D62" s="5">
-        <v>46135.58157879629</v>
+        <v>46135.41491212963</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5076,13 +5076,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.55618355324</v>
+        <v>46065.38951688657</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.71850153935</v>
+        <v>46107.551834872684</v>
       </c>
       <c r="D63" s="8">
-        <v>46122.17992891204</v>
+        <v>46122.01326224537</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>170</v>
@@ -5139,13 +5139,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.55618385416</v>
+        <v>46065.389517187505</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.718607002316</v>
+        <v>46107.551940335645</v>
       </c>
       <c r="D64" s="5">
-        <v>46135.58272097222</v>
+        <v>46135.416054305555</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5202,13 +5202,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.55618413194</v>
+        <v>46065.38951746528</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.58418903935</v>
+        <v>46197.417522372685</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.584207858796</v>
+        <v>46197.41754119213</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5255,13 +5255,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.55618443287</v>
+        <v>46065.389517766205</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.584170208334</v>
+        <v>46197.41750354167</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.584189560184</v>
+        <v>46197.41752289352</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5318,13 +5318,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.55618472223</v>
+        <v>46065.389518055556</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.498886817135</v>
+        <v>46197.33222015046</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.58418701389</v>
+        <v>46197.417520347226</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5381,13 +5381,13 @@
         <v>250</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.55618501158</v>
+        <v>46065.389518344906</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.58183895833</v>
+        <v>46197.415172291665</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.58185835648</v>
+        <v>46197.41519168981</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>251</v>
@@ -5444,13 +5444,13 @@
         <v>253</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.55618528935</v>
+        <v>46065.38951862269</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.58195770833</v>
+        <v>46197.41529104167</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.58252302083</v>
+        <v>46197.41585635417</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>254</v>
@@ -5507,11 +5507,11 @@
         <v>256</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.55618287037</v>
+        <v>46065.38951620371</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.861133530096</v>
+        <v>46126.694466863424</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>257</v>
@@ -5560,11 +5560,11 @@
         <v>259</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.55618353009</v>
+        <v>46065.389516863426</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.581980393516</v>
+        <v>46197.41531372685</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>260</v>
@@ -5623,11 +5623,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.55618322917</v>
+        <v>46065.3895165625</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.581980787036</v>
+        <v>46197.41531412037</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5686,13 +5686,13 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46086.62191810185</v>
+        <v>46086.45525143518</v>
       </c>
       <c r="C73" s="8">
-        <v>46198.633247314814</v>
+        <v>46198.46658064815</v>
       </c>
       <c r="D73" s="8">
-        <v>46198.63326113426</v>
+        <v>46198.466594467594</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5739,13 +5739,13 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46086.62261061343</v>
+        <v>46086.455943946756</v>
       </c>
       <c r="C74" s="5">
-        <v>46198.633180185185</v>
+        <v>46198.46651351852</v>
       </c>
       <c r="D74" s="5">
-        <v>46198.63339207176</v>
+        <v>46198.46672540509</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5804,13 +5804,13 @@
         <v>272</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.54719644676</v>
+        <v>46090.380529780094</v>
       </c>
       <c r="C75" s="8">
-        <v>46198.63323150463</v>
+        <v>46198.46656483796</v>
       </c>
       <c r="D75" s="8">
-        <v>46198.63332905092</v>
+        <v>46198.466662384264</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -1459,13 +1459,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.38951664352</v>
+        <v>46065.55618331018</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.547958055555</v>
+        <v>46092.714624722226</v>
       </c>
       <c r="D4" s="5">
-        <v>46141.61330008102</v>
+        <v>46141.77996674769</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1508,13 +1508,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.38951724537</v>
+        <v>46065.556183912035</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.54792871528</v>
+        <v>46092.71459538194</v>
       </c>
       <c r="D5" s="8">
-        <v>46147.008964189816</v>
+        <v>46147.17563085648</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1571,13 +1571,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.38951759259</v>
+        <v>46065.55618425926</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.547929305554</v>
+        <v>46092.714595972226</v>
       </c>
       <c r="D6" s="5">
-        <v>46147.008964039356</v>
+        <v>46147.17563070601</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1636,13 +1636,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.38951795139</v>
+        <v>46065.55618461806</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54792972222</v>
+        <v>46092.71459638889</v>
       </c>
       <c r="D7" s="8">
-        <v>46147.0089640625</v>
+        <v>46147.175630729165</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1701,13 +1701,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.38951825231</v>
+        <v>46065.55618491898</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.547930138884</v>
+        <v>46092.714596805556</v>
       </c>
       <c r="D8" s="5">
-        <v>46147.008964016204</v>
+        <v>46147.175630682876</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1764,13 +1764,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.38951861111</v>
+        <v>46065.556185277776</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54793074074</v>
+        <v>46092.71459740741</v>
       </c>
       <c r="D9" s="8">
-        <v>46147.008964444445</v>
+        <v>46147.17563111111</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1829,13 +1829,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.38951894676</v>
+        <v>46065.55618561343</v>
       </c>
       <c r="C10" s="5">
-        <v>46154.39088356482</v>
+        <v>46154.55755023148</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.618514305555</v>
+        <v>46196.78518097222</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1880,13 +1880,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.38951925926</v>
+        <v>46065.556185925925</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.30508837963</v>
+        <v>46114.471755046296</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.3051068287</v>
+        <v>46114.471773495374</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1945,13 +1945,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.38951961805</v>
+        <v>46065.556186284724</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.6184946875</v>
+        <v>46196.78516135417</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.61849761574</v>
+        <v>46196.78516428241</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2010,13 +2010,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.38951994213</v>
+        <v>46065.556186608796</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.3467809838</v>
+        <v>46114.51344765046</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.346793668985</v>
+        <v>46114.51346033565</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2063,13 +2063,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.38951606481</v>
+        <v>46065.55618273148</v>
       </c>
       <c r="C14" s="5">
-        <v>46107.54966615741</v>
+        <v>46107.71633282407</v>
       </c>
       <c r="D14" s="5">
-        <v>46107.549685289356</v>
+        <v>46107.71635195602</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2128,13 +2128,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.38951679398</v>
+        <v>46065.55618346065</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.549728645834</v>
+        <v>46107.7163953125</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.54974859954</v>
+        <v>46107.7164152662</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2193,13 +2193,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.38951710648</v>
+        <v>46065.55618377315</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.549819328706</v>
+        <v>46107.71648599537</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.549835011574</v>
+        <v>46107.71650167824</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2258,13 +2258,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.38951743055</v>
+        <v>46065.55618409722</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34676168981</v>
+        <v>46114.513428356484</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.346781898144</v>
+        <v>46114.513448564816</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2323,13 +2323,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.389517766205</v>
+        <v>46065.55618443287</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.346884178245</v>
+        <v>46114.5135508449</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.346898125004</v>
+        <v>46114.51356479166</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2376,13 +2376,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.38951809028</v>
+        <v>46065.55618475695</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.549961875004</v>
+        <v>46107.71662854167</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.549979965275</v>
+        <v>46107.71664663195</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2441,13 +2441,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.3895184375</v>
+        <v>46065.55618510417</v>
       </c>
       <c r="C20" s="5">
-        <v>46107.55000682871</v>
+        <v>46107.71667349537</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.55002149305</v>
+        <v>46107.71668815972</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2506,13 +2506,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.38951879629</v>
+        <v>46065.55618546296</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.34686798611</v>
+        <v>46114.51353465278</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.346884375</v>
+        <v>46114.513551041666</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>
@@ -2571,13 +2571,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.389519131946</v>
+        <v>46065.55618579861</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.55006083334</v>
+        <v>46107.716727499996</v>
       </c>
       <c r="D22" s="5">
-        <v>46107.55007583334</v>
+        <v>46107.7167425</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2636,13 +2636,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.38951710648</v>
+        <v>46065.55618377315</v>
       </c>
       <c r="C23" s="8">
-        <v>46107.55029724537</v>
+        <v>46107.71696391204</v>
       </c>
       <c r="D23" s="8">
-        <v>46107.55031475694</v>
+        <v>46107.71698142361</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2701,13 +2701,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.38951741898</v>
+        <v>46065.55618408565</v>
       </c>
       <c r="C24" s="5">
-        <v>46155.6624807176</v>
+        <v>46155.829147384255</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.66249818287</v>
+        <v>46155.829164849536</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2754,13 +2754,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.38951790509</v>
+        <v>46065.55618457176</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.62113777778</v>
+        <v>46111.787804444444</v>
       </c>
       <c r="D25" s="8">
-        <v>46111.62113914352</v>
+        <v>46111.787805810185</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2819,13 +2819,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.38951821759</v>
+        <v>46065.55618488426</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.62098633102</v>
+        <v>46111.787652997686</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.62098839121</v>
+        <v>46111.787655057866</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2880,13 +2880,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.38951853009</v>
+        <v>46065.55618519676</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.62103630787</v>
+        <v>46111.787702974536</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.621037777775</v>
+        <v>46111.78770444445</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>110</v>
@@ -2941,13 +2941,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.38951887732</v>
+        <v>46065.55618554398</v>
       </c>
       <c r="C28" s="5">
-        <v>46154.39079186342</v>
+        <v>46154.55745853009</v>
       </c>
       <c r="D28" s="5">
-        <v>46189.00093152778</v>
+        <v>46189.16759819444</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3006,13 +3006,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.389519247685</v>
+        <v>46065.55618591435</v>
       </c>
       <c r="C29" s="8">
-        <v>46129.428751875</v>
+        <v>46129.59541854166</v>
       </c>
       <c r="D29" s="8">
-        <v>46129.428753125</v>
+        <v>46129.595419791665</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3067,13 +3067,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.389519652774</v>
+        <v>46065.556186319445</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.39077186343</v>
+        <v>46154.55743853009</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.390773391206</v>
+        <v>46154.55744005787</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3128,13 +3128,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.389519965276</v>
+        <v>46065.55618663195</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.6213315625</v>
+        <v>46111.78799822916</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.62134431713</v>
+        <v>46111.7880109838</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3193,13 +3193,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.389520625</v>
+        <v>46065.556187291666</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.6212590162</v>
+        <v>46111.787925682875</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.62126035879</v>
+        <v>46111.78792702546</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3254,13 +3254,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.38952170139</v>
+        <v>46065.55618836806</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.62131702546</v>
+        <v>46111.787983692135</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.621318668986</v>
+        <v>46111.78798533565</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3315,13 +3315,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46067.69045797454</v>
+        <v>46067.8571246412</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.62158</v>
+        <v>46111.78824666666</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.621604375</v>
+        <v>46111.78827104167</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3380,13 +3380,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46067.69061002315</v>
+        <v>46067.857276689814</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.62149472222</v>
+        <v>46111.78816138889</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.621495949075</v>
+        <v>46111.78816261574</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3435,13 +3435,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46067.69069710648</v>
+        <v>46067.857363773146</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.621563622684</v>
+        <v>46111.788230289356</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.62156525463</v>
+        <v>46111.788231921295</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3490,13 +3490,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46067.69078010417</v>
+        <v>46067.85744677084</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.621536562496</v>
+        <v>46111.78820322917</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.62153788195</v>
+        <v>46111.78820454861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3545,13 +3545,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.38952369213</v>
+        <v>46065.556190358795</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.621906747685</v>
+        <v>46111.78857341435</v>
       </c>
       <c r="D38" s="5">
-        <v>46135.41441790509</v>
+        <v>46135.581084571764</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3610,13 +3610,13 @@
         <v>147</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.3895240625</v>
+        <v>46065.55619072917</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.622016134264</v>
+        <v>46111.78868280092</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.346894375005</v>
+        <v>46114.51356104166</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>78</v>
@@ -3671,13 +3671,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.389524432874</v>
+        <v>46065.55619109954</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.62209619213</v>
+        <v>46111.78876285879</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.62209752315</v>
+        <v>46111.78876418981</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3732,13 +3732,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.38951626157</v>
+        <v>46065.55618292824</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.630251319446</v>
+        <v>46114.79691798611</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.630264004634</v>
+        <v>46114.79693067129</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3785,13 +3785,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.64314940972</v>
+        <v>46070.80981607639</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59716626158</v>
+        <v>46114.76383292824</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.597182604164</v>
+        <v>46114.763849270836</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3850,13 +3850,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.38951653935</v>
+        <v>46065.55618320602</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.630152858794</v>
+        <v>46114.796819525465</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.63016990741</v>
+        <v>46114.796836574074</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -3915,13 +3915,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46086.459633136576</v>
+        <v>46086.62629980324</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.63019277778</v>
+        <v>46114.79685944444</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.63020814815</v>
+        <v>46114.79687481481</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3978,13 +3978,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="8">
-        <v>46086.45999190972</v>
+        <v>46086.62665857639</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.63022989583</v>
+        <v>46114.796896562504</v>
       </c>
       <c r="D45" s="8">
-        <v>46123.013042708335</v>
+        <v>46123.179709375</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>169</v>
@@ -4041,13 +4041,13 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46065.38951681713</v>
+        <v>46065.5561834838</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.550847199076</v>
+        <v>46107.71751386574</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.55086023148</v>
+        <v>46107.71752689815</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4094,13 +4094,13 @@
         <v>175</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.389517083335</v>
+        <v>46065.55618375</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.55074893519</v>
+        <v>46107.71741560185</v>
       </c>
       <c r="D47" s="8">
-        <v>46135.41438908565</v>
+        <v>46135.581055752315</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>176</v>
@@ -4159,13 +4159,13 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46065.38951743055</v>
+        <v>46065.55618409722</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.55083096065</v>
+        <v>46107.717497627316</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.55084773148</v>
+        <v>46107.717514398144</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>181</v>
@@ -4224,13 +4224,13 @@
         <v>185</v>
       </c>
       <c r="B49" s="8">
-        <v>46065.3895194213</v>
+        <v>46065.55618608797</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.55120021991</v>
+        <v>46107.717866886574</v>
       </c>
       <c r="D49" s="8">
-        <v>46135.414471655095</v>
+        <v>46135.58113832176</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>186</v>
@@ -4275,13 +4275,13 @@
         <v>188</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.38952199074</v>
+        <v>46065.55618865741</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.5509347801</v>
+        <v>46107.717601446755</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.55095311343</v>
+        <v>46107.71761978009</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>189</v>
@@ -4340,13 +4340,13 @@
         <v>193</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.389524479164</v>
+        <v>46065.556191145835</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.551059722224</v>
+        <v>46107.71772638889</v>
       </c>
       <c r="D51" s="8">
-        <v>46135.41434469908</v>
+        <v>46135.581011365735</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>194</v>
@@ -4405,13 +4405,13 @@
         <v>197</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.389516446754</v>
+        <v>46065.556183113426</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.55118377315</v>
+        <v>46107.71785043982</v>
       </c>
       <c r="D52" s="5">
-        <v>46135.41444496528</v>
+        <v>46135.581111631946</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>198</v>
@@ -4468,13 +4468,13 @@
         <v>201</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.389516875</v>
+        <v>46065.55618354167</v>
       </c>
       <c r="C53" s="8">
-        <v>46154.3908409838</v>
+        <v>46154.55750765046</v>
       </c>
       <c r="D53" s="8">
-        <v>46154.390852916666</v>
+        <v>46154.55751958334</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>173</v>
@@ -4521,13 +4521,13 @@
         <v>203</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.38951719907</v>
+        <v>46065.556183865745</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.5523522338</v>
+        <v>46107.71901890046</v>
       </c>
       <c r="D54" s="5">
-        <v>46135.414625868056</v>
+        <v>46135.58129253473</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>204</v>
@@ -4584,13 +4584,13 @@
         <v>206</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.389517511576</v>
+        <v>46065.55618417824</v>
       </c>
       <c r="C55" s="8">
-        <v>46107.552395833336</v>
+        <v>46107.7190625</v>
       </c>
       <c r="D55" s="8">
-        <v>46135.41464859954</v>
+        <v>46135.5813152662</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>207</v>
@@ -4647,13 +4647,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.38951784722</v>
+        <v>46065.55618451389</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.55242975694</v>
+        <v>46107.71909642361</v>
       </c>
       <c r="D56" s="5">
-        <v>46135.41467578703</v>
+        <v>46135.581342453705</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4710,13 +4710,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.3895181713</v>
+        <v>46065.55618483796</v>
       </c>
       <c r="C57" s="8">
-        <v>46154.39082331018</v>
+        <v>46154.557489976854</v>
       </c>
       <c r="D57" s="8">
-        <v>46189.000931400464</v>
+        <v>46189.16759806713</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>57</v>
@@ -4773,13 +4773,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.389518807875</v>
+        <v>46065.55618547453</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.5519617824</v>
+        <v>46107.718628449074</v>
       </c>
       <c r="D58" s="5">
-        <v>46135.41480413194</v>
+        <v>46135.581470798614</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4822,13 +4822,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.389519108794</v>
+        <v>46065.556185775466</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.55139565972</v>
+        <v>46107.718062326385</v>
       </c>
       <c r="D59" s="8">
-        <v>46115.99319787037</v>
+        <v>46116.15986453704</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4887,13 +4887,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.3895194213</v>
+        <v>46065.55618608797</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.55150810185</v>
+        <v>46107.71817476852</v>
       </c>
       <c r="D60" s="5">
-        <v>46135.41579668982</v>
+        <v>46135.58246335648</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4950,13 +4950,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.38951586805</v>
+        <v>46065.556182534725</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.5516275463</v>
+        <v>46107.71829421296</v>
       </c>
       <c r="D61" s="8">
-        <v>46135.414911597225</v>
+        <v>46135.58157826389</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>225</v>
@@ -5013,13 +5013,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.38951627315</v>
+        <v>46065.556182939814</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.55173928241</v>
+        <v>46107.718405949076</v>
       </c>
       <c r="D62" s="5">
-        <v>46135.41491212963</v>
+        <v>46135.58157879629</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5076,13 +5076,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.38951688657</v>
+        <v>46065.55618355324</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.551834872684</v>
+        <v>46107.71850153935</v>
       </c>
       <c r="D63" s="8">
-        <v>46122.01326224537</v>
+        <v>46122.17992891204</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>170</v>
@@ -5139,13 +5139,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.389517187505</v>
+        <v>46065.55618385416</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.551940335645</v>
+        <v>46107.718607002316</v>
       </c>
       <c r="D64" s="5">
-        <v>46135.416054305555</v>
+        <v>46135.58272097222</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5202,13 +5202,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.38951746528</v>
+        <v>46065.55618413194</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.417522372685</v>
+        <v>46197.58418903935</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.41754119213</v>
+        <v>46197.584207858796</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5255,13 +5255,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.389517766205</v>
+        <v>46065.55618443287</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.41750354167</v>
+        <v>46197.584170208334</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.41752289352</v>
+        <v>46197.584189560184</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5318,13 +5318,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.389518055556</v>
+        <v>46065.55618472223</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.33222015046</v>
+        <v>46197.498886817135</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.417520347226</v>
+        <v>46197.58418701389</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5381,13 +5381,13 @@
         <v>250</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.389518344906</v>
+        <v>46065.55618501158</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.415172291665</v>
+        <v>46197.58183895833</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.41519168981</v>
+        <v>46197.58185835648</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>251</v>
@@ -5444,13 +5444,13 @@
         <v>253</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.38951862269</v>
+        <v>46065.55618528935</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.41529104167</v>
+        <v>46197.58195770833</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.41585635417</v>
+        <v>46197.58252302083</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>254</v>
@@ -5507,11 +5507,11 @@
         <v>256</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.38951620371</v>
+        <v>46065.55618287037</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.694466863424</v>
+        <v>46126.861133530096</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>257</v>
@@ -5560,11 +5560,11 @@
         <v>259</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.389516863426</v>
+        <v>46065.55618353009</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.41531372685</v>
+        <v>46197.581980393516</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>260</v>
@@ -5623,11 +5623,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.3895165625</v>
+        <v>46065.55618322917</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.41531412037</v>
+        <v>46197.581980787036</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5686,13 +5686,13 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46086.45525143518</v>
+        <v>46086.62191810185</v>
       </c>
       <c r="C73" s="8">
-        <v>46198.46658064815</v>
+        <v>46198.633247314814</v>
       </c>
       <c r="D73" s="8">
-        <v>46198.466594467594</v>
+        <v>46198.63326113426</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5739,13 +5739,13 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46086.455943946756</v>
+        <v>46086.62261061343</v>
       </c>
       <c r="C74" s="5">
-        <v>46198.46651351852</v>
+        <v>46198.633180185185</v>
       </c>
       <c r="D74" s="5">
-        <v>46198.46672540509</v>
+        <v>46198.63339207176</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5804,13 +5804,13 @@
         <v>272</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.380529780094</v>
+        <v>46090.54719644676</v>
       </c>
       <c r="C75" s="8">
-        <v>46198.46656483796</v>
+        <v>46198.63323150463</v>
       </c>
       <c r="D75" s="8">
-        <v>46198.466662384264</v>
+        <v>46198.63332905092</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -760,16 +760,16 @@
     <t>Logistica:,PACKING LIST</t>
   </si>
   <si>
+    <t>1213242667616396</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
+    <t>Despacho,Logistica:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213242667616396</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
-  </si>
-  <si>
-    <t>Despacho,Logistica:</t>
   </si>
   <si>
     <t>1213242667616397</t>
@@ -5324,7 +5324,7 @@
         <v>46197.498886817135</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.58418701389</v>
+        <v>46199.177003923614</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5369,8 +5369,8 @@
       <c r="S67" s="9">
         <v>1</v>
       </c>
-      <c r="T67" s="12" t="s">
-        <v>249</v>
+      <c r="T67" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U67" s="12" t="s">
         <v>47</v>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B68" s="5">
         <v>46065.55618501158</v>
@@ -5390,7 +5390,7 @@
         <v>46197.58185835648</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5421,7 +5421,7 @@
         <v>246</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q68" s="5">
         <v>46202</v>
@@ -5433,7 +5433,7 @@
         <v>1</v>
       </c>
       <c r="T68" s="12" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="U68" s="11" t="s">
         <v>32</v>
@@ -5481,7 +5481,7 @@
         <v>237</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>255</v>
@@ -5496,7 +5496,7 @@
         <v>1</v>
       </c>
       <c r="T69" s="12" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="U69" s="11" t="s">
         <v>32</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -769,16 +769,16 @@
     <t>Despacho,Logistica:</t>
   </si>
   <si>
+    <t>1213242667616397</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Logistica:,Gestion,Costos,Instalación de componentes</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213242667616397</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Logistica:,Gestion,Costos,Instalación de componentes</t>
   </si>
   <si>
     <t>1213242667616398</t>
@@ -5387,7 +5387,7 @@
         <v>46197.58183895833</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.58185835648</v>
+        <v>46203.17214591435</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>250</v>
@@ -5432,8 +5432,8 @@
       <c r="S68" s="6">
         <v>1</v>
       </c>
-      <c r="T68" s="12" t="s">
-        <v>252</v>
+      <c r="T68" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U68" s="11" t="s">
         <v>32</v>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B69" s="8">
         <v>46065.55618528935</v>
@@ -5453,7 +5453,7 @@
         <v>46197.58252302083</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5484,7 +5484,7 @@
         <v>250</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q69" s="8">
         <v>46203</v>
@@ -5496,7 +5496,7 @@
         <v>1</v>
       </c>
       <c r="T69" s="12" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="U69" s="11" t="s">
         <v>32</v>
@@ -5597,7 +5597,7 @@
         <v>257</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>257</v>
@@ -5778,7 +5778,7 @@
         <v>267</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>271</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="273">
   <si>
     <t>50001515 - CLIENTE POR DEFINIR</t>
   </si>
@@ -776,9 +776,6 @@
   </si>
   <si>
     <t>Logistica:,Gestion,Costos,Instalación de componentes</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213242667616398</t>
@@ -5450,7 +5447,7 @@
         <v>46197.58195770833</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.58252302083</v>
+        <v>46204.17730309028</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>253</v>
@@ -5495,8 +5492,8 @@
       <c r="S69" s="9">
         <v>1</v>
       </c>
-      <c r="T69" s="12" t="s">
-        <v>255</v>
+      <c r="T69" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U69" s="11" t="s">
         <v>32</v>
@@ -5504,7 +5501,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B70" s="5">
         <v>46065.55618287037</v>
@@ -5514,7 +5511,7 @@
         <v>46126.861133530096</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5538,7 +5535,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5557,7 +5554,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B71" s="8">
         <v>46065.55618353009</v>
@@ -5567,16 +5564,16 @@
         <v>46197.581980393516</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
+      <c r="H71" s="9" t="s">
         <v>261</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>262</v>
       </c>
       <c r="I71" s="8">
         <v>46206</v>
@@ -5594,13 +5591,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>253</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q71" s="8">
         <v>46217</v>
@@ -5620,7 +5617,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B72" s="5">
         <v>46065.55618322917</v>
@@ -5630,16 +5627,16 @@
         <v>46197.581980787036</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>262</v>
       </c>
       <c r="I72" s="5">
         <v>46206</v>
@@ -5657,13 +5654,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q72" s="5">
         <v>46217</v>
@@ -5683,7 +5680,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B73" s="8">
         <v>46086.62191810185</v>
@@ -5695,7 +5692,7 @@
         <v>46198.63326113426</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5719,7 +5716,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5736,7 +5733,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B74" s="5">
         <v>46086.62261061343</v>
@@ -5748,7 +5745,7 @@
         <v>46198.63339207176</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5775,13 +5772,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>253</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q74" s="5">
         <v>46217</v>
@@ -5801,7 +5798,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B75" s="8">
         <v>46090.54719644676</v>
@@ -5813,7 +5810,7 @@
         <v>46198.63332905092</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5840,13 +5837,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q75" s="8">
         <v>46226</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -1456,13 +1456,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.55618331018</v>
+        <v>46065.38951664352</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.714624722226</v>
+        <v>46092.547958055555</v>
       </c>
       <c r="D4" s="5">
-        <v>46141.77996674769</v>
+        <v>46141.61330008102</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1505,13 +1505,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.556183912035</v>
+        <v>46065.38951724537</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.71459538194</v>
+        <v>46092.54792871528</v>
       </c>
       <c r="D5" s="8">
-        <v>46147.17563085648</v>
+        <v>46147.008964189816</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1568,13 +1568,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.55618425926</v>
+        <v>46065.38951759259</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.714595972226</v>
+        <v>46092.547929305554</v>
       </c>
       <c r="D6" s="5">
-        <v>46147.17563070601</v>
+        <v>46147.008964039356</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1633,13 +1633,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.55618461806</v>
+        <v>46065.38951795139</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71459638889</v>
+        <v>46092.54792972222</v>
       </c>
       <c r="D7" s="8">
-        <v>46147.175630729165</v>
+        <v>46147.0089640625</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1698,13 +1698,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.55618491898</v>
+        <v>46065.38951825231</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.714596805556</v>
+        <v>46092.547930138884</v>
       </c>
       <c r="D8" s="5">
-        <v>46147.175630682876</v>
+        <v>46147.008964016204</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1761,13 +1761,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.556185277776</v>
+        <v>46065.38951861111</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71459740741</v>
+        <v>46092.54793074074</v>
       </c>
       <c r="D9" s="8">
-        <v>46147.17563111111</v>
+        <v>46147.008964444445</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1826,13 +1826,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.55618561343</v>
+        <v>46065.38951894676</v>
       </c>
       <c r="C10" s="5">
-        <v>46154.55755023148</v>
+        <v>46154.39088356482</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.78518097222</v>
+        <v>46196.618514305555</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1877,13 +1877,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.556185925925</v>
+        <v>46065.38951925926</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.471755046296</v>
+        <v>46114.30508837963</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.471773495374</v>
+        <v>46114.3051068287</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1942,13 +1942,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.556186284724</v>
+        <v>46065.38951961805</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.78516135417</v>
+        <v>46196.6184946875</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.78516428241</v>
+        <v>46196.61849761574</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2007,13 +2007,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.556186608796</v>
+        <v>46065.38951994213</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51344765046</v>
+        <v>46114.3467809838</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.51346033565</v>
+        <v>46114.346793668985</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2060,13 +2060,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.55618273148</v>
+        <v>46065.38951606481</v>
       </c>
       <c r="C14" s="5">
-        <v>46107.71633282407</v>
+        <v>46107.54966615741</v>
       </c>
       <c r="D14" s="5">
-        <v>46107.71635195602</v>
+        <v>46107.549685289356</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2125,13 +2125,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.55618346065</v>
+        <v>46065.38951679398</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.7163953125</v>
+        <v>46107.549728645834</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.7164152662</v>
+        <v>46107.54974859954</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2190,13 +2190,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.55618377315</v>
+        <v>46065.38951710648</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.71648599537</v>
+        <v>46107.549819328706</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.71650167824</v>
+        <v>46107.549835011574</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2255,13 +2255,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.55618409722</v>
+        <v>46065.38951743055</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.513428356484</v>
+        <v>46114.34676168981</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.513448564816</v>
+        <v>46114.346781898144</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2320,13 +2320,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.55618443287</v>
+        <v>46065.389517766205</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.5135508449</v>
+        <v>46114.346884178245</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.51356479166</v>
+        <v>46114.346898125004</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2373,13 +2373,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.55618475695</v>
+        <v>46065.38951809028</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.71662854167</v>
+        <v>46107.549961875004</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.71664663195</v>
+        <v>46107.549979965275</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2438,13 +2438,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.55618510417</v>
+        <v>46065.3895184375</v>
       </c>
       <c r="C20" s="5">
-        <v>46107.71667349537</v>
+        <v>46107.55000682871</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.71668815972</v>
+        <v>46107.55002149305</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2503,13 +2503,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.55618546296</v>
+        <v>46065.38951879629</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.51353465278</v>
+        <v>46114.34686798611</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.513551041666</v>
+        <v>46114.346884375</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>
@@ -2568,13 +2568,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.55618579861</v>
+        <v>46065.389519131946</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.716727499996</v>
+        <v>46107.55006083334</v>
       </c>
       <c r="D22" s="5">
-        <v>46107.7167425</v>
+        <v>46107.55007583334</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2633,13 +2633,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.55618377315</v>
+        <v>46065.38951710648</v>
       </c>
       <c r="C23" s="8">
-        <v>46107.71696391204</v>
+        <v>46107.55029724537</v>
       </c>
       <c r="D23" s="8">
-        <v>46107.71698142361</v>
+        <v>46107.55031475694</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2698,13 +2698,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.55618408565</v>
+        <v>46065.38951741898</v>
       </c>
       <c r="C24" s="5">
-        <v>46155.829147384255</v>
+        <v>46155.6624807176</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.829164849536</v>
+        <v>46155.66249818287</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2751,13 +2751,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.55618457176</v>
+        <v>46065.38951790509</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.787804444444</v>
+        <v>46111.62113777778</v>
       </c>
       <c r="D25" s="8">
-        <v>46111.787805810185</v>
+        <v>46111.62113914352</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2816,13 +2816,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.55618488426</v>
+        <v>46065.38951821759</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.787652997686</v>
+        <v>46111.62098633102</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.787655057866</v>
+        <v>46111.62098839121</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2877,13 +2877,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.55618519676</v>
+        <v>46065.38951853009</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.787702974536</v>
+        <v>46111.62103630787</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.78770444445</v>
+        <v>46111.621037777775</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>110</v>
@@ -2938,13 +2938,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.55618554398</v>
+        <v>46065.38951887732</v>
       </c>
       <c r="C28" s="5">
-        <v>46154.55745853009</v>
+        <v>46154.39079186342</v>
       </c>
       <c r="D28" s="5">
-        <v>46189.16759819444</v>
+        <v>46189.00093152778</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3003,13 +3003,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.55618591435</v>
+        <v>46065.389519247685</v>
       </c>
       <c r="C29" s="8">
-        <v>46129.59541854166</v>
+        <v>46129.428751875</v>
       </c>
       <c r="D29" s="8">
-        <v>46129.595419791665</v>
+        <v>46129.428753125</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3064,13 +3064,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.556186319445</v>
+        <v>46065.389519652774</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.55743853009</v>
+        <v>46154.39077186343</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.55744005787</v>
+        <v>46154.390773391206</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3125,13 +3125,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.55618663195</v>
+        <v>46065.389519965276</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.78799822916</v>
+        <v>46111.6213315625</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.7880109838</v>
+        <v>46111.62134431713</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3190,13 +3190,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.556187291666</v>
+        <v>46065.389520625</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.787925682875</v>
+        <v>46111.6212590162</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.78792702546</v>
+        <v>46111.62126035879</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3251,13 +3251,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.55618836806</v>
+        <v>46065.38952170139</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.787983692135</v>
+        <v>46111.62131702546</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.78798533565</v>
+        <v>46111.621318668986</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3312,13 +3312,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46067.8571246412</v>
+        <v>46067.69045797454</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.78824666666</v>
+        <v>46111.62158</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.78827104167</v>
+        <v>46111.621604375</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3377,13 +3377,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46067.857276689814</v>
+        <v>46067.69061002315</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.78816138889</v>
+        <v>46111.62149472222</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.78816261574</v>
+        <v>46111.621495949075</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3432,13 +3432,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46067.857363773146</v>
+        <v>46067.69069710648</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.788230289356</v>
+        <v>46111.621563622684</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.788231921295</v>
+        <v>46111.62156525463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3487,13 +3487,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46067.85744677084</v>
+        <v>46067.69078010417</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.78820322917</v>
+        <v>46111.621536562496</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.78820454861</v>
+        <v>46111.62153788195</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3542,13 +3542,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.556190358795</v>
+        <v>46065.38952369213</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.78857341435</v>
+        <v>46111.621906747685</v>
       </c>
       <c r="D38" s="5">
-        <v>46135.581084571764</v>
+        <v>46135.41441790509</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3607,13 +3607,13 @@
         <v>147</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.55619072917</v>
+        <v>46065.3895240625</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.78868280092</v>
+        <v>46111.622016134264</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.51356104166</v>
+        <v>46114.346894375005</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>78</v>
@@ -3668,13 +3668,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.55619109954</v>
+        <v>46065.389524432874</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.78876285879</v>
+        <v>46111.62209619213</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.78876418981</v>
+        <v>46111.62209752315</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3729,13 +3729,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.55618292824</v>
+        <v>46065.38951626157</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.79691798611</v>
+        <v>46114.630251319446</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.79693067129</v>
+        <v>46114.630264004634</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3782,13 +3782,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.80981607639</v>
+        <v>46070.64314940972</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.76383292824</v>
+        <v>46114.59716626158</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.763849270836</v>
+        <v>46114.597182604164</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3847,13 +3847,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.55618320602</v>
+        <v>46065.38951653935</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.796819525465</v>
+        <v>46114.630152858794</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.796836574074</v>
+        <v>46114.63016990741</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -3912,13 +3912,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46086.62629980324</v>
+        <v>46086.459633136576</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.79685944444</v>
+        <v>46114.63019277778</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.79687481481</v>
+        <v>46114.63020814815</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3975,13 +3975,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="8">
-        <v>46086.62665857639</v>
+        <v>46086.45999190972</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.796896562504</v>
+        <v>46114.63022989583</v>
       </c>
       <c r="D45" s="8">
-        <v>46123.179709375</v>
+        <v>46123.013042708335</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>169</v>
@@ -4038,13 +4038,13 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46065.5561834838</v>
+        <v>46065.38951681713</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.71751386574</v>
+        <v>46107.550847199076</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.71752689815</v>
+        <v>46107.55086023148</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4091,13 +4091,13 @@
         <v>175</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.55618375</v>
+        <v>46065.389517083335</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.71741560185</v>
+        <v>46107.55074893519</v>
       </c>
       <c r="D47" s="8">
-        <v>46135.581055752315</v>
+        <v>46135.41438908565</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>176</v>
@@ -4156,13 +4156,13 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46065.55618409722</v>
+        <v>46065.38951743055</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.717497627316</v>
+        <v>46107.55083096065</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.717514398144</v>
+        <v>46107.55084773148</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>181</v>
@@ -4221,13 +4221,13 @@
         <v>185</v>
       </c>
       <c r="B49" s="8">
-        <v>46065.55618608797</v>
+        <v>46065.3895194213</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.717866886574</v>
+        <v>46107.55120021991</v>
       </c>
       <c r="D49" s="8">
-        <v>46135.58113832176</v>
+        <v>46135.414471655095</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>186</v>
@@ -4272,13 +4272,13 @@
         <v>188</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.55618865741</v>
+        <v>46065.38952199074</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.717601446755</v>
+        <v>46107.5509347801</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.71761978009</v>
+        <v>46107.55095311343</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>189</v>
@@ -4337,13 +4337,13 @@
         <v>193</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.556191145835</v>
+        <v>46065.389524479164</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.71772638889</v>
+        <v>46107.551059722224</v>
       </c>
       <c r="D51" s="8">
-        <v>46135.581011365735</v>
+        <v>46135.41434469908</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>194</v>
@@ -4402,13 +4402,13 @@
         <v>197</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.556183113426</v>
+        <v>46065.389516446754</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.71785043982</v>
+        <v>46107.55118377315</v>
       </c>
       <c r="D52" s="5">
-        <v>46135.581111631946</v>
+        <v>46135.41444496528</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>198</v>
@@ -4465,13 +4465,13 @@
         <v>201</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.55618354167</v>
+        <v>46065.389516875</v>
       </c>
       <c r="C53" s="8">
-        <v>46154.55750765046</v>
+        <v>46154.3908409838</v>
       </c>
       <c r="D53" s="8">
-        <v>46154.55751958334</v>
+        <v>46154.390852916666</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>173</v>
@@ -4518,13 +4518,13 @@
         <v>203</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.556183865745</v>
+        <v>46065.38951719907</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.71901890046</v>
+        <v>46107.5523522338</v>
       </c>
       <c r="D54" s="5">
-        <v>46135.58129253473</v>
+        <v>46135.414625868056</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>204</v>
@@ -4581,13 +4581,13 @@
         <v>206</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.55618417824</v>
+        <v>46065.389517511576</v>
       </c>
       <c r="C55" s="8">
-        <v>46107.7190625</v>
+        <v>46107.552395833336</v>
       </c>
       <c r="D55" s="8">
-        <v>46135.5813152662</v>
+        <v>46135.41464859954</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>207</v>
@@ -4644,13 +4644,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.55618451389</v>
+        <v>46065.38951784722</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.71909642361</v>
+        <v>46107.55242975694</v>
       </c>
       <c r="D56" s="5">
-        <v>46135.581342453705</v>
+        <v>46135.41467578703</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4707,13 +4707,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.55618483796</v>
+        <v>46065.3895181713</v>
       </c>
       <c r="C57" s="8">
-        <v>46154.557489976854</v>
+        <v>46154.39082331018</v>
       </c>
       <c r="D57" s="8">
-        <v>46189.16759806713</v>
+        <v>46189.000931400464</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>57</v>
@@ -4770,13 +4770,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.55618547453</v>
+        <v>46065.389518807875</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.718628449074</v>
+        <v>46107.5519617824</v>
       </c>
       <c r="D58" s="5">
-        <v>46135.581470798614</v>
+        <v>46135.41480413194</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4819,13 +4819,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.556185775466</v>
+        <v>46065.389519108794</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.718062326385</v>
+        <v>46107.55139565972</v>
       </c>
       <c r="D59" s="8">
-        <v>46116.15986453704</v>
+        <v>46115.99319787037</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4884,13 +4884,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.55618608797</v>
+        <v>46065.3895194213</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.71817476852</v>
+        <v>46107.55150810185</v>
       </c>
       <c r="D60" s="5">
-        <v>46135.58246335648</v>
+        <v>46135.41579668982</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4947,13 +4947,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.556182534725</v>
+        <v>46065.38951586805</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.71829421296</v>
+        <v>46107.5516275463</v>
       </c>
       <c r="D61" s="8">
-        <v>46135.58157826389</v>
+        <v>46135.414911597225</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>225</v>
@@ -5010,13 +5010,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.556182939814</v>
+        <v>46065.38951627315</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.718405949076</v>
+        <v>46107.55173928241</v>
       </c>
       <c r="D62" s="5">
-        <v>46135.58157879629</v>
+        <v>46135.41491212963</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5073,13 +5073,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.55618355324</v>
+        <v>46065.38951688657</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.71850153935</v>
+        <v>46107.551834872684</v>
       </c>
       <c r="D63" s="8">
-        <v>46122.17992891204</v>
+        <v>46122.01326224537</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>170</v>
@@ -5136,13 +5136,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.55618385416</v>
+        <v>46065.389517187505</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.718607002316</v>
+        <v>46107.551940335645</v>
       </c>
       <c r="D64" s="5">
-        <v>46135.58272097222</v>
+        <v>46135.416054305555</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5199,13 +5199,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.55618413194</v>
+        <v>46065.38951746528</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.58418903935</v>
+        <v>46197.417522372685</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.584207858796</v>
+        <v>46197.41754119213</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5252,13 +5252,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.55618443287</v>
+        <v>46065.389517766205</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.584170208334</v>
+        <v>46197.41750354167</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.584189560184</v>
+        <v>46197.41752289352</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5315,13 +5315,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.55618472223</v>
+        <v>46065.389518055556</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.498886817135</v>
+        <v>46197.33222015046</v>
       </c>
       <c r="D67" s="8">
-        <v>46199.177003923614</v>
+        <v>46199.01033725694</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5378,13 +5378,13 @@
         <v>249</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.55618501158</v>
+        <v>46065.389518344906</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.58183895833</v>
+        <v>46197.415172291665</v>
       </c>
       <c r="D68" s="5">
-        <v>46203.17214591435</v>
+        <v>46203.00547924769</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>250</v>
@@ -5441,13 +5441,13 @@
         <v>252</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.55618528935</v>
+        <v>46065.38951862269</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.58195770833</v>
+        <v>46197.41529104167</v>
       </c>
       <c r="D69" s="8">
-        <v>46204.17730309028</v>
+        <v>46204.01063642361</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>253</v>
@@ -5504,11 +5504,11 @@
         <v>255</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.55618287037</v>
+        <v>46065.38951620371</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.861133530096</v>
+        <v>46126.694466863424</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>256</v>
@@ -5557,11 +5557,11 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.55618353009</v>
+        <v>46065.389516863426</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.581980393516</v>
+        <v>46197.41531372685</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5620,11 +5620,11 @@
         <v>262</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.55618322917</v>
+        <v>46065.3895165625</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.581980787036</v>
+        <v>46197.41531412037</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>263</v>
@@ -5683,13 +5683,13 @@
         <v>265</v>
       </c>
       <c r="B73" s="8">
-        <v>46086.62191810185</v>
+        <v>46086.45525143518</v>
       </c>
       <c r="C73" s="8">
-        <v>46198.633247314814</v>
+        <v>46198.46658064815</v>
       </c>
       <c r="D73" s="8">
-        <v>46198.63326113426</v>
+        <v>46198.466594467594</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>266</v>
@@ -5736,13 +5736,13 @@
         <v>268</v>
       </c>
       <c r="B74" s="5">
-        <v>46086.62261061343</v>
+        <v>46086.455943946756</v>
       </c>
       <c r="C74" s="5">
-        <v>46198.633180185185</v>
+        <v>46198.46651351852</v>
       </c>
       <c r="D74" s="5">
-        <v>46198.63339207176</v>
+        <v>46198.46672540509</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>269</v>
@@ -5801,13 +5801,13 @@
         <v>271</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.54719644676</v>
+        <v>46090.380529780094</v>
       </c>
       <c r="C75" s="8">
-        <v>46198.63323150463</v>
+        <v>46198.46656483796</v>
       </c>
       <c r="D75" s="8">
-        <v>46198.63332905092</v>
+        <v>46198.466662384264</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>272</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -1456,13 +1456,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.38951664352</v>
+        <v>46065.55618331018</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.547958055555</v>
+        <v>46092.714624722226</v>
       </c>
       <c r="D4" s="5">
-        <v>46141.61330008102</v>
+        <v>46141.77996674769</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1505,13 +1505,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.38951724537</v>
+        <v>46065.556183912035</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.54792871528</v>
+        <v>46092.71459538194</v>
       </c>
       <c r="D5" s="8">
-        <v>46147.008964189816</v>
+        <v>46147.17563085648</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1568,13 +1568,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.38951759259</v>
+        <v>46065.55618425926</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.547929305554</v>
+        <v>46092.714595972226</v>
       </c>
       <c r="D6" s="5">
-        <v>46147.008964039356</v>
+        <v>46147.17563070601</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1633,13 +1633,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.38951795139</v>
+        <v>46065.55618461806</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54792972222</v>
+        <v>46092.71459638889</v>
       </c>
       <c r="D7" s="8">
-        <v>46147.0089640625</v>
+        <v>46147.175630729165</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1698,13 +1698,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.38951825231</v>
+        <v>46065.55618491898</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.547930138884</v>
+        <v>46092.714596805556</v>
       </c>
       <c r="D8" s="5">
-        <v>46147.008964016204</v>
+        <v>46147.175630682876</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1761,13 +1761,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.38951861111</v>
+        <v>46065.556185277776</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54793074074</v>
+        <v>46092.71459740741</v>
       </c>
       <c r="D9" s="8">
-        <v>46147.008964444445</v>
+        <v>46147.17563111111</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1826,13 +1826,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.38951894676</v>
+        <v>46065.55618561343</v>
       </c>
       <c r="C10" s="5">
-        <v>46154.39088356482</v>
+        <v>46154.55755023148</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.618514305555</v>
+        <v>46196.78518097222</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1877,13 +1877,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.38951925926</v>
+        <v>46065.556185925925</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.30508837963</v>
+        <v>46114.471755046296</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.3051068287</v>
+        <v>46114.471773495374</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1942,13 +1942,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.38951961805</v>
+        <v>46065.556186284724</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.6184946875</v>
+        <v>46196.78516135417</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.61849761574</v>
+        <v>46196.78516428241</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2007,13 +2007,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.38951994213</v>
+        <v>46065.556186608796</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.3467809838</v>
+        <v>46114.51344765046</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.346793668985</v>
+        <v>46114.51346033565</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2060,13 +2060,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.38951606481</v>
+        <v>46065.55618273148</v>
       </c>
       <c r="C14" s="5">
-        <v>46107.54966615741</v>
+        <v>46107.71633282407</v>
       </c>
       <c r="D14" s="5">
-        <v>46107.549685289356</v>
+        <v>46107.71635195602</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2125,13 +2125,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.38951679398</v>
+        <v>46065.55618346065</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.549728645834</v>
+        <v>46107.7163953125</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.54974859954</v>
+        <v>46107.7164152662</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2190,13 +2190,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.38951710648</v>
+        <v>46065.55618377315</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.549819328706</v>
+        <v>46107.71648599537</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.549835011574</v>
+        <v>46107.71650167824</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2255,13 +2255,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.38951743055</v>
+        <v>46065.55618409722</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34676168981</v>
+        <v>46114.513428356484</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.346781898144</v>
+        <v>46114.513448564816</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2320,13 +2320,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.389517766205</v>
+        <v>46065.55618443287</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.346884178245</v>
+        <v>46114.5135508449</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.346898125004</v>
+        <v>46114.51356479166</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2373,13 +2373,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.38951809028</v>
+        <v>46065.55618475695</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.549961875004</v>
+        <v>46107.71662854167</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.549979965275</v>
+        <v>46107.71664663195</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2438,13 +2438,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.3895184375</v>
+        <v>46065.55618510417</v>
       </c>
       <c r="C20" s="5">
-        <v>46107.55000682871</v>
+        <v>46107.71667349537</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.55002149305</v>
+        <v>46107.71668815972</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2503,13 +2503,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.38951879629</v>
+        <v>46065.55618546296</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.34686798611</v>
+        <v>46114.51353465278</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.346884375</v>
+        <v>46114.513551041666</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>
@@ -2568,13 +2568,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.389519131946</v>
+        <v>46065.55618579861</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.55006083334</v>
+        <v>46107.716727499996</v>
       </c>
       <c r="D22" s="5">
-        <v>46107.55007583334</v>
+        <v>46107.7167425</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2633,13 +2633,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.38951710648</v>
+        <v>46065.55618377315</v>
       </c>
       <c r="C23" s="8">
-        <v>46107.55029724537</v>
+        <v>46107.71696391204</v>
       </c>
       <c r="D23" s="8">
-        <v>46107.55031475694</v>
+        <v>46107.71698142361</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2698,13 +2698,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.38951741898</v>
+        <v>46065.55618408565</v>
       </c>
       <c r="C24" s="5">
-        <v>46155.6624807176</v>
+        <v>46155.829147384255</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.66249818287</v>
+        <v>46155.829164849536</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2751,13 +2751,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.38951790509</v>
+        <v>46065.55618457176</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.62113777778</v>
+        <v>46111.787804444444</v>
       </c>
       <c r="D25" s="8">
-        <v>46111.62113914352</v>
+        <v>46111.787805810185</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2816,13 +2816,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.38951821759</v>
+        <v>46065.55618488426</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.62098633102</v>
+        <v>46111.787652997686</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.62098839121</v>
+        <v>46111.787655057866</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2877,13 +2877,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.38951853009</v>
+        <v>46065.55618519676</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.62103630787</v>
+        <v>46111.787702974536</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.621037777775</v>
+        <v>46111.78770444445</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>110</v>
@@ -2938,13 +2938,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.38951887732</v>
+        <v>46065.55618554398</v>
       </c>
       <c r="C28" s="5">
-        <v>46154.39079186342</v>
+        <v>46154.55745853009</v>
       </c>
       <c r="D28" s="5">
-        <v>46189.00093152778</v>
+        <v>46189.16759819444</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3003,13 +3003,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.389519247685</v>
+        <v>46065.55618591435</v>
       </c>
       <c r="C29" s="8">
-        <v>46129.428751875</v>
+        <v>46129.59541854166</v>
       </c>
       <c r="D29" s="8">
-        <v>46129.428753125</v>
+        <v>46129.595419791665</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3064,13 +3064,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.389519652774</v>
+        <v>46065.556186319445</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.39077186343</v>
+        <v>46154.55743853009</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.390773391206</v>
+        <v>46154.55744005787</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3125,13 +3125,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.389519965276</v>
+        <v>46065.55618663195</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.6213315625</v>
+        <v>46111.78799822916</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.62134431713</v>
+        <v>46111.7880109838</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3190,13 +3190,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.389520625</v>
+        <v>46065.556187291666</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.6212590162</v>
+        <v>46111.787925682875</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.62126035879</v>
+        <v>46111.78792702546</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3251,13 +3251,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.38952170139</v>
+        <v>46065.55618836806</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.62131702546</v>
+        <v>46111.787983692135</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.621318668986</v>
+        <v>46111.78798533565</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3312,13 +3312,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46067.69045797454</v>
+        <v>46067.8571246412</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.62158</v>
+        <v>46111.78824666666</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.621604375</v>
+        <v>46111.78827104167</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3377,13 +3377,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46067.69061002315</v>
+        <v>46067.857276689814</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.62149472222</v>
+        <v>46111.78816138889</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.621495949075</v>
+        <v>46111.78816261574</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3432,13 +3432,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46067.69069710648</v>
+        <v>46067.857363773146</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.621563622684</v>
+        <v>46111.788230289356</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.62156525463</v>
+        <v>46111.788231921295</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3487,13 +3487,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46067.69078010417</v>
+        <v>46067.85744677084</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.621536562496</v>
+        <v>46111.78820322917</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.62153788195</v>
+        <v>46111.78820454861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3542,13 +3542,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.38952369213</v>
+        <v>46065.556190358795</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.621906747685</v>
+        <v>46111.78857341435</v>
       </c>
       <c r="D38" s="5">
-        <v>46135.41441790509</v>
+        <v>46135.581084571764</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3607,13 +3607,13 @@
         <v>147</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.3895240625</v>
+        <v>46065.55619072917</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.622016134264</v>
+        <v>46111.78868280092</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.346894375005</v>
+        <v>46114.51356104166</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>78</v>
@@ -3668,13 +3668,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.389524432874</v>
+        <v>46065.55619109954</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.62209619213</v>
+        <v>46111.78876285879</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.62209752315</v>
+        <v>46111.78876418981</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3729,13 +3729,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.38951626157</v>
+        <v>46065.55618292824</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.630251319446</v>
+        <v>46114.79691798611</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.630264004634</v>
+        <v>46114.79693067129</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3782,13 +3782,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.64314940972</v>
+        <v>46070.80981607639</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59716626158</v>
+        <v>46114.76383292824</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.597182604164</v>
+        <v>46114.763849270836</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3847,13 +3847,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.38951653935</v>
+        <v>46065.55618320602</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.630152858794</v>
+        <v>46114.796819525465</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.63016990741</v>
+        <v>46114.796836574074</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -3912,13 +3912,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46086.459633136576</v>
+        <v>46086.62629980324</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.63019277778</v>
+        <v>46114.79685944444</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.63020814815</v>
+        <v>46114.79687481481</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3975,13 +3975,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="8">
-        <v>46086.45999190972</v>
+        <v>46086.62665857639</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.63022989583</v>
+        <v>46114.796896562504</v>
       </c>
       <c r="D45" s="8">
-        <v>46123.013042708335</v>
+        <v>46123.179709375</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>169</v>
@@ -4038,13 +4038,13 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46065.38951681713</v>
+        <v>46065.5561834838</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.550847199076</v>
+        <v>46107.71751386574</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.55086023148</v>
+        <v>46107.71752689815</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4091,13 +4091,13 @@
         <v>175</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.389517083335</v>
+        <v>46065.55618375</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.55074893519</v>
+        <v>46107.71741560185</v>
       </c>
       <c r="D47" s="8">
-        <v>46135.41438908565</v>
+        <v>46135.581055752315</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>176</v>
@@ -4156,13 +4156,13 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46065.38951743055</v>
+        <v>46065.55618409722</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.55083096065</v>
+        <v>46107.717497627316</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.55084773148</v>
+        <v>46107.717514398144</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>181</v>
@@ -4221,13 +4221,13 @@
         <v>185</v>
       </c>
       <c r="B49" s="8">
-        <v>46065.3895194213</v>
+        <v>46065.55618608797</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.55120021991</v>
+        <v>46107.717866886574</v>
       </c>
       <c r="D49" s="8">
-        <v>46135.414471655095</v>
+        <v>46135.58113832176</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>186</v>
@@ -4272,13 +4272,13 @@
         <v>188</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.38952199074</v>
+        <v>46065.55618865741</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.5509347801</v>
+        <v>46107.717601446755</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.55095311343</v>
+        <v>46107.71761978009</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>189</v>
@@ -4337,13 +4337,13 @@
         <v>193</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.389524479164</v>
+        <v>46065.556191145835</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.551059722224</v>
+        <v>46107.71772638889</v>
       </c>
       <c r="D51" s="8">
-        <v>46135.41434469908</v>
+        <v>46135.581011365735</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>194</v>
@@ -4402,13 +4402,13 @@
         <v>197</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.389516446754</v>
+        <v>46065.556183113426</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.55118377315</v>
+        <v>46107.71785043982</v>
       </c>
       <c r="D52" s="5">
-        <v>46135.41444496528</v>
+        <v>46135.581111631946</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>198</v>
@@ -4465,13 +4465,13 @@
         <v>201</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.389516875</v>
+        <v>46065.55618354167</v>
       </c>
       <c r="C53" s="8">
-        <v>46154.3908409838</v>
+        <v>46154.55750765046</v>
       </c>
       <c r="D53" s="8">
-        <v>46154.390852916666</v>
+        <v>46154.55751958334</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>173</v>
@@ -4518,13 +4518,13 @@
         <v>203</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.38951719907</v>
+        <v>46065.556183865745</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.5523522338</v>
+        <v>46107.71901890046</v>
       </c>
       <c r="D54" s="5">
-        <v>46135.414625868056</v>
+        <v>46135.58129253473</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>204</v>
@@ -4581,13 +4581,13 @@
         <v>206</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.389517511576</v>
+        <v>46065.55618417824</v>
       </c>
       <c r="C55" s="8">
-        <v>46107.552395833336</v>
+        <v>46107.7190625</v>
       </c>
       <c r="D55" s="8">
-        <v>46135.41464859954</v>
+        <v>46135.5813152662</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>207</v>
@@ -4644,13 +4644,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.38951784722</v>
+        <v>46065.55618451389</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.55242975694</v>
+        <v>46107.71909642361</v>
       </c>
       <c r="D56" s="5">
-        <v>46135.41467578703</v>
+        <v>46135.581342453705</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4707,13 +4707,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.3895181713</v>
+        <v>46065.55618483796</v>
       </c>
       <c r="C57" s="8">
-        <v>46154.39082331018</v>
+        <v>46154.557489976854</v>
       </c>
       <c r="D57" s="8">
-        <v>46189.000931400464</v>
+        <v>46189.16759806713</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>57</v>
@@ -4770,13 +4770,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.389518807875</v>
+        <v>46065.55618547453</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.5519617824</v>
+        <v>46107.718628449074</v>
       </c>
       <c r="D58" s="5">
-        <v>46135.41480413194</v>
+        <v>46135.581470798614</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4819,13 +4819,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.389519108794</v>
+        <v>46065.556185775466</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.55139565972</v>
+        <v>46107.718062326385</v>
       </c>
       <c r="D59" s="8">
-        <v>46115.99319787037</v>
+        <v>46116.15986453704</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4884,13 +4884,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.3895194213</v>
+        <v>46065.55618608797</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.55150810185</v>
+        <v>46107.71817476852</v>
       </c>
       <c r="D60" s="5">
-        <v>46135.41579668982</v>
+        <v>46135.58246335648</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4947,13 +4947,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.38951586805</v>
+        <v>46065.556182534725</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.5516275463</v>
+        <v>46107.71829421296</v>
       </c>
       <c r="D61" s="8">
-        <v>46135.414911597225</v>
+        <v>46135.58157826389</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>225</v>
@@ -5010,13 +5010,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.38951627315</v>
+        <v>46065.556182939814</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.55173928241</v>
+        <v>46107.718405949076</v>
       </c>
       <c r="D62" s="5">
-        <v>46135.41491212963</v>
+        <v>46135.58157879629</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5073,13 +5073,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.38951688657</v>
+        <v>46065.55618355324</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.551834872684</v>
+        <v>46107.71850153935</v>
       </c>
       <c r="D63" s="8">
-        <v>46122.01326224537</v>
+        <v>46122.17992891204</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>170</v>
@@ -5136,13 +5136,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.389517187505</v>
+        <v>46065.55618385416</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.551940335645</v>
+        <v>46107.718607002316</v>
       </c>
       <c r="D64" s="5">
-        <v>46135.416054305555</v>
+        <v>46135.58272097222</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5199,13 +5199,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.38951746528</v>
+        <v>46065.55618413194</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.417522372685</v>
+        <v>46197.58418903935</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.41754119213</v>
+        <v>46197.584207858796</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5252,13 +5252,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.389517766205</v>
+        <v>46065.55618443287</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.41750354167</v>
+        <v>46197.584170208334</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.41752289352</v>
+        <v>46197.584189560184</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5315,13 +5315,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.389518055556</v>
+        <v>46065.55618472223</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.33222015046</v>
+        <v>46197.498886817135</v>
       </c>
       <c r="D67" s="8">
-        <v>46199.01033725694</v>
+        <v>46199.177003923614</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5378,13 +5378,13 @@
         <v>249</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.389518344906</v>
+        <v>46065.55618501158</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.415172291665</v>
+        <v>46197.58183895833</v>
       </c>
       <c r="D68" s="5">
-        <v>46203.00547924769</v>
+        <v>46203.17214591435</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>250</v>
@@ -5441,13 +5441,13 @@
         <v>252</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.38951862269</v>
+        <v>46065.55618528935</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.41529104167</v>
+        <v>46197.58195770833</v>
       </c>
       <c r="D69" s="8">
-        <v>46204.01063642361</v>
+        <v>46204.17730309028</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>253</v>
@@ -5504,11 +5504,11 @@
         <v>255</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.38951620371</v>
+        <v>46065.55618287037</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.694466863424</v>
+        <v>46126.861133530096</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>256</v>
@@ -5557,11 +5557,11 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.389516863426</v>
+        <v>46065.55618353009</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.41531372685</v>
+        <v>46197.581980393516</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5620,11 +5620,11 @@
         <v>262</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.3895165625</v>
+        <v>46065.55618322917</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.41531412037</v>
+        <v>46197.581980787036</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>263</v>
@@ -5683,13 +5683,13 @@
         <v>265</v>
       </c>
       <c r="B73" s="8">
-        <v>46086.45525143518</v>
+        <v>46086.62191810185</v>
       </c>
       <c r="C73" s="8">
-        <v>46198.46658064815</v>
+        <v>46198.633247314814</v>
       </c>
       <c r="D73" s="8">
-        <v>46198.466594467594</v>
+        <v>46198.63326113426</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>266</v>
@@ -5736,13 +5736,13 @@
         <v>268</v>
       </c>
       <c r="B74" s="5">
-        <v>46086.455943946756</v>
+        <v>46086.62261061343</v>
       </c>
       <c r="C74" s="5">
-        <v>46198.46651351852</v>
+        <v>46198.633180185185</v>
       </c>
       <c r="D74" s="5">
-        <v>46198.46672540509</v>
+        <v>46198.63339207176</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>269</v>
@@ -5801,13 +5801,13 @@
         <v>271</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.380529780094</v>
+        <v>46090.54719644676</v>
       </c>
       <c r="C75" s="8">
-        <v>46198.46656483796</v>
+        <v>46198.63323150463</v>
       </c>
       <c r="D75" s="8">
-        <v>46198.466662384264</v>
+        <v>46198.63332905092</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>272</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="274">
   <si>
     <t>50001515 - CLIENTE POR DEFINIR</t>
   </si>
@@ -797,6 +797,9 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1213242667616399</t>
@@ -5561,7 +5564,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.581980393516</v>
+        <v>46210.17306695602</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5608,8 +5611,8 @@
       <c r="S71" s="9">
         <v>0</v>
       </c>
-      <c r="T71" s="11" t="s">
-        <v>107</v>
+      <c r="T71" s="12" t="s">
+        <v>262</v>
       </c>
       <c r="U71" s="12" t="s">
         <v>47</v>
@@ -5617,17 +5620,17 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B72" s="5">
         <v>46065.55618322917</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.581980787036</v>
+        <v>46210.17306699074</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5657,7 +5660,7 @@
         <v>256</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>256</v>
@@ -5671,8 +5674,8 @@
       <c r="S72" s="6">
         <v>0</v>
       </c>
-      <c r="T72" s="11" t="s">
-        <v>107</v>
+      <c r="T72" s="12" t="s">
+        <v>262</v>
       </c>
       <c r="U72" s="12" t="s">
         <v>47</v>
@@ -5680,7 +5683,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B73" s="8">
         <v>46086.62191810185</v>
@@ -5692,7 +5695,7 @@
         <v>46198.63326113426</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5716,7 +5719,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5733,7 +5736,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B74" s="5">
         <v>46086.62261061343</v>
@@ -5742,10 +5745,10 @@
         <v>46198.633180185185</v>
       </c>
       <c r="D74" s="5">
-        <v>46198.63339207176</v>
+        <v>46210.17306774306</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5772,13 +5775,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>253</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q74" s="5">
         <v>46217</v>
@@ -5789,8 +5792,8 @@
       <c r="S74" s="6">
         <v>1</v>
       </c>
-      <c r="T74" s="11" t="s">
-        <v>107</v>
+      <c r="T74" s="12" t="s">
+        <v>262</v>
       </c>
       <c r="U74" s="11" t="s">
         <v>32</v>
@@ -5798,7 +5801,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B75" s="8">
         <v>46090.54719644676</v>
@@ -5810,7 +5813,7 @@
         <v>46198.63332905092</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5837,13 +5840,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q75" s="8">
         <v>46226</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -1459,13 +1459,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.55618331018</v>
+        <v>46065.38951664352</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.714624722226</v>
+        <v>46092.547958055555</v>
       </c>
       <c r="D4" s="5">
-        <v>46141.77996674769</v>
+        <v>46141.61330008102</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1508,13 +1508,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.556183912035</v>
+        <v>46065.38951724537</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.71459538194</v>
+        <v>46092.54792871528</v>
       </c>
       <c r="D5" s="8">
-        <v>46147.17563085648</v>
+        <v>46147.008964189816</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1571,13 +1571,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.55618425926</v>
+        <v>46065.38951759259</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.714595972226</v>
+        <v>46092.547929305554</v>
       </c>
       <c r="D6" s="5">
-        <v>46147.17563070601</v>
+        <v>46147.008964039356</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1636,13 +1636,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.55618461806</v>
+        <v>46065.38951795139</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71459638889</v>
+        <v>46092.54792972222</v>
       </c>
       <c r="D7" s="8">
-        <v>46147.175630729165</v>
+        <v>46147.0089640625</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1701,13 +1701,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.55618491898</v>
+        <v>46065.38951825231</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.714596805556</v>
+        <v>46092.547930138884</v>
       </c>
       <c r="D8" s="5">
-        <v>46147.175630682876</v>
+        <v>46147.008964016204</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1764,13 +1764,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.556185277776</v>
+        <v>46065.38951861111</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71459740741</v>
+        <v>46092.54793074074</v>
       </c>
       <c r="D9" s="8">
-        <v>46147.17563111111</v>
+        <v>46147.008964444445</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1829,13 +1829,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.55618561343</v>
+        <v>46065.38951894676</v>
       </c>
       <c r="C10" s="5">
-        <v>46154.55755023148</v>
+        <v>46154.39088356482</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.78518097222</v>
+        <v>46196.618514305555</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1880,13 +1880,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.556185925925</v>
+        <v>46065.38951925926</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.471755046296</v>
+        <v>46114.30508837963</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.471773495374</v>
+        <v>46114.3051068287</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1945,13 +1945,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.556186284724</v>
+        <v>46065.38951961805</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.78516135417</v>
+        <v>46196.6184946875</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.78516428241</v>
+        <v>46196.61849761574</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2010,13 +2010,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.556186608796</v>
+        <v>46065.38951994213</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51344765046</v>
+        <v>46114.3467809838</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.51346033565</v>
+        <v>46114.346793668985</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2063,13 +2063,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.55618273148</v>
+        <v>46065.38951606481</v>
       </c>
       <c r="C14" s="5">
-        <v>46107.71633282407</v>
+        <v>46107.54966615741</v>
       </c>
       <c r="D14" s="5">
-        <v>46107.71635195602</v>
+        <v>46107.549685289356</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2128,13 +2128,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.55618346065</v>
+        <v>46065.38951679398</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.7163953125</v>
+        <v>46107.549728645834</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.7164152662</v>
+        <v>46107.54974859954</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2193,13 +2193,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.55618377315</v>
+        <v>46065.38951710648</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.71648599537</v>
+        <v>46107.549819328706</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.71650167824</v>
+        <v>46107.549835011574</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2258,13 +2258,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.55618409722</v>
+        <v>46065.38951743055</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.513428356484</v>
+        <v>46114.34676168981</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.513448564816</v>
+        <v>46114.346781898144</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2323,13 +2323,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.55618443287</v>
+        <v>46065.389517766205</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.5135508449</v>
+        <v>46114.346884178245</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.51356479166</v>
+        <v>46114.346898125004</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2376,13 +2376,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.55618475695</v>
+        <v>46065.38951809028</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.71662854167</v>
+        <v>46107.549961875004</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.71664663195</v>
+        <v>46107.549979965275</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2441,13 +2441,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.55618510417</v>
+        <v>46065.3895184375</v>
       </c>
       <c r="C20" s="5">
-        <v>46107.71667349537</v>
+        <v>46107.55000682871</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.71668815972</v>
+        <v>46107.55002149305</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2506,13 +2506,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.55618546296</v>
+        <v>46065.38951879629</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.51353465278</v>
+        <v>46114.34686798611</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.513551041666</v>
+        <v>46114.346884375</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>
@@ -2571,13 +2571,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.55618579861</v>
+        <v>46065.389519131946</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.716727499996</v>
+        <v>46107.55006083334</v>
       </c>
       <c r="D22" s="5">
-        <v>46107.7167425</v>
+        <v>46107.55007583334</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2636,13 +2636,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.55618377315</v>
+        <v>46065.38951710648</v>
       </c>
       <c r="C23" s="8">
-        <v>46107.71696391204</v>
+        <v>46107.55029724537</v>
       </c>
       <c r="D23" s="8">
-        <v>46107.71698142361</v>
+        <v>46107.55031475694</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2701,13 +2701,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.55618408565</v>
+        <v>46065.38951741898</v>
       </c>
       <c r="C24" s="5">
-        <v>46155.829147384255</v>
+        <v>46155.6624807176</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.829164849536</v>
+        <v>46155.66249818287</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2754,13 +2754,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.55618457176</v>
+        <v>46065.38951790509</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.787804444444</v>
+        <v>46111.62113777778</v>
       </c>
       <c r="D25" s="8">
-        <v>46111.787805810185</v>
+        <v>46111.62113914352</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2819,13 +2819,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.55618488426</v>
+        <v>46065.38951821759</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.787652997686</v>
+        <v>46111.62098633102</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.787655057866</v>
+        <v>46111.62098839121</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2880,13 +2880,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.55618519676</v>
+        <v>46065.38951853009</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.787702974536</v>
+        <v>46111.62103630787</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.78770444445</v>
+        <v>46111.621037777775</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>110</v>
@@ -2941,13 +2941,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.55618554398</v>
+        <v>46065.38951887732</v>
       </c>
       <c r="C28" s="5">
-        <v>46154.55745853009</v>
+        <v>46154.39079186342</v>
       </c>
       <c r="D28" s="5">
-        <v>46189.16759819444</v>
+        <v>46189.00093152778</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3006,13 +3006,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.55618591435</v>
+        <v>46065.389519247685</v>
       </c>
       <c r="C29" s="8">
-        <v>46129.59541854166</v>
+        <v>46129.428751875</v>
       </c>
       <c r="D29" s="8">
-        <v>46129.595419791665</v>
+        <v>46129.428753125</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3067,13 +3067,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.556186319445</v>
+        <v>46065.389519652774</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.55743853009</v>
+        <v>46154.39077186343</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.55744005787</v>
+        <v>46154.390773391206</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3128,13 +3128,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.55618663195</v>
+        <v>46065.389519965276</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.78799822916</v>
+        <v>46111.6213315625</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.7880109838</v>
+        <v>46111.62134431713</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3193,13 +3193,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.556187291666</v>
+        <v>46065.389520625</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.787925682875</v>
+        <v>46111.6212590162</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.78792702546</v>
+        <v>46111.62126035879</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3254,13 +3254,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.55618836806</v>
+        <v>46065.38952170139</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.787983692135</v>
+        <v>46111.62131702546</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.78798533565</v>
+        <v>46111.621318668986</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3315,13 +3315,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46067.8571246412</v>
+        <v>46067.69045797454</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.78824666666</v>
+        <v>46111.62158</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.78827104167</v>
+        <v>46111.621604375</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3380,13 +3380,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46067.857276689814</v>
+        <v>46067.69061002315</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.78816138889</v>
+        <v>46111.62149472222</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.78816261574</v>
+        <v>46111.621495949075</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3435,13 +3435,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46067.857363773146</v>
+        <v>46067.69069710648</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.788230289356</v>
+        <v>46111.621563622684</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.788231921295</v>
+        <v>46111.62156525463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3490,13 +3490,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46067.85744677084</v>
+        <v>46067.69078010417</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.78820322917</v>
+        <v>46111.621536562496</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.78820454861</v>
+        <v>46111.62153788195</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3545,13 +3545,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.556190358795</v>
+        <v>46065.38952369213</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.78857341435</v>
+        <v>46111.621906747685</v>
       </c>
       <c r="D38" s="5">
-        <v>46135.581084571764</v>
+        <v>46135.41441790509</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3610,13 +3610,13 @@
         <v>147</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.55619072917</v>
+        <v>46065.3895240625</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.78868280092</v>
+        <v>46111.622016134264</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.51356104166</v>
+        <v>46114.346894375005</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>78</v>
@@ -3671,13 +3671,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.55619109954</v>
+        <v>46065.389524432874</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.78876285879</v>
+        <v>46111.62209619213</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.78876418981</v>
+        <v>46111.62209752315</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3732,13 +3732,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.55618292824</v>
+        <v>46065.38951626157</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.79691798611</v>
+        <v>46114.630251319446</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.79693067129</v>
+        <v>46114.630264004634</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3785,13 +3785,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.80981607639</v>
+        <v>46070.64314940972</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.76383292824</v>
+        <v>46114.59716626158</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.763849270836</v>
+        <v>46114.597182604164</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3850,13 +3850,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.55618320602</v>
+        <v>46065.38951653935</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.796819525465</v>
+        <v>46114.630152858794</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.796836574074</v>
+        <v>46114.63016990741</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -3915,13 +3915,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46086.62629980324</v>
+        <v>46086.459633136576</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.79685944444</v>
+        <v>46114.63019277778</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.79687481481</v>
+        <v>46114.63020814815</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3978,13 +3978,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="8">
-        <v>46086.62665857639</v>
+        <v>46086.45999190972</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.796896562504</v>
+        <v>46114.63022989583</v>
       </c>
       <c r="D45" s="8">
-        <v>46123.179709375</v>
+        <v>46123.013042708335</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>169</v>
@@ -4041,13 +4041,13 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46065.5561834838</v>
+        <v>46065.38951681713</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.71751386574</v>
+        <v>46107.550847199076</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.71752689815</v>
+        <v>46107.55086023148</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4094,13 +4094,13 @@
         <v>175</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.55618375</v>
+        <v>46065.389517083335</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.71741560185</v>
+        <v>46107.55074893519</v>
       </c>
       <c r="D47" s="8">
-        <v>46135.581055752315</v>
+        <v>46135.41438908565</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>176</v>
@@ -4159,13 +4159,13 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46065.55618409722</v>
+        <v>46065.38951743055</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.717497627316</v>
+        <v>46107.55083096065</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.717514398144</v>
+        <v>46107.55084773148</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>181</v>
@@ -4224,13 +4224,13 @@
         <v>185</v>
       </c>
       <c r="B49" s="8">
-        <v>46065.55618608797</v>
+        <v>46065.3895194213</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.717866886574</v>
+        <v>46107.55120021991</v>
       </c>
       <c r="D49" s="8">
-        <v>46135.58113832176</v>
+        <v>46135.414471655095</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>186</v>
@@ -4275,13 +4275,13 @@
         <v>188</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.55618865741</v>
+        <v>46065.38952199074</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.717601446755</v>
+        <v>46107.5509347801</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.71761978009</v>
+        <v>46107.55095311343</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>189</v>
@@ -4340,13 +4340,13 @@
         <v>193</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.556191145835</v>
+        <v>46065.389524479164</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.71772638889</v>
+        <v>46107.551059722224</v>
       </c>
       <c r="D51" s="8">
-        <v>46135.581011365735</v>
+        <v>46135.41434469908</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>194</v>
@@ -4405,13 +4405,13 @@
         <v>197</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.556183113426</v>
+        <v>46065.389516446754</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.71785043982</v>
+        <v>46107.55118377315</v>
       </c>
       <c r="D52" s="5">
-        <v>46135.581111631946</v>
+        <v>46135.41444496528</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>198</v>
@@ -4468,13 +4468,13 @@
         <v>201</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.55618354167</v>
+        <v>46065.389516875</v>
       </c>
       <c r="C53" s="8">
-        <v>46154.55750765046</v>
+        <v>46154.3908409838</v>
       </c>
       <c r="D53" s="8">
-        <v>46154.55751958334</v>
+        <v>46154.390852916666</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>173</v>
@@ -4521,13 +4521,13 @@
         <v>203</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.556183865745</v>
+        <v>46065.38951719907</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.71901890046</v>
+        <v>46107.5523522338</v>
       </c>
       <c r="D54" s="5">
-        <v>46135.58129253473</v>
+        <v>46135.414625868056</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>204</v>
@@ -4584,13 +4584,13 @@
         <v>206</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.55618417824</v>
+        <v>46065.389517511576</v>
       </c>
       <c r="C55" s="8">
-        <v>46107.7190625</v>
+        <v>46107.552395833336</v>
       </c>
       <c r="D55" s="8">
-        <v>46135.5813152662</v>
+        <v>46135.41464859954</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>207</v>
@@ -4647,13 +4647,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.55618451389</v>
+        <v>46065.38951784722</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.71909642361</v>
+        <v>46107.55242975694</v>
       </c>
       <c r="D56" s="5">
-        <v>46135.581342453705</v>
+        <v>46135.41467578703</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4710,13 +4710,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.55618483796</v>
+        <v>46065.3895181713</v>
       </c>
       <c r="C57" s="8">
-        <v>46154.557489976854</v>
+        <v>46154.39082331018</v>
       </c>
       <c r="D57" s="8">
-        <v>46189.16759806713</v>
+        <v>46189.000931400464</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>57</v>
@@ -4773,13 +4773,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.55618547453</v>
+        <v>46065.389518807875</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.718628449074</v>
+        <v>46107.5519617824</v>
       </c>
       <c r="D58" s="5">
-        <v>46135.581470798614</v>
+        <v>46135.41480413194</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4822,13 +4822,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.556185775466</v>
+        <v>46065.389519108794</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.718062326385</v>
+        <v>46107.55139565972</v>
       </c>
       <c r="D59" s="8">
-        <v>46116.15986453704</v>
+        <v>46115.99319787037</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4887,13 +4887,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.55618608797</v>
+        <v>46065.3895194213</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.71817476852</v>
+        <v>46107.55150810185</v>
       </c>
       <c r="D60" s="5">
-        <v>46135.58246335648</v>
+        <v>46135.41579668982</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4950,13 +4950,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.556182534725</v>
+        <v>46065.38951586805</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.71829421296</v>
+        <v>46107.5516275463</v>
       </c>
       <c r="D61" s="8">
-        <v>46135.58157826389</v>
+        <v>46135.414911597225</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>225</v>
@@ -5013,13 +5013,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.556182939814</v>
+        <v>46065.38951627315</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.718405949076</v>
+        <v>46107.55173928241</v>
       </c>
       <c r="D62" s="5">
-        <v>46135.58157879629</v>
+        <v>46135.41491212963</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5076,13 +5076,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.55618355324</v>
+        <v>46065.38951688657</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.71850153935</v>
+        <v>46107.551834872684</v>
       </c>
       <c r="D63" s="8">
-        <v>46122.17992891204</v>
+        <v>46122.01326224537</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>170</v>
@@ -5139,13 +5139,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.55618385416</v>
+        <v>46065.389517187505</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.718607002316</v>
+        <v>46107.551940335645</v>
       </c>
       <c r="D64" s="5">
-        <v>46135.58272097222</v>
+        <v>46135.416054305555</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5202,13 +5202,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.55618413194</v>
+        <v>46065.38951746528</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.58418903935</v>
+        <v>46197.417522372685</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.584207858796</v>
+        <v>46197.41754119213</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5255,13 +5255,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.55618443287</v>
+        <v>46065.389517766205</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.584170208334</v>
+        <v>46197.41750354167</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.584189560184</v>
+        <v>46197.41752289352</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5318,13 +5318,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.55618472223</v>
+        <v>46065.389518055556</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.498886817135</v>
+        <v>46197.33222015046</v>
       </c>
       <c r="D67" s="8">
-        <v>46199.177003923614</v>
+        <v>46199.01033725694</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5381,13 +5381,13 @@
         <v>249</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.55618501158</v>
+        <v>46065.389518344906</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.58183895833</v>
+        <v>46197.415172291665</v>
       </c>
       <c r="D68" s="5">
-        <v>46203.17214591435</v>
+        <v>46203.00547924769</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>250</v>
@@ -5444,13 +5444,13 @@
         <v>252</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.55618528935</v>
+        <v>46065.38951862269</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.58195770833</v>
+        <v>46197.41529104167</v>
       </c>
       <c r="D69" s="8">
-        <v>46204.17730309028</v>
+        <v>46204.01063642361</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>253</v>
@@ -5507,11 +5507,11 @@
         <v>255</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.55618287037</v>
+        <v>46065.38951620371</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.861133530096</v>
+        <v>46126.694466863424</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>256</v>
@@ -5560,11 +5560,11 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.55618353009</v>
+        <v>46065.389516863426</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46210.17306695602</v>
+        <v>46210.00640028935</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5623,11 +5623,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.55618322917</v>
+        <v>46065.3895165625</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46210.17306699074</v>
+        <v>46210.00640032407</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5686,13 +5686,13 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46086.62191810185</v>
+        <v>46086.45525143518</v>
       </c>
       <c r="C73" s="8">
-        <v>46198.633247314814</v>
+        <v>46198.46658064815</v>
       </c>
       <c r="D73" s="8">
-        <v>46198.63326113426</v>
+        <v>46198.466594467594</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5739,13 +5739,13 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46086.62261061343</v>
+        <v>46086.455943946756</v>
       </c>
       <c r="C74" s="5">
-        <v>46198.633180185185</v>
+        <v>46198.46651351852</v>
       </c>
       <c r="D74" s="5">
-        <v>46210.17306774306</v>
+        <v>46210.00640107639</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5804,13 +5804,13 @@
         <v>272</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.54719644676</v>
+        <v>46090.380529780094</v>
       </c>
       <c r="C75" s="8">
-        <v>46198.63323150463</v>
+        <v>46198.46656483796</v>
       </c>
       <c r="D75" s="8">
-        <v>46198.63332905092</v>
+        <v>46198.466662384264</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -1459,13 +1459,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.38951664352</v>
+        <v>46065.55618331018</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.547958055555</v>
+        <v>46092.714624722226</v>
       </c>
       <c r="D4" s="5">
-        <v>46141.61330008102</v>
+        <v>46141.77996674769</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1508,13 +1508,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.38951724537</v>
+        <v>46065.556183912035</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.54792871528</v>
+        <v>46092.71459538194</v>
       </c>
       <c r="D5" s="8">
-        <v>46147.008964189816</v>
+        <v>46147.17563085648</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1571,13 +1571,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.38951759259</v>
+        <v>46065.55618425926</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.547929305554</v>
+        <v>46092.714595972226</v>
       </c>
       <c r="D6" s="5">
-        <v>46147.008964039356</v>
+        <v>46147.17563070601</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1636,13 +1636,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.38951795139</v>
+        <v>46065.55618461806</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.54792972222</v>
+        <v>46092.71459638889</v>
       </c>
       <c r="D7" s="8">
-        <v>46147.0089640625</v>
+        <v>46147.175630729165</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1701,13 +1701,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.38951825231</v>
+        <v>46065.55618491898</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.547930138884</v>
+        <v>46092.714596805556</v>
       </c>
       <c r="D8" s="5">
-        <v>46147.008964016204</v>
+        <v>46147.175630682876</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1764,13 +1764,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.38951861111</v>
+        <v>46065.556185277776</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.54793074074</v>
+        <v>46092.71459740741</v>
       </c>
       <c r="D9" s="8">
-        <v>46147.008964444445</v>
+        <v>46147.17563111111</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1829,13 +1829,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.38951894676</v>
+        <v>46065.55618561343</v>
       </c>
       <c r="C10" s="5">
-        <v>46154.39088356482</v>
+        <v>46154.55755023148</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.618514305555</v>
+        <v>46196.78518097222</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1880,13 +1880,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.38951925926</v>
+        <v>46065.556185925925</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.30508837963</v>
+        <v>46114.471755046296</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.3051068287</v>
+        <v>46114.471773495374</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1945,13 +1945,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.38951961805</v>
+        <v>46065.556186284724</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.6184946875</v>
+        <v>46196.78516135417</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.61849761574</v>
+        <v>46196.78516428241</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2010,13 +2010,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.38951994213</v>
+        <v>46065.556186608796</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.3467809838</v>
+        <v>46114.51344765046</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.346793668985</v>
+        <v>46114.51346033565</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2063,13 +2063,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.38951606481</v>
+        <v>46065.55618273148</v>
       </c>
       <c r="C14" s="5">
-        <v>46107.54966615741</v>
+        <v>46107.71633282407</v>
       </c>
       <c r="D14" s="5">
-        <v>46107.549685289356</v>
+        <v>46107.71635195602</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2128,13 +2128,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.38951679398</v>
+        <v>46065.55618346065</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.549728645834</v>
+        <v>46107.7163953125</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.54974859954</v>
+        <v>46107.7164152662</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2193,13 +2193,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.38951710648</v>
+        <v>46065.55618377315</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.549819328706</v>
+        <v>46107.71648599537</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.549835011574</v>
+        <v>46107.71650167824</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2258,13 +2258,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.38951743055</v>
+        <v>46065.55618409722</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34676168981</v>
+        <v>46114.513428356484</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.346781898144</v>
+        <v>46114.513448564816</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2323,13 +2323,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.389517766205</v>
+        <v>46065.55618443287</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.346884178245</v>
+        <v>46114.5135508449</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.346898125004</v>
+        <v>46114.51356479166</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2376,13 +2376,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.38951809028</v>
+        <v>46065.55618475695</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.549961875004</v>
+        <v>46107.71662854167</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.549979965275</v>
+        <v>46107.71664663195</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2441,13 +2441,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.3895184375</v>
+        <v>46065.55618510417</v>
       </c>
       <c r="C20" s="5">
-        <v>46107.55000682871</v>
+        <v>46107.71667349537</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.55002149305</v>
+        <v>46107.71668815972</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2506,13 +2506,13 @@
         <v>85</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.38951879629</v>
+        <v>46065.55618546296</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.34686798611</v>
+        <v>46114.51353465278</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.346884375</v>
+        <v>46114.513551041666</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>86</v>
@@ -2571,13 +2571,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.389519131946</v>
+        <v>46065.55618579861</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.55006083334</v>
+        <v>46107.716727499996</v>
       </c>
       <c r="D22" s="5">
-        <v>46107.55007583334</v>
+        <v>46107.7167425</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2636,13 +2636,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.38951710648</v>
+        <v>46065.55618377315</v>
       </c>
       <c r="C23" s="8">
-        <v>46107.55029724537</v>
+        <v>46107.71696391204</v>
       </c>
       <c r="D23" s="8">
-        <v>46107.55031475694</v>
+        <v>46107.71698142361</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2701,13 +2701,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.38951741898</v>
+        <v>46065.55618408565</v>
       </c>
       <c r="C24" s="5">
-        <v>46155.6624807176</v>
+        <v>46155.829147384255</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.66249818287</v>
+        <v>46155.829164849536</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -2754,13 +2754,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.38951790509</v>
+        <v>46065.55618457176</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.62113777778</v>
+        <v>46111.787804444444</v>
       </c>
       <c r="D25" s="8">
-        <v>46111.62113914352</v>
+        <v>46111.787805810185</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2819,13 +2819,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.38951821759</v>
+        <v>46065.55618488426</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.62098633102</v>
+        <v>46111.787652997686</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.62098839121</v>
+        <v>46111.787655057866</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2880,13 +2880,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.38951853009</v>
+        <v>46065.55618519676</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.62103630787</v>
+        <v>46111.787702974536</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.621037777775</v>
+        <v>46111.78770444445</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>110</v>
@@ -2941,13 +2941,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.38951887732</v>
+        <v>46065.55618554398</v>
       </c>
       <c r="C28" s="5">
-        <v>46154.39079186342</v>
+        <v>46154.55745853009</v>
       </c>
       <c r="D28" s="5">
-        <v>46189.00093152778</v>
+        <v>46189.16759819444</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3006,13 +3006,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.389519247685</v>
+        <v>46065.55618591435</v>
       </c>
       <c r="C29" s="8">
-        <v>46129.428751875</v>
+        <v>46129.59541854166</v>
       </c>
       <c r="D29" s="8">
-        <v>46129.428753125</v>
+        <v>46129.595419791665</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3067,13 +3067,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.389519652774</v>
+        <v>46065.556186319445</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.39077186343</v>
+        <v>46154.55743853009</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.390773391206</v>
+        <v>46154.55744005787</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3128,13 +3128,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.389519965276</v>
+        <v>46065.55618663195</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.6213315625</v>
+        <v>46111.78799822916</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.62134431713</v>
+        <v>46111.7880109838</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3193,13 +3193,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.389520625</v>
+        <v>46065.556187291666</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.6212590162</v>
+        <v>46111.787925682875</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.62126035879</v>
+        <v>46111.78792702546</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3254,13 +3254,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.38952170139</v>
+        <v>46065.55618836806</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.62131702546</v>
+        <v>46111.787983692135</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.621318668986</v>
+        <v>46111.78798533565</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3315,13 +3315,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46067.69045797454</v>
+        <v>46067.8571246412</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.62158</v>
+        <v>46111.78824666666</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.621604375</v>
+        <v>46111.78827104167</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3380,13 +3380,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46067.69061002315</v>
+        <v>46067.857276689814</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.62149472222</v>
+        <v>46111.78816138889</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.621495949075</v>
+        <v>46111.78816261574</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3435,13 +3435,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46067.69069710648</v>
+        <v>46067.857363773146</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.621563622684</v>
+        <v>46111.788230289356</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.62156525463</v>
+        <v>46111.788231921295</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3490,13 +3490,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46067.69078010417</v>
+        <v>46067.85744677084</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.621536562496</v>
+        <v>46111.78820322917</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.62153788195</v>
+        <v>46111.78820454861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3545,13 +3545,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.38952369213</v>
+        <v>46065.556190358795</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.621906747685</v>
+        <v>46111.78857341435</v>
       </c>
       <c r="D38" s="5">
-        <v>46135.41441790509</v>
+        <v>46135.581084571764</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3610,13 +3610,13 @@
         <v>147</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.3895240625</v>
+        <v>46065.55619072917</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.622016134264</v>
+        <v>46111.78868280092</v>
       </c>
       <c r="D39" s="8">
-        <v>46114.346894375005</v>
+        <v>46114.51356104166</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>78</v>
@@ -3671,13 +3671,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.389524432874</v>
+        <v>46065.55619109954</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.62209619213</v>
+        <v>46111.78876285879</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.62209752315</v>
+        <v>46111.78876418981</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3732,13 +3732,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.38951626157</v>
+        <v>46065.55618292824</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.630251319446</v>
+        <v>46114.79691798611</v>
       </c>
       <c r="D41" s="8">
-        <v>46114.630264004634</v>
+        <v>46114.79693067129</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3785,13 +3785,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.64314940972</v>
+        <v>46070.80981607639</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.59716626158</v>
+        <v>46114.76383292824</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.597182604164</v>
+        <v>46114.763849270836</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3850,13 +3850,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.38951653935</v>
+        <v>46065.55618320602</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.630152858794</v>
+        <v>46114.796819525465</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.63016990741</v>
+        <v>46114.796836574074</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>161</v>
@@ -3915,13 +3915,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46086.459633136576</v>
+        <v>46086.62629980324</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.63019277778</v>
+        <v>46114.79685944444</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.63020814815</v>
+        <v>46114.79687481481</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -3978,13 +3978,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="8">
-        <v>46086.45999190972</v>
+        <v>46086.62665857639</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.63022989583</v>
+        <v>46114.796896562504</v>
       </c>
       <c r="D45" s="8">
-        <v>46123.013042708335</v>
+        <v>46123.179709375</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>169</v>
@@ -4041,13 +4041,13 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46065.38951681713</v>
+        <v>46065.5561834838</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.550847199076</v>
+        <v>46107.71751386574</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.55086023148</v>
+        <v>46107.71752689815</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4094,13 +4094,13 @@
         <v>175</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.389517083335</v>
+        <v>46065.55618375</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.55074893519</v>
+        <v>46107.71741560185</v>
       </c>
       <c r="D47" s="8">
-        <v>46135.41438908565</v>
+        <v>46135.581055752315</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>176</v>
@@ -4159,13 +4159,13 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46065.38951743055</v>
+        <v>46065.55618409722</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.55083096065</v>
+        <v>46107.717497627316</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.55084773148</v>
+        <v>46107.717514398144</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>181</v>
@@ -4224,13 +4224,13 @@
         <v>185</v>
       </c>
       <c r="B49" s="8">
-        <v>46065.3895194213</v>
+        <v>46065.55618608797</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.55120021991</v>
+        <v>46107.717866886574</v>
       </c>
       <c r="D49" s="8">
-        <v>46135.414471655095</v>
+        <v>46135.58113832176</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>186</v>
@@ -4275,13 +4275,13 @@
         <v>188</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.38952199074</v>
+        <v>46065.55618865741</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.5509347801</v>
+        <v>46107.717601446755</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.55095311343</v>
+        <v>46107.71761978009</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>189</v>
@@ -4340,13 +4340,13 @@
         <v>193</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.389524479164</v>
+        <v>46065.556191145835</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.551059722224</v>
+        <v>46107.71772638889</v>
       </c>
       <c r="D51" s="8">
-        <v>46135.41434469908</v>
+        <v>46135.581011365735</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>194</v>
@@ -4405,13 +4405,13 @@
         <v>197</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.389516446754</v>
+        <v>46065.556183113426</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.55118377315</v>
+        <v>46107.71785043982</v>
       </c>
       <c r="D52" s="5">
-        <v>46135.41444496528</v>
+        <v>46135.581111631946</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>198</v>
@@ -4468,13 +4468,13 @@
         <v>201</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.389516875</v>
+        <v>46065.55618354167</v>
       </c>
       <c r="C53" s="8">
-        <v>46154.3908409838</v>
+        <v>46154.55750765046</v>
       </c>
       <c r="D53" s="8">
-        <v>46154.390852916666</v>
+        <v>46154.55751958334</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>173</v>
@@ -4521,13 +4521,13 @@
         <v>203</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.38951719907</v>
+        <v>46065.556183865745</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.5523522338</v>
+        <v>46107.71901890046</v>
       </c>
       <c r="D54" s="5">
-        <v>46135.414625868056</v>
+        <v>46135.58129253473</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>204</v>
@@ -4584,13 +4584,13 @@
         <v>206</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.389517511576</v>
+        <v>46065.55618417824</v>
       </c>
       <c r="C55" s="8">
-        <v>46107.552395833336</v>
+        <v>46107.7190625</v>
       </c>
       <c r="D55" s="8">
-        <v>46135.41464859954</v>
+        <v>46135.5813152662</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>207</v>
@@ -4647,13 +4647,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.38951784722</v>
+        <v>46065.55618451389</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.55242975694</v>
+        <v>46107.71909642361</v>
       </c>
       <c r="D56" s="5">
-        <v>46135.41467578703</v>
+        <v>46135.581342453705</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4710,13 +4710,13 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.3895181713</v>
+        <v>46065.55618483796</v>
       </c>
       <c r="C57" s="8">
-        <v>46154.39082331018</v>
+        <v>46154.557489976854</v>
       </c>
       <c r="D57" s="8">
-        <v>46189.000931400464</v>
+        <v>46189.16759806713</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>57</v>
@@ -4773,13 +4773,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.389518807875</v>
+        <v>46065.55618547453</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.5519617824</v>
+        <v>46107.718628449074</v>
       </c>
       <c r="D58" s="5">
-        <v>46135.41480413194</v>
+        <v>46135.581470798614</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4822,13 +4822,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.389519108794</v>
+        <v>46065.556185775466</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.55139565972</v>
+        <v>46107.718062326385</v>
       </c>
       <c r="D59" s="8">
-        <v>46115.99319787037</v>
+        <v>46116.15986453704</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4887,13 +4887,13 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.3895194213</v>
+        <v>46065.55618608797</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.55150810185</v>
+        <v>46107.71817476852</v>
       </c>
       <c r="D60" s="5">
-        <v>46135.41579668982</v>
+        <v>46135.58246335648</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4950,13 +4950,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.38951586805</v>
+        <v>46065.556182534725</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.5516275463</v>
+        <v>46107.71829421296</v>
       </c>
       <c r="D61" s="8">
-        <v>46135.414911597225</v>
+        <v>46135.58157826389</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>225</v>
@@ -5013,13 +5013,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.38951627315</v>
+        <v>46065.556182939814</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.55173928241</v>
+        <v>46107.718405949076</v>
       </c>
       <c r="D62" s="5">
-        <v>46135.41491212963</v>
+        <v>46135.58157879629</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5076,13 +5076,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.38951688657</v>
+        <v>46065.55618355324</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.551834872684</v>
+        <v>46107.71850153935</v>
       </c>
       <c r="D63" s="8">
-        <v>46122.01326224537</v>
+        <v>46122.17992891204</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>170</v>
@@ -5139,13 +5139,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.389517187505</v>
+        <v>46065.55618385416</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.551940335645</v>
+        <v>46107.718607002316</v>
       </c>
       <c r="D64" s="5">
-        <v>46135.416054305555</v>
+        <v>46135.58272097222</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5202,13 +5202,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.38951746528</v>
+        <v>46065.55618413194</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.417522372685</v>
+        <v>46197.58418903935</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.41754119213</v>
+        <v>46197.584207858796</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5255,13 +5255,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.389517766205</v>
+        <v>46065.55618443287</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.41750354167</v>
+        <v>46197.584170208334</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.41752289352</v>
+        <v>46197.584189560184</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5318,13 +5318,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.389518055556</v>
+        <v>46065.55618472223</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.33222015046</v>
+        <v>46197.498886817135</v>
       </c>
       <c r="D67" s="8">
-        <v>46199.01033725694</v>
+        <v>46199.177003923614</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5381,13 +5381,13 @@
         <v>249</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.389518344906</v>
+        <v>46065.55618501158</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.415172291665</v>
+        <v>46197.58183895833</v>
       </c>
       <c r="D68" s="5">
-        <v>46203.00547924769</v>
+        <v>46203.17214591435</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>250</v>
@@ -5444,13 +5444,13 @@
         <v>252</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.38951862269</v>
+        <v>46065.55618528935</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.41529104167</v>
+        <v>46197.58195770833</v>
       </c>
       <c r="D69" s="8">
-        <v>46204.01063642361</v>
+        <v>46204.17730309028</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>253</v>
@@ -5507,11 +5507,11 @@
         <v>255</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.38951620371</v>
+        <v>46065.55618287037</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.694466863424</v>
+        <v>46126.861133530096</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>256</v>
@@ -5560,11 +5560,11 @@
         <v>258</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.389516863426</v>
+        <v>46065.55618353009</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46210.00640028935</v>
+        <v>46210.17306695602</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5623,11 +5623,11 @@
         <v>263</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.3895165625</v>
+        <v>46065.55618322917</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46210.00640032407</v>
+        <v>46210.17306699074</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5686,13 +5686,13 @@
         <v>266</v>
       </c>
       <c r="B73" s="8">
-        <v>46086.45525143518</v>
+        <v>46086.62191810185</v>
       </c>
       <c r="C73" s="8">
-        <v>46198.46658064815</v>
+        <v>46198.633247314814</v>
       </c>
       <c r="D73" s="8">
-        <v>46198.466594467594</v>
+        <v>46198.63326113426</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>267</v>
@@ -5739,13 +5739,13 @@
         <v>269</v>
       </c>
       <c r="B74" s="5">
-        <v>46086.455943946756</v>
+        <v>46086.62261061343</v>
       </c>
       <c r="C74" s="5">
-        <v>46198.46651351852</v>
+        <v>46198.633180185185</v>
       </c>
       <c r="D74" s="5">
-        <v>46210.00640107639</v>
+        <v>46210.17306774306</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>270</v>
@@ -5804,13 +5804,13 @@
         <v>272</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.380529780094</v>
+        <v>46090.54719644676</v>
       </c>
       <c r="C75" s="8">
-        <v>46198.46656483796</v>
+        <v>46198.63323150463</v>
       </c>
       <c r="D75" s="8">
-        <v>46198.466662384264</v>
+        <v>46198.63332905092</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -5509,9 +5509,11 @@
       <c r="B70" s="5">
         <v>46065.55618287037</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46213.82998854166</v>
+      </c>
       <c r="D70" s="5">
-        <v>46126.861133530096</v>
+        <v>46213.83000314815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>256</v>
@@ -5546,13 +5548,13 @@
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
       <c r="S70" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="U70" s="10" t="s">
-        <v>108</v>
+      <c r="U70" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5562,9 +5564,11 @@
       <c r="B71" s="8">
         <v>46065.55618353009</v>
       </c>
-      <c r="C71" s="9"/>
+      <c r="C71" s="8">
+        <v>46213.82995895833</v>
+      </c>
       <c r="D71" s="8">
-        <v>46210.17306695602</v>
+        <v>46213.82997866898</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5609,13 +5613,13 @@
         <v>46206</v>
       </c>
       <c r="S71" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="U71" s="12" t="s">
-        <v>47</v>
+      <c r="U71" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5625,9 +5629,11 @@
       <c r="B72" s="5">
         <v>46065.55618322917</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46213.82997023148</v>
+      </c>
       <c r="D72" s="5">
-        <v>46210.17306699074</v>
+        <v>46213.829988680554</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>264</v>
@@ -5672,13 +5678,13 @@
         <v>46206</v>
       </c>
       <c r="S72" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="U72" s="12" t="s">
-        <v>47</v>
+      <c r="U72" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="273">
   <si>
     <t>50001515 - CLIENTE POR DEFINIR</t>
   </si>
@@ -797,9 +797,6 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213242667616399</t>
@@ -5568,7 +5565,7 @@
         <v>46213.82995895833</v>
       </c>
       <c r="D71" s="8">
-        <v>46213.82997866898</v>
+        <v>46218.20642386574</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>259</v>
@@ -5615,8 +5612,8 @@
       <c r="S71" s="9">
         <v>1</v>
       </c>
-      <c r="T71" s="12" t="s">
-        <v>262</v>
+      <c r="T71" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U71" s="11" t="s">
         <v>32</v>
@@ -5624,7 +5621,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B72" s="5">
         <v>46065.55618322917</v>
@@ -5633,10 +5630,10 @@
         <v>46213.82997023148</v>
       </c>
       <c r="D72" s="5">
-        <v>46213.829988680554</v>
+        <v>46218.20642361111</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5666,7 +5663,7 @@
         <v>256</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>256</v>
@@ -5680,8 +5677,8 @@
       <c r="S72" s="6">
         <v>1</v>
       </c>
-      <c r="T72" s="12" t="s">
-        <v>262</v>
+      <c r="T72" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U72" s="11" t="s">
         <v>32</v>
@@ -5689,7 +5686,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B73" s="8">
         <v>46086.62191810185</v>
@@ -5701,7 +5698,7 @@
         <v>46198.63326113426</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5725,7 +5722,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5742,7 +5739,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B74" s="5">
         <v>46086.62261061343</v>
@@ -5751,10 +5748,10 @@
         <v>46198.633180185185</v>
       </c>
       <c r="D74" s="5">
-        <v>46210.17306774306</v>
+        <v>46218.20642375</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5781,13 +5778,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>253</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q74" s="5">
         <v>46217</v>
@@ -5798,8 +5795,8 @@
       <c r="S74" s="6">
         <v>1</v>
       </c>
-      <c r="T74" s="12" t="s">
-        <v>262</v>
+      <c r="T74" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U74" s="11" t="s">
         <v>32</v>
@@ -5807,7 +5804,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B75" s="8">
         <v>46090.54719644676</v>
@@ -5819,7 +5816,7 @@
         <v>46198.63332905092</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5846,13 +5843,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q75" s="8">
         <v>46226</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="270">
   <si>
     <t>50001515 - CLIENTE POR DEFINIR</t>
   </si>
@@ -283,9 +283,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
   </si>
   <si>
@@ -293,12 +290,6 @@
   </si>
   <si>
     <t>propuestas compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>1213242666769870</t>
@@ -2583,11 +2574,9 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="5">
         <v>46062</v>
       </c>
@@ -2610,7 +2599,7 @@
         <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46063</v>
@@ -2630,7 +2619,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46065.55618377315</v>
@@ -2642,17 +2631,15 @@
         <v>46107.71698142361</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>95</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H23" s="9"/>
       <c r="I23" s="8">
         <v>46063</v>
       </c>
@@ -2695,7 +2682,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46065.55618408565</v>
@@ -2707,7 +2694,7 @@
         <v>46155.829164849536</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>25</v>
@@ -2731,7 +2718,7 @@
         <v>26</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2748,7 +2735,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B25" s="8">
         <v>46065.55618457176</v>
@@ -2760,16 +2747,16 @@
         <v>46111.787805810185</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I25" s="8">
         <v>46064</v>
@@ -2787,13 +2774,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Q25" s="8">
         <v>46069</v>
@@ -2813,7 +2800,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>46065.55618488426</v>
@@ -2825,16 +2812,16 @@
         <v>46111.787655057866</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46064</v>
@@ -2852,13 +2839,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2866,15 +2853,15 @@
         <v>0</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B27" s="8">
         <v>46065.55618519676</v>
@@ -2886,16 +2873,16 @@
         <v>46111.78770444445</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I27" s="8">
         <v>46066</v>
@@ -2913,13 +2900,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2927,15 +2914,15 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46065.55618554398</v>
@@ -2947,16 +2934,16 @@
         <v>46189.16759819444</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I28" s="5">
         <v>46129</v>
@@ -2974,13 +2961,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Q28" s="5">
         <v>46188</v>
@@ -3000,7 +2987,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B29" s="8">
         <v>46065.55618591435</v>
@@ -3012,16 +2999,16 @@
         <v>46129.595419791665</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I29" s="8">
         <v>46129</v>
@@ -3039,13 +3026,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3053,15 +3040,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46065.556186319445</v>
@@ -3073,16 +3060,16 @@
         <v>46154.55744005787</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46141</v>
@@ -3100,13 +3087,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="O30" s="6" t="s">
-        <v>116</v>
-      </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3114,15 +3101,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46065.55618663195</v>
@@ -3134,16 +3121,16 @@
         <v>46111.7880109838</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I31" s="8">
         <v>46064</v>
@@ -3161,13 +3148,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Q31" s="8">
         <v>46084</v>
@@ -3187,7 +3174,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46065.556187291666</v>
@@ -3199,16 +3186,16 @@
         <v>46111.78792702546</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I32" s="5">
         <v>46064</v>
@@ -3226,13 +3213,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3240,15 +3227,15 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B33" s="8">
         <v>46065.55618836806</v>
@@ -3260,16 +3247,16 @@
         <v>46111.78798533565</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I33" s="8">
         <v>46065</v>
@@ -3287,13 +3274,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="O33" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="O33" s="9" t="s">
-        <v>125</v>
-      </c>
       <c r="P33" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3301,15 +3288,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46067.8571246412</v>
@@ -3321,16 +3308,16 @@
         <v>46111.78827104167</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I34" s="5">
         <v>46064</v>
@@ -3348,10 +3335,10 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3374,7 +3361,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46067.857276689814</v>
@@ -3386,16 +3373,16 @@
         <v>46111.78816261574</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I35" s="8">
         <v>46064</v>
@@ -3413,13 +3400,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3429,7 +3416,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46067.857363773146</v>
@@ -3441,16 +3428,16 @@
         <v>46111.788231921295</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I36" s="5">
         <v>46073</v>
@@ -3468,13 +3455,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="O36" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="O36" s="6" t="s">
-        <v>134</v>
-      </c>
       <c r="P36" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3484,7 +3471,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B37" s="8">
         <v>46067.85744677084</v>
@@ -3496,16 +3483,16 @@
         <v>46111.78820454861</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I37" s="8">
         <v>46073</v>
@@ -3523,13 +3510,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="O37" s="9" t="s">
-        <v>134</v>
-      </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3539,7 +3526,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46065.556190358795</v>
@@ -3551,16 +3538,16 @@
         <v>46135.581084571764</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I38" s="5">
         <v>46065</v>
@@ -3578,13 +3565,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Q38" s="5">
         <v>46091</v>
@@ -3604,7 +3591,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46065.55619072917</v>
@@ -3622,10 +3609,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I39" s="8">
         <v>46065</v>
@@ -3643,13 +3630,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>76</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3657,15 +3644,15 @@
         <v>0</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46065.55619109954</v>
@@ -3677,16 +3664,16 @@
         <v>46111.78876418981</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I40" s="5">
         <v>46076</v>
@@ -3704,13 +3691,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3718,15 +3705,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46065.55618292824</v>
@@ -3738,7 +3725,7 @@
         <v>46114.79693067129</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>25</v>
@@ -3762,7 +3749,7 @@
         <v>26</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -3779,7 +3766,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46070.80981607639</v>
@@ -3791,16 +3778,16 @@
         <v>46114.763849270836</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I42" s="5">
         <v>46063</v>
@@ -3818,13 +3805,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="5">
         <v>46069</v>
@@ -3844,7 +3831,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46065.55618320602</v>
@@ -3856,16 +3843,16 @@
         <v>46114.796836574074</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I43" s="8">
         <v>46084</v>
@@ -3883,13 +3870,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="8">
         <v>46090</v>
@@ -3909,7 +3896,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46086.62629980324</v>
@@ -3921,16 +3908,16 @@
         <v>46114.79687481481</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -3946,13 +3933,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="5">
         <v>46091</v>
@@ -3972,7 +3959,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46086.62665857639</v>
@@ -3984,16 +3971,16 @@
         <v>46123.179709375</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4009,13 +3996,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="8">
         <v>46122</v>
@@ -4035,7 +4022,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46065.5561834838</v>
@@ -4047,7 +4034,7 @@
         <v>46107.71752689815</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4071,7 +4058,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4088,7 +4075,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46065.55618375</v>
@@ -4100,16 +4087,16 @@
         <v>46135.581055752315</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46092</v>
@@ -4127,13 +4114,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="8">
         <v>46093</v>
@@ -4153,7 +4140,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46065.55618409722</v>
@@ -4165,16 +4152,16 @@
         <v>46107.717514398144</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I48" s="5">
         <v>46094</v>
@@ -4192,13 +4179,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="O48" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="O48" s="6" t="s">
-        <v>176</v>
-      </c>
       <c r="P48" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46097</v>
@@ -4218,7 +4205,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B49" s="8">
         <v>46065.55618608797</v>
@@ -4230,7 +4217,7 @@
         <v>46135.58113832176</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>25</v>
@@ -4254,7 +4241,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4269,7 +4256,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46065.55618865741</v>
@@ -4281,16 +4268,16 @@
         <v>46107.71761978009</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46098</v>
@@ -4308,13 +4295,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q50" s="5">
         <v>46100</v>
@@ -4334,7 +4321,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B51" s="8">
         <v>46065.556191145835</v>
@@ -4346,16 +4333,16 @@
         <v>46135.581011365735</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I51" s="8">
         <v>46101</v>
@@ -4373,13 +4360,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="8">
         <v>46107</v>
@@ -4399,7 +4386,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46065.556183113426</v>
@@ -4411,16 +4398,16 @@
         <v>46135.581111631946</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4436,13 +4423,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q52" s="5">
         <v>46108</v>
@@ -4462,7 +4449,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B53" s="8">
         <v>46065.55618354167</v>
@@ -4474,7 +4461,7 @@
         <v>46154.55751958334</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4498,7 +4485,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4515,7 +4502,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46065.556183865745</v>
@@ -4527,16 +4514,16 @@
         <v>46135.58129253473</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4552,13 +4539,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46070</v>
@@ -4578,7 +4565,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B55" s="8">
         <v>46065.55618417824</v>
@@ -4590,16 +4577,16 @@
         <v>46135.5813152662</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4615,13 +4602,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Q55" s="8">
         <v>46086</v>
@@ -4641,7 +4628,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46065.55618451389</v>
@@ -4653,16 +4640,16 @@
         <v>46135.581342453705</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -4678,13 +4665,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4704,7 +4691,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B57" s="8">
         <v>46065.55618483796</v>
@@ -4722,10 +4709,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -4741,13 +4728,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q57" s="8">
         <v>46188</v>
@@ -4767,7 +4754,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B58" s="5">
         <v>46065.55618547453</v>
@@ -4779,7 +4766,7 @@
         <v>46135.581470798614</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4803,7 +4790,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4816,7 +4803,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B59" s="8">
         <v>46065.556185775466</v>
@@ -4828,17 +4815,15 @@
         <v>46116.15986453704</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H59" s="9"/>
       <c r="I59" s="8">
         <v>46111</v>
       </c>
@@ -4855,13 +4840,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q59" s="8">
         <v>46115</v>
@@ -4881,7 +4866,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46065.55618608797</v>
@@ -4893,17 +4878,15 @@
         <v>46135.58246335648</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H60" s="6"/>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
         <v>46119</v>
@@ -4918,13 +4901,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q60" s="5">
         <v>46119</v>
@@ -4944,7 +4927,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B61" s="8">
         <v>46065.556182534725</v>
@@ -4956,17 +4939,15 @@
         <v>46135.58157826389</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H61" s="9"/>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
         <v>46119</v>
@@ -4981,13 +4962,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="8">
         <v>46119</v>
@@ -5007,7 +4988,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46065.556182939814</v>
@@ -5019,17 +5000,15 @@
         <v>46135.58157879629</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H62" s="6"/>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
         <v>46120</v>
@@ -5044,13 +5023,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q62" s="5">
         <v>46120</v>
@@ -5070,7 +5049,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B63" s="8">
         <v>46065.55618355324</v>
@@ -5082,17 +5061,15 @@
         <v>46122.17992891204</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H63" s="9"/>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
         <v>46121</v>
@@ -5107,13 +5084,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q63" s="8">
         <v>46121</v>
@@ -5133,7 +5110,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
         <v>46065.55618385416</v>
@@ -5145,17 +5122,15 @@
         <v>46135.58272097222</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H64" s="6"/>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
         <v>46125</v>
@@ -5170,13 +5145,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q64" s="5">
         <v>46125</v>
@@ -5196,7 +5171,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B65" s="8">
         <v>46065.55618413194</v>
@@ -5208,7 +5183,7 @@
         <v>46197.584207858796</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5232,7 +5207,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5249,7 +5224,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B66" s="5">
         <v>46065.55618443287</v>
@@ -5261,16 +5236,16 @@
         <v>46197.584189560184</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5286,13 +5261,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Q66" s="5">
         <v>46191</v>
@@ -5312,7 +5287,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B67" s="8">
         <v>46065.55618472223</v>
@@ -5324,17 +5299,15 @@
         <v>46199.177003923614</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H67" s="9"/>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
         <v>46198</v>
@@ -5349,13 +5322,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q67" s="8">
         <v>46198</v>
@@ -5375,7 +5348,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B68" s="5">
         <v>46065.55618501158</v>
@@ -5387,16 +5360,16 @@
         <v>46203.17214591435</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5412,13 +5385,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q68" s="5">
         <v>46202</v>
@@ -5438,7 +5411,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B69" s="8">
         <v>46065.55618528935</v>
@@ -5450,16 +5423,16 @@
         <v>46204.17730309028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5475,13 +5448,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="Q69" s="8">
         <v>46203</v>
@@ -5501,7 +5474,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B70" s="5">
         <v>46065.55618287037</v>
@@ -5513,7 +5486,7 @@
         <v>46213.83000314815</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5537,7 +5510,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5548,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="T70" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U70" s="11" t="s">
         <v>32</v>
@@ -5556,7 +5529,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B71" s="8">
         <v>46065.55618353009</v>
@@ -5568,16 +5541,16 @@
         <v>46218.20642386574</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I71" s="8">
         <v>46206</v>
@@ -5595,13 +5568,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O71" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>253</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>256</v>
       </c>
       <c r="Q71" s="8">
         <v>46217</v>
@@ -5621,7 +5594,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B72" s="5">
         <v>46065.55618322917</v>
@@ -5633,16 +5606,16 @@
         <v>46218.20642361111</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I72" s="5">
         <v>46206</v>
@@ -5660,13 +5633,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="Q72" s="5">
         <v>46217</v>
@@ -5686,7 +5659,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B73" s="8">
         <v>46086.62191810185</v>
@@ -5698,7 +5671,7 @@
         <v>46198.63326113426</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5722,7 +5695,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5739,7 +5712,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B74" s="5">
         <v>46086.62261061343</v>
@@ -5751,7 +5724,7 @@
         <v>46218.20642375</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5778,13 +5751,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q74" s="5">
         <v>46217</v>
@@ -5804,7 +5777,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B75" s="8">
         <v>46090.54719644676</v>
@@ -5816,7 +5789,7 @@
         <v>46198.63332905092</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5843,13 +5816,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="O75" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="O75" s="9" t="s">
-        <v>269</v>
-      </c>
       <c r="P75" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q75" s="8">
         <v>46226</v>
@@ -5861,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="T75" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U75" s="11" t="s">
         <v>32</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="271">
   <si>
     <t>50001515 - CLIENTE POR DEFINIR</t>
   </si>
@@ -821,6 +821,9 @@
   </si>
   <si>
     <t>Pruebas de instalación componentes</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
 </sst>
 </file>
@@ -5786,7 +5789,7 @@
         <v>46198.63323150463</v>
       </c>
       <c r="D75" s="8">
-        <v>46198.63332905092</v>
+        <v>46219.18163760417</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>269</v>
@@ -5833,8 +5836,8 @@
       <c r="S75" s="9">
         <v>1</v>
       </c>
-      <c r="T75" s="11" t="s">
-        <v>104</v>
+      <c r="T75" s="12" t="s">
+        <v>270</v>
       </c>
       <c r="U75" s="11" t="s">
         <v>32</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -2320,7 +2320,7 @@
         <v>46114.5135508449</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.51356479166</v>
+        <v>46220.87441708334</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2694,7 +2694,7 @@
         <v>46155.829147384255</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.829164849536</v>
+        <v>46220.86329395833</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -2320,7 +2320,7 @@
         <v>46114.5135508449</v>
       </c>
       <c r="D18" s="5">
-        <v>46220.87441708334</v>
+        <v>46220.90209800926</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -2320,7 +2320,7 @@
         <v>46114.5135508449</v>
       </c>
       <c r="D18" s="5">
-        <v>46220.90209800926</v>
+        <v>46221.64357028935</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="272">
   <si>
     <t>50001515 - CLIENTE POR DEFINIR</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
@@ -2568,7 +2571,7 @@
         <v>46107.716727499996</v>
       </c>
       <c r="D22" s="5">
-        <v>46107.7167425</v>
+        <v>46223.80659853009</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2577,9 +2580,11 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I22" s="5">
         <v>46062</v>
       </c>
@@ -2602,7 +2607,7 @@
         <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46063</v>
@@ -2622,7 +2627,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46065.55618377315</v>
@@ -2631,18 +2636,20 @@
         <v>46107.71696391204</v>
       </c>
       <c r="D23" s="8">
-        <v>46107.71698142361</v>
+        <v>46223.80659251157</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I23" s="8">
         <v>46063</v>
       </c>
@@ -2685,7 +2692,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46065.55618408565</v>
@@ -2697,7 +2704,7 @@
         <v>46220.86329395833</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>25</v>
@@ -2721,7 +2728,7 @@
         <v>26</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2738,7 +2745,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" s="8">
         <v>46065.55618457176</v>
@@ -2750,16 +2757,16 @@
         <v>46111.787805810185</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I25" s="8">
         <v>46064</v>
@@ -2777,13 +2784,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="8">
         <v>46069</v>
@@ -2803,7 +2810,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46065.55618488426</v>
@@ -2815,16 +2822,16 @@
         <v>46111.787655057866</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I26" s="5">
         <v>46064</v>
@@ -2842,13 +2849,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2856,15 +2863,15 @@
         <v>0</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="8">
         <v>46065.55618519676</v>
@@ -2876,16 +2883,16 @@
         <v>46111.78770444445</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I27" s="8">
         <v>46066</v>
@@ -2903,13 +2910,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2917,15 +2924,15 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46065.55618554398</v>
@@ -2937,16 +2944,16 @@
         <v>46189.16759819444</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I28" s="5">
         <v>46129</v>
@@ -2964,13 +2971,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q28" s="5">
         <v>46188</v>
@@ -2990,7 +2997,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46065.55618591435</v>
@@ -3002,16 +3009,16 @@
         <v>46129.595419791665</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I29" s="8">
         <v>46129</v>
@@ -3029,13 +3036,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3043,15 +3050,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46065.556186319445</v>
@@ -3063,16 +3070,16 @@
         <v>46154.55744005787</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I30" s="5">
         <v>46141</v>
@@ -3090,13 +3097,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3104,15 +3111,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46065.55618663195</v>
@@ -3124,16 +3131,16 @@
         <v>46111.7880109838</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I31" s="8">
         <v>46064</v>
@@ -3151,13 +3158,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q31" s="8">
         <v>46084</v>
@@ -3177,7 +3184,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46065.556187291666</v>
@@ -3189,16 +3196,16 @@
         <v>46111.78792702546</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I32" s="5">
         <v>46064</v>
@@ -3216,13 +3223,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3230,15 +3237,15 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46065.55618836806</v>
@@ -3250,16 +3257,16 @@
         <v>46111.78798533565</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I33" s="8">
         <v>46065</v>
@@ -3277,13 +3284,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3291,15 +3298,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46067.8571246412</v>
@@ -3311,16 +3318,16 @@
         <v>46111.78827104167</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I34" s="5">
         <v>46064</v>
@@ -3338,10 +3345,10 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3364,7 +3371,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46067.857276689814</v>
@@ -3376,16 +3383,16 @@
         <v>46111.78816261574</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I35" s="8">
         <v>46064</v>
@@ -3403,13 +3410,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3419,7 +3426,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46067.857363773146</v>
@@ -3431,16 +3438,16 @@
         <v>46111.788231921295</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I36" s="5">
         <v>46073</v>
@@ -3458,13 +3465,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3474,7 +3481,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46067.85744677084</v>
@@ -3486,16 +3493,16 @@
         <v>46111.78820454861</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I37" s="8">
         <v>46073</v>
@@ -3513,13 +3520,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3529,7 +3536,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46065.556190358795</v>
@@ -3541,16 +3548,16 @@
         <v>46135.581084571764</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I38" s="5">
         <v>46065</v>
@@ -3568,13 +3575,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q38" s="5">
         <v>46091</v>
@@ -3594,7 +3601,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46065.55619072917</v>
@@ -3612,10 +3619,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I39" s="8">
         <v>46065</v>
@@ -3633,13 +3640,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>76</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3647,15 +3654,15 @@
         <v>0</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46065.55619109954</v>
@@ -3667,16 +3674,16 @@
         <v>46111.78876418981</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I40" s="5">
         <v>46076</v>
@@ -3694,13 +3701,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3708,15 +3715,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46065.55618292824</v>
@@ -3728,7 +3735,7 @@
         <v>46114.79693067129</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>25</v>
@@ -3752,7 +3759,7 @@
         <v>26</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -3769,7 +3776,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46070.80981607639</v>
@@ -3781,16 +3788,16 @@
         <v>46114.763849270836</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I42" s="5">
         <v>46063</v>
@@ -3808,13 +3815,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="5">
         <v>46069</v>
@@ -3834,7 +3841,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46065.55618320602</v>
@@ -3846,16 +3853,16 @@
         <v>46114.796836574074</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I43" s="8">
         <v>46084</v>
@@ -3873,13 +3880,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q43" s="8">
         <v>46090</v>
@@ -3899,7 +3906,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46086.62629980324</v>
@@ -3911,16 +3918,16 @@
         <v>46114.79687481481</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -3936,13 +3943,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="5">
         <v>46091</v>
@@ -3962,7 +3969,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46086.62665857639</v>
@@ -3974,16 +3981,16 @@
         <v>46123.179709375</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -3999,13 +4006,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="8">
         <v>46122</v>
@@ -4025,7 +4032,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46065.5561834838</v>
@@ -4037,7 +4044,7 @@
         <v>46107.71752689815</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4061,7 +4068,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4078,7 +4085,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B47" s="8">
         <v>46065.55618375</v>
@@ -4090,16 +4097,16 @@
         <v>46135.581055752315</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I47" s="8">
         <v>46092</v>
@@ -4117,13 +4124,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q47" s="8">
         <v>46093</v>
@@ -4143,7 +4150,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46065.55618409722</v>
@@ -4155,16 +4162,16 @@
         <v>46107.717514398144</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I48" s="5">
         <v>46094</v>
@@ -4182,13 +4189,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="5">
         <v>46097</v>
@@ -4208,7 +4215,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="8">
         <v>46065.55618608797</v>
@@ -4220,7 +4227,7 @@
         <v>46135.58113832176</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>25</v>
@@ -4244,7 +4251,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4259,7 +4266,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46065.55618865741</v>
@@ -4271,16 +4278,16 @@
         <v>46107.71761978009</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I50" s="5">
         <v>46098</v>
@@ -4298,13 +4305,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q50" s="5">
         <v>46100</v>
@@ -4324,7 +4331,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="8">
         <v>46065.556191145835</v>
@@ -4336,16 +4343,16 @@
         <v>46135.581011365735</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I51" s="8">
         <v>46101</v>
@@ -4363,13 +4370,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q51" s="8">
         <v>46107</v>
@@ -4389,7 +4396,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B52" s="5">
         <v>46065.556183113426</v>
@@ -4401,16 +4408,16 @@
         <v>46135.581111631946</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4426,13 +4433,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q52" s="5">
         <v>46108</v>
@@ -4452,7 +4459,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B53" s="8">
         <v>46065.55618354167</v>
@@ -4464,7 +4471,7 @@
         <v>46154.55751958334</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4488,7 +4495,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4505,7 +4512,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B54" s="5">
         <v>46065.556183865745</v>
@@ -4517,16 +4524,16 @@
         <v>46135.58129253473</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4542,13 +4549,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="5">
         <v>46070</v>
@@ -4568,7 +4575,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B55" s="8">
         <v>46065.55618417824</v>
@@ -4580,16 +4587,16 @@
         <v>46135.5813152662</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4605,13 +4612,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q55" s="8">
         <v>46086</v>
@@ -4631,7 +4638,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46065.55618451389</v>
@@ -4643,16 +4650,16 @@
         <v>46135.581342453705</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -4668,13 +4675,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4694,7 +4701,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B57" s="8">
         <v>46065.55618483796</v>
@@ -4712,10 +4719,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -4731,13 +4738,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q57" s="8">
         <v>46188</v>
@@ -4757,7 +4764,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46065.55618547453</v>
@@ -4769,7 +4776,7 @@
         <v>46135.581470798614</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4793,7 +4800,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4806,7 +4813,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B59" s="8">
         <v>46065.556185775466</v>
@@ -4815,18 +4822,20 @@
         <v>46107.718062326385</v>
       </c>
       <c r="D59" s="8">
-        <v>46116.15986453704</v>
+        <v>46223.8067166088</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I59" s="8">
         <v>46111</v>
       </c>
@@ -4843,13 +4852,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q59" s="8">
         <v>46115</v>
@@ -4869,7 +4878,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
         <v>46065.55618608797</v>
@@ -4878,18 +4887,20 @@
         <v>46107.71817476852</v>
       </c>
       <c r="D60" s="5">
-        <v>46135.58246335648</v>
+        <v>46223.80671290509</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
         <v>46119</v>
@@ -4904,13 +4915,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q60" s="5">
         <v>46119</v>
@@ -4930,7 +4941,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="8">
         <v>46065.556182534725</v>
@@ -4939,18 +4950,20 @@
         <v>46107.71829421296</v>
       </c>
       <c r="D61" s="8">
-        <v>46135.58157826389</v>
+        <v>46223.80670902778</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H61" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
         <v>46119</v>
@@ -4965,13 +4978,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q61" s="8">
         <v>46119</v>
@@ -4991,7 +5004,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46065.556182939814</v>
@@ -5000,18 +5013,20 @@
         <v>46107.718405949076</v>
       </c>
       <c r="D62" s="5">
-        <v>46135.58157879629</v>
+        <v>46223.80670523148</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
         <v>46120</v>
@@ -5026,13 +5041,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q62" s="5">
         <v>46120</v>
@@ -5052,7 +5067,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B63" s="8">
         <v>46065.55618355324</v>
@@ -5061,18 +5076,20 @@
         <v>46107.71850153935</v>
       </c>
       <c r="D63" s="8">
-        <v>46122.17992891204</v>
+        <v>46223.80670148148</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
         <v>46121</v>
@@ -5087,13 +5104,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q63" s="8">
         <v>46121</v>
@@ -5113,7 +5130,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
         <v>46065.55618385416</v>
@@ -5122,18 +5139,20 @@
         <v>46107.718607002316</v>
       </c>
       <c r="D64" s="5">
-        <v>46135.58272097222</v>
+        <v>46223.80669592593</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
         <v>46125</v>
@@ -5148,13 +5167,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="5">
         <v>46125</v>
@@ -5174,7 +5193,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B65" s="8">
         <v>46065.55618413194</v>
@@ -5186,7 +5205,7 @@
         <v>46197.584207858796</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5210,7 +5229,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5227,7 +5246,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B66" s="5">
         <v>46065.55618443287</v>
@@ -5239,16 +5258,16 @@
         <v>46197.584189560184</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5264,13 +5283,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q66" s="5">
         <v>46191</v>
@@ -5290,7 +5309,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B67" s="8">
         <v>46065.55618472223</v>
@@ -5302,7 +5321,7 @@
         <v>46199.177003923614</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5325,13 +5344,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q67" s="8">
         <v>46198</v>
@@ -5351,7 +5370,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B68" s="5">
         <v>46065.55618501158</v>
@@ -5363,16 +5382,16 @@
         <v>46203.17214591435</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5388,13 +5407,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q68" s="5">
         <v>46202</v>
@@ -5414,7 +5433,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B69" s="8">
         <v>46065.55618528935</v>
@@ -5426,16 +5445,16 @@
         <v>46204.17730309028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5451,13 +5470,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q69" s="8">
         <v>46203</v>
@@ -5477,7 +5496,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B70" s="5">
         <v>46065.55618287037</v>
@@ -5489,7 +5508,7 @@
         <v>46213.83000314815</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5513,7 +5532,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5524,7 +5543,7 @@
         <v>1</v>
       </c>
       <c r="T70" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U70" s="11" t="s">
         <v>32</v>
@@ -5532,7 +5551,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B71" s="8">
         <v>46065.55618353009</v>
@@ -5544,16 +5563,16 @@
         <v>46218.20642386574</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I71" s="8">
         <v>46206</v>
@@ -5571,13 +5590,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q71" s="8">
         <v>46217</v>
@@ -5597,7 +5616,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B72" s="5">
         <v>46065.55618322917</v>
@@ -5609,16 +5628,16 @@
         <v>46218.20642361111</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I72" s="5">
         <v>46206</v>
@@ -5636,13 +5655,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q72" s="5">
         <v>46217</v>
@@ -5662,7 +5681,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B73" s="8">
         <v>46086.62191810185</v>
@@ -5674,7 +5693,7 @@
         <v>46198.63326113426</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5698,7 +5717,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5715,7 +5734,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B74" s="5">
         <v>46086.62261061343</v>
@@ -5727,7 +5746,7 @@
         <v>46218.20642375</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5754,13 +5773,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q74" s="5">
         <v>46217</v>
@@ -5780,7 +5799,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B75" s="8">
         <v>46090.54719644676</v>
@@ -5792,7 +5811,7 @@
         <v>46219.18163760417</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5819,13 +5838,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q75" s="8">
         <v>46226</v>
@@ -5837,7 +5856,7 @@
         <v>1</v>
       </c>
       <c r="T75" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="U75" s="11" t="s">
         <v>32</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="272">
   <si>
     <t>50001515 - CLIENTE POR DEFINIR</t>
   </si>
@@ -5318,7 +5318,7 @@
         <v>46197.498886817135</v>
       </c>
       <c r="D67" s="8">
-        <v>46199.177003923614</v>
+        <v>46223.835604803244</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5327,9 +5327,11 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
         <v>46198</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="273">
   <si>
     <t>50001515 - CLIENTE POR DEFINIR</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2583,7 +2586,7 @@
         <v>90</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I22" s="5">
         <v>46062</v>
@@ -2607,7 +2610,7 @@
         <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q22" s="5">
         <v>46063</v>
@@ -2627,7 +2630,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="8">
         <v>46065.55618377315</v>
@@ -2639,7 +2642,7 @@
         <v>46223.80659251157</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2648,7 +2651,7 @@
         <v>90</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I23" s="8">
         <v>46063</v>
@@ -2692,7 +2695,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46065.55618408565</v>
@@ -2704,7 +2707,7 @@
         <v>46220.86329395833</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>25</v>
@@ -2728,7 +2731,7 @@
         <v>26</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2745,7 +2748,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" s="8">
         <v>46065.55618457176</v>
@@ -2757,16 +2760,16 @@
         <v>46111.787805810185</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I25" s="8">
         <v>46064</v>
@@ -2784,13 +2787,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q25" s="8">
         <v>46069</v>
@@ -2810,7 +2813,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46065.55618488426</v>
@@ -2822,16 +2825,16 @@
         <v>46111.787655057866</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I26" s="5">
         <v>46064</v>
@@ -2849,13 +2852,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2863,15 +2866,15 @@
         <v>0</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8">
         <v>46065.55618519676</v>
@@ -2883,16 +2886,16 @@
         <v>46111.78770444445</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I27" s="8">
         <v>46066</v>
@@ -2910,13 +2913,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2924,15 +2927,15 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46065.55618554398</v>
@@ -2944,16 +2947,16 @@
         <v>46189.16759819444</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I28" s="5">
         <v>46129</v>
@@ -2971,13 +2974,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q28" s="5">
         <v>46188</v>
@@ -2997,7 +3000,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46065.55618591435</v>
@@ -3009,16 +3012,16 @@
         <v>46129.595419791665</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I29" s="8">
         <v>46129</v>
@@ -3036,13 +3039,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3050,15 +3053,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46065.556186319445</v>
@@ -3070,16 +3073,16 @@
         <v>46154.55744005787</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I30" s="5">
         <v>46141</v>
@@ -3097,13 +3100,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3111,15 +3114,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46065.55618663195</v>
@@ -3131,16 +3134,16 @@
         <v>46111.7880109838</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I31" s="8">
         <v>46064</v>
@@ -3158,13 +3161,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q31" s="8">
         <v>46084</v>
@@ -3184,7 +3187,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46065.556187291666</v>
@@ -3196,16 +3199,16 @@
         <v>46111.78792702546</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I32" s="5">
         <v>46064</v>
@@ -3223,13 +3226,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3237,15 +3240,15 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46065.55618836806</v>
@@ -3257,16 +3260,16 @@
         <v>46111.78798533565</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I33" s="8">
         <v>46065</v>
@@ -3284,13 +3287,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3298,15 +3301,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46067.8571246412</v>
@@ -3318,16 +3321,16 @@
         <v>46111.78827104167</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I34" s="5">
         <v>46064</v>
@@ -3345,10 +3348,10 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>26</v>
@@ -3371,7 +3374,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46067.857276689814</v>
@@ -3383,16 +3386,16 @@
         <v>46111.78816261574</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I35" s="8">
         <v>46064</v>
@@ -3410,13 +3413,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3426,7 +3429,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46067.857363773146</v>
@@ -3438,16 +3441,16 @@
         <v>46111.788231921295</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I36" s="5">
         <v>46073</v>
@@ -3465,13 +3468,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3481,7 +3484,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46067.85744677084</v>
@@ -3493,16 +3496,16 @@
         <v>46111.78820454861</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I37" s="8">
         <v>46073</v>
@@ -3520,13 +3523,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3536,7 +3539,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46065.556190358795</v>
@@ -3548,16 +3551,16 @@
         <v>46135.581084571764</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I38" s="5">
         <v>46065</v>
@@ -3575,13 +3578,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q38" s="5">
         <v>46091</v>
@@ -3601,7 +3604,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46065.55619072917</v>
@@ -3619,10 +3622,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I39" s="8">
         <v>46065</v>
@@ -3640,13 +3643,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>76</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3654,15 +3657,15 @@
         <v>0</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46065.55619109954</v>
@@ -3674,16 +3677,16 @@
         <v>46111.78876418981</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I40" s="5">
         <v>46076</v>
@@ -3701,13 +3704,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3715,15 +3718,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46065.55618292824</v>
@@ -3735,7 +3738,7 @@
         <v>46114.79693067129</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>25</v>
@@ -3759,7 +3762,7 @@
         <v>26</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -3776,7 +3779,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46070.80981607639</v>
@@ -3788,16 +3791,16 @@
         <v>46114.763849270836</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46063</v>
@@ -3815,13 +3818,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="5">
         <v>46069</v>
@@ -3841,7 +3844,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46065.55618320602</v>
@@ -3853,16 +3856,16 @@
         <v>46114.796836574074</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I43" s="8">
         <v>46084</v>
@@ -3880,13 +3883,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q43" s="8">
         <v>46090</v>
@@ -3906,7 +3909,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46086.62629980324</v>
@@ -3918,16 +3921,16 @@
         <v>46114.79687481481</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="5">
@@ -3943,13 +3946,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="5">
         <v>46091</v>
@@ -3969,7 +3972,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="8">
         <v>46086.62665857639</v>
@@ -3981,16 +3984,16 @@
         <v>46123.179709375</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4006,13 +4009,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="8">
         <v>46122</v>
@@ -4032,7 +4035,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46065.5561834838</v>
@@ -4044,7 +4047,7 @@
         <v>46107.71752689815</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4068,7 +4071,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4085,7 +4088,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B47" s="8">
         <v>46065.55618375</v>
@@ -4097,16 +4100,16 @@
         <v>46135.581055752315</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I47" s="8">
         <v>46092</v>
@@ -4124,13 +4127,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="8">
         <v>46093</v>
@@ -4150,7 +4153,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46065.55618409722</v>
@@ -4162,16 +4165,16 @@
         <v>46107.717514398144</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I48" s="5">
         <v>46094</v>
@@ -4189,13 +4192,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q48" s="5">
         <v>46097</v>
@@ -4215,7 +4218,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B49" s="8">
         <v>46065.55618608797</v>
@@ -4227,7 +4230,7 @@
         <v>46135.58113832176</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>25</v>
@@ -4251,7 +4254,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4266,7 +4269,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46065.55618865741</v>
@@ -4278,16 +4281,16 @@
         <v>46107.71761978009</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I50" s="5">
         <v>46098</v>
@@ -4305,13 +4308,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q50" s="5">
         <v>46100</v>
@@ -4331,7 +4334,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B51" s="8">
         <v>46065.556191145835</v>
@@ -4343,16 +4346,16 @@
         <v>46135.581011365735</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I51" s="8">
         <v>46101</v>
@@ -4370,13 +4373,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q51" s="8">
         <v>46107</v>
@@ -4396,7 +4399,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B52" s="5">
         <v>46065.556183113426</v>
@@ -4408,16 +4411,16 @@
         <v>46135.581111631946</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4433,13 +4436,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q52" s="5">
         <v>46108</v>
@@ -4459,7 +4462,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B53" s="8">
         <v>46065.55618354167</v>
@@ -4471,7 +4474,7 @@
         <v>46154.55751958334</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4495,7 +4498,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4512,7 +4515,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B54" s="5">
         <v>46065.556183865745</v>
@@ -4524,16 +4527,16 @@
         <v>46135.58129253473</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4549,13 +4552,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46070</v>
@@ -4575,7 +4578,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B55" s="8">
         <v>46065.55618417824</v>
@@ -4587,16 +4590,16 @@
         <v>46135.5813152662</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4612,13 +4615,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="8">
         <v>46086</v>
@@ -4638,7 +4641,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46065.55618451389</v>
@@ -4650,16 +4653,16 @@
         <v>46135.581342453705</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -4675,13 +4678,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4701,7 +4704,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46065.55618483796</v>
@@ -4719,10 +4722,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -4738,13 +4741,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="8">
         <v>46188</v>
@@ -4764,7 +4767,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46065.55618547453</v>
@@ -4776,7 +4779,7 @@
         <v>46135.581470798614</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4800,7 +4803,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4813,7 +4816,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B59" s="8">
         <v>46065.556185775466</v>
@@ -4825,7 +4828,7 @@
         <v>46223.8067166088</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -4834,7 +4837,7 @@
         <v>90</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I59" s="8">
         <v>46111</v>
@@ -4852,13 +4855,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q59" s="8">
         <v>46115</v>
@@ -4878,7 +4881,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46065.55618608797</v>
@@ -4890,7 +4893,7 @@
         <v>46223.80671290509</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4899,7 +4902,7 @@
         <v>90</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -4915,13 +4918,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q60" s="5">
         <v>46119</v>
@@ -4941,7 +4944,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
         <v>46065.556182534725</v>
@@ -4953,7 +4956,7 @@
         <v>46223.80670902778</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -4962,7 +4965,7 @@
         <v>90</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -4978,13 +4981,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="8">
         <v>46119</v>
@@ -5004,7 +5007,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46065.556182939814</v>
@@ -5016,7 +5019,7 @@
         <v>46223.80670523148</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5025,7 +5028,7 @@
         <v>90</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5041,13 +5044,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q62" s="5">
         <v>46120</v>
@@ -5067,7 +5070,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B63" s="8">
         <v>46065.55618355324</v>
@@ -5079,7 +5082,7 @@
         <v>46223.80670148148</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5088,7 +5091,7 @@
         <v>90</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5104,13 +5107,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q63" s="8">
         <v>46121</v>
@@ -5130,7 +5133,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B64" s="5">
         <v>46065.55618385416</v>
@@ -5142,7 +5145,7 @@
         <v>46223.80669592593</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5151,7 +5154,7 @@
         <v>90</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5167,13 +5170,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q64" s="5">
         <v>46125</v>
@@ -5193,7 +5196,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B65" s="8">
         <v>46065.55618413194</v>
@@ -5205,7 +5208,7 @@
         <v>46197.584207858796</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5229,7 +5232,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5246,7 +5249,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B66" s="5">
         <v>46065.55618443287</v>
@@ -5258,16 +5261,16 @@
         <v>46197.584189560184</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5283,13 +5286,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q66" s="5">
         <v>46191</v>
@@ -5309,7 +5312,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B67" s="8">
         <v>46065.55618472223</v>
@@ -5321,7 +5324,7 @@
         <v>46223.835604803244</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5330,7 +5333,7 @@
         <v>90</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5346,13 +5349,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q67" s="8">
         <v>46198</v>
@@ -5372,7 +5375,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B68" s="5">
         <v>46065.55618501158</v>
@@ -5384,16 +5387,16 @@
         <v>46203.17214591435</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5409,13 +5412,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q68" s="5">
         <v>46202</v>
@@ -5435,7 +5438,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B69" s="8">
         <v>46065.55618528935</v>
@@ -5447,16 +5450,16 @@
         <v>46204.17730309028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5472,13 +5475,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q69" s="8">
         <v>46203</v>
@@ -5498,7 +5501,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B70" s="5">
         <v>46065.55618287037</v>
@@ -5510,7 +5513,7 @@
         <v>46213.83000314815</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5534,7 +5537,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5545,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="T70" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U70" s="11" t="s">
         <v>32</v>
@@ -5553,7 +5556,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B71" s="8">
         <v>46065.55618353009</v>
@@ -5565,16 +5568,16 @@
         <v>46218.20642386574</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I71" s="8">
         <v>46206</v>
@@ -5592,13 +5595,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q71" s="8">
         <v>46217</v>
@@ -5618,7 +5621,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B72" s="5">
         <v>46065.55618322917</v>
@@ -5630,16 +5633,16 @@
         <v>46218.20642361111</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I72" s="5">
         <v>46206</v>
@@ -5657,13 +5660,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q72" s="5">
         <v>46217</v>
@@ -5683,7 +5686,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B73" s="8">
         <v>46086.62191810185</v>
@@ -5695,7 +5698,7 @@
         <v>46198.63326113426</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5719,7 +5722,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5736,7 +5739,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B74" s="5">
         <v>46086.62261061343</v>
@@ -5748,7 +5751,7 @@
         <v>46218.20642375</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5775,13 +5778,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q74" s="5">
         <v>46217</v>
@@ -5801,7 +5804,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B75" s="8">
         <v>46090.54719644676</v>
@@ -5813,7 +5816,7 @@
         <v>46219.18163760417</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5840,13 +5843,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q75" s="8">
         <v>46226</v>
@@ -5858,7 +5861,7 @@
         <v>1</v>
       </c>
       <c r="T75" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="U75" s="11" t="s">
         <v>32</v>

--- a/data/50001515 - CLIENTE POR DEFINIR B.xlsx
+++ b/data/50001515 - CLIENTE POR DEFINIR B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="272">
   <si>
     <t>50001515 - CLIENTE POR DEFINIR</t>
   </si>
@@ -827,9 +827,6 @@
   </si>
   <si>
     <t>Pruebas de instalación componentes</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
 </sst>
 </file>
@@ -5813,7 +5810,7 @@
         <v>46198.63323150463</v>
       </c>
       <c r="D75" s="8">
-        <v>46219.18163760417</v>
+        <v>46227.17110211805</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>271</v>
@@ -5860,8 +5857,8 @@
       <c r="S75" s="9">
         <v>1</v>
       </c>
-      <c r="T75" s="12" t="s">
-        <v>272</v>
+      <c r="T75" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U75" s="11" t="s">
         <v>32</v>
